--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mishra's Thirteen</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mishra's Thirteen</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D24" t="n">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -490,12 +490,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -511,12 +511,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -553,12 +553,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -574,12 +574,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -616,12 +616,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -637,12 +637,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -658,12 +658,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -679,12 +679,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -700,12 +700,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -721,12 +721,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -742,12 +742,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -784,12 +784,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -826,12 +826,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -847,12 +847,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -868,12 +868,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -889,12 +889,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -910,12 +910,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -952,12 +952,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -973,12 +973,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -994,12 +994,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1057,18 +1057,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>His Name is Diogo</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Fluente in Football</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1083,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,201 +1117,208 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
+        <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Yash Beohar</t>
         </is>
@@ -1431,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1454,7 +1482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1469,7 +1497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1484,7 +1512,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1499,7 +1527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1514,7 +1542,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1529,7 +1557,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1540,7 +1568,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1551,7 +1579,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1562,7 +1590,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1573,7 +1601,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1584,7 +1612,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1595,7 +1623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1606,7 +1634,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1617,7 +1645,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1628,7 +1656,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1639,7 +1667,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1650,7 +1678,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1661,7 +1689,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1672,7 +1700,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1683,7 +1711,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1694,7 +1722,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1705,7 +1733,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1716,7 +1744,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1727,7 +1755,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1738,7 +1766,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1749,7 +1777,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1760,7 +1788,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1771,7 +1799,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1782,13 +1810,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1801,7 +1840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,7 +1863,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1839,7 +1878,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1854,7 +1893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1869,7 +1908,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1884,7 +1923,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1899,7 +1938,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1910,7 +1949,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1921,7 +1960,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1932,7 +1971,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1943,7 +1982,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1954,7 +1993,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1965,7 +2004,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1976,7 +2015,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1987,7 +2026,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1998,7 +2037,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2009,7 +2048,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2020,7 +2059,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2031,7 +2070,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2042,7 +2081,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2053,7 +2092,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2064,7 +2103,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2075,7 +2114,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2086,7 +2125,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2097,7 +2136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2108,7 +2147,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2119,7 +2158,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2130,7 +2169,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2141,7 +2180,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2152,13 +2191,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2238,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2284,27 +2334,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1128645</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1128645</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2313,19 +2352,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2333,7 +2372,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
     </row>
     <row r="4">
@@ -2342,19 +2381,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2362,7 +2401,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
     </row>
     <row r="5">
@@ -2371,27 +2410,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>81907</v>
+        <v>117338</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>11118394</v>
+        <v>117338</v>
       </c>
     </row>
     <row r="6">
@@ -2400,19 +2439,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>71857</v>
+        <v>81907</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2420,7 +2459,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>297407</v>
+        <v>11118394</v>
       </c>
     </row>
     <row r="7">
@@ -2429,27 +2468,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>14603</v>
+        <v>71857</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>515830</v>
+        <v>297407</v>
       </c>
     </row>
     <row r="8">
@@ -2458,27 +2497,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>6474</v>
+        <v>14603</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6474</v>
+        <v>515830</v>
       </c>
     </row>
     <row r="9">
@@ -2487,27 +2526,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>1320699</v>
+        <v>6474</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1861933</v>
+        <v>6474</v>
       </c>
     </row>
     <row r="10">
@@ -2516,27 +2555,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>676529</v>
+        <v>1320699</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>676529</v>
+        <v>1861933</v>
       </c>
     </row>
     <row r="11">
@@ -2545,27 +2584,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>95791</v>
+        <v>676529</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5124417</v>
+        <v>676529</v>
       </c>
     </row>
     <row r="12">
@@ -2574,27 +2613,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>31543</v>
+        <v>95791</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1637750</v>
+        <v>5124417</v>
       </c>
     </row>
     <row r="13">
@@ -2603,27 +2642,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>189374</v>
+        <v>31543</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>250879</v>
+        <v>1637750</v>
       </c>
     </row>
     <row r="14">
@@ -2632,27 +2671,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>453230</v>
+        <v>189374</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8188106</v>
+        <v>250879</v>
       </c>
     </row>
     <row r="15">
@@ -2661,27 +2700,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>27153</v>
+        <v>453230</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>240451</v>
+        <v>8188106</v>
       </c>
     </row>
     <row r="16">
@@ -2690,27 +2729,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>273503</v>
+        <v>27153</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1917309</v>
+        <v>240451</v>
       </c>
     </row>
     <row r="17">
@@ -2719,27 +2758,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>4884220</v>
+        <v>273503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4884220</v>
+        <v>1917309</v>
       </c>
     </row>
     <row r="18">
@@ -2748,27 +2787,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>281617</v>
+        <v>4884220</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1076546</v>
+        <v>4884220</v>
       </c>
     </row>
     <row r="19">
@@ -2777,27 +2816,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>38561</v>
+        <v>281617</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>726260</v>
+        <v>1076546</v>
       </c>
     </row>
     <row r="20">
@@ -2806,27 +2845,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>8917</v>
+        <v>38561</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9146930</v>
+        <v>726260</v>
       </c>
     </row>
     <row r="21">
@@ -2835,19 +2874,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>28582</v>
+        <v>8917</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2855,7 +2894,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>239490</v>
+        <v>9146930</v>
       </c>
     </row>
     <row r="22">
@@ -2864,27 +2903,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>410102</v>
+        <v>28582</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5360778</v>
+        <v>239490</v>
       </c>
     </row>
     <row r="23">
@@ -2893,27 +2932,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>1615102</v>
+        <v>410102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6092784</v>
+        <v>5360778</v>
       </c>
     </row>
     <row r="24">
@@ -2922,27 +2961,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>334016</v>
+        <v>1615102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2691725</v>
+        <v>6092784</v>
       </c>
     </row>
     <row r="25">
@@ -2951,27 +2990,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>486041</v>
+        <v>334016</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1206623</v>
+        <v>2691725</v>
       </c>
     </row>
     <row r="26">
@@ -2980,27 +3019,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>37120</v>
+        <v>486041</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3349378</v>
+        <v>1206623</v>
       </c>
     </row>
     <row r="27">
@@ -3009,27 +3048,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>15136</v>
+        <v>37120</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>45077</v>
+        <v>3349378</v>
       </c>
     </row>
     <row r="28">
@@ -3038,27 +3077,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>182900</v>
+        <v>15136</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>182900</v>
+        <v>45077</v>
       </c>
     </row>
     <row r="29">
@@ -3067,27 +3106,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>15288</v>
+        <v>182900</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>538046</v>
+        <v>182900</v>
       </c>
     </row>
     <row r="30">
@@ -3096,26 +3135,55 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>His Name is Diogo</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15288</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>538046</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Fluente in Football</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E31" t="n">
         <v>30971</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>2018/19</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="G31" t="n">
         <v>58227</v>
       </c>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Hits (pts)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
@@ -483,6 +488,9 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -504,6 +512,9 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +536,9 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -546,6 +560,9 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -567,6 +584,9 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -588,6 +608,9 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -609,6 +632,9 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -630,6 +656,9 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,6 +680,9 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -672,6 +704,9 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -693,6 +728,9 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -714,6 +752,9 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -735,6 +776,9 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -756,6 +800,9 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -777,6 +824,9 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -798,6 +848,9 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -819,6 +872,9 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -840,6 +896,9 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -861,6 +920,9 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -882,6 +944,9 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -903,6 +968,9 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -924,6 +992,9 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -945,6 +1016,9 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -966,6 +1040,9 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -987,6 +1064,9 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1008,6 +1088,9 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1029,6 +1112,9 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1050,6 +1136,9 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1071,6 +1160,9 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1090,6 +1182,9 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,12 +474,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -498,12 +498,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -546,12 +546,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -570,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -594,12 +594,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -618,12 +618,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -642,12 +642,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -666,12 +666,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -690,12 +690,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -714,12 +714,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -738,12 +738,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -762,12 +762,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -810,12 +810,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -834,12 +834,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -858,12 +858,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -882,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -954,12 +954,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1170,21 +1170,45 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>His Name is Diogo</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Fluente in Football</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1199,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1212,208 +1236,215 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Yash Beohar</t>
         </is>
@@ -1554,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,7 +1608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1592,7 +1623,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1607,7 +1638,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1622,7 +1653,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1637,7 +1668,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1652,7 +1683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1663,7 +1694,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1674,7 +1705,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1685,7 +1716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1696,7 +1727,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1707,7 +1738,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1718,7 +1749,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1729,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1740,7 +1771,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1751,7 +1782,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1762,7 +1793,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1773,7 +1804,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1784,7 +1815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1795,7 +1826,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1806,7 +1837,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1817,7 +1848,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1828,7 +1859,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1839,7 +1870,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1850,7 +1881,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1861,7 +1892,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1872,7 +1903,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1883,7 +1914,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1894,7 +1925,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1905,7 +1936,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1916,13 +1947,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1935,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,7 +2000,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1973,7 +2015,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1988,7 +2030,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2003,7 +2045,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2018,7 +2060,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2033,7 +2075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2044,7 +2086,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2055,7 +2097,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2066,7 +2108,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2077,7 +2119,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2088,7 +2130,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2099,7 +2141,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2110,7 +2152,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2121,7 +2163,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2132,7 +2174,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2143,7 +2185,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2154,7 +2196,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2165,7 +2207,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2176,7 +2218,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2187,7 +2229,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2198,7 +2240,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2209,7 +2251,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2220,7 +2262,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2231,7 +2273,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2242,7 +2284,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2253,7 +2295,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2264,7 +2306,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2275,7 +2317,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2286,7 +2328,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2297,13 +2339,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2383,7 +2436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,16 +2482,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60517</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2015/16</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>339763</v>
       </c>
     </row>
     <row r="3">
@@ -2447,27 +2511,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1128645</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1128645</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2476,19 +2529,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2496,7 +2549,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
     </row>
     <row r="5">
@@ -2505,19 +2558,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2525,7 +2578,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
     </row>
     <row r="6">
@@ -2534,27 +2587,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>81907</v>
+        <v>117338</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11118394</v>
+        <v>117338</v>
       </c>
     </row>
     <row r="7">
@@ -2563,19 +2616,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>71857</v>
+        <v>81907</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2583,7 +2636,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>297407</v>
+        <v>11118394</v>
       </c>
     </row>
     <row r="8">
@@ -2592,27 +2645,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>14603</v>
+        <v>71857</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>515830</v>
+        <v>297407</v>
       </c>
     </row>
     <row r="9">
@@ -2621,27 +2674,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>6474</v>
+        <v>14603</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6474</v>
+        <v>515830</v>
       </c>
     </row>
     <row r="10">
@@ -2650,27 +2703,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>1320699</v>
+        <v>6474</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1861933</v>
+        <v>6474</v>
       </c>
     </row>
     <row r="11">
@@ -2679,27 +2732,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>676529</v>
+        <v>1320699</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>676529</v>
+        <v>1861933</v>
       </c>
     </row>
     <row r="12">
@@ -2708,27 +2761,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>95791</v>
+        <v>676529</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5124417</v>
+        <v>676529</v>
       </c>
     </row>
     <row r="13">
@@ -2737,27 +2790,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>31543</v>
+        <v>95791</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1637750</v>
+        <v>5124417</v>
       </c>
     </row>
     <row r="14">
@@ -2766,27 +2819,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>189374</v>
+        <v>31543</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>250879</v>
+        <v>1637750</v>
       </c>
     </row>
     <row r="15">
@@ -2795,27 +2848,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>453230</v>
+        <v>189374</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8188106</v>
+        <v>250879</v>
       </c>
     </row>
     <row r="16">
@@ -2824,27 +2877,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>27153</v>
+        <v>453230</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>240451</v>
+        <v>8188106</v>
       </c>
     </row>
     <row r="17">
@@ -2853,27 +2906,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>273503</v>
+        <v>27153</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1917309</v>
+        <v>240451</v>
       </c>
     </row>
     <row r="18">
@@ -2882,27 +2935,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>4884220</v>
+        <v>273503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4884220</v>
+        <v>1917309</v>
       </c>
     </row>
     <row r="19">
@@ -2911,27 +2964,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>281617</v>
+        <v>4884220</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1076546</v>
+        <v>4884220</v>
       </c>
     </row>
     <row r="20">
@@ -2940,27 +2993,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>38561</v>
+        <v>281617</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>726260</v>
+        <v>1076546</v>
       </c>
     </row>
     <row r="21">
@@ -2969,27 +3022,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>8917</v>
+        <v>38561</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>9146930</v>
+        <v>726260</v>
       </c>
     </row>
     <row r="22">
@@ -2998,19 +3051,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>28582</v>
+        <v>8917</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3018,7 +3071,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>239490</v>
+        <v>9146930</v>
       </c>
     </row>
     <row r="23">
@@ -3027,27 +3080,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>410102</v>
+        <v>28582</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5360778</v>
+        <v>239490</v>
       </c>
     </row>
     <row r="24">
@@ -3056,27 +3109,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>1615102</v>
+        <v>410102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>6092784</v>
+        <v>5360778</v>
       </c>
     </row>
     <row r="25">
@@ -3085,27 +3138,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>334016</v>
+        <v>1615102</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2691725</v>
+        <v>6092784</v>
       </c>
     </row>
     <row r="26">
@@ -3114,27 +3167,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>486041</v>
+        <v>334016</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1206623</v>
+        <v>2691725</v>
       </c>
     </row>
     <row r="27">
@@ -3143,27 +3196,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>37120</v>
+        <v>486041</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3349378</v>
+        <v>1206623</v>
       </c>
     </row>
     <row r="28">
@@ -3172,27 +3225,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>15136</v>
+        <v>37120</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>45077</v>
+        <v>3349378</v>
       </c>
     </row>
     <row r="29">
@@ -3201,27 +3254,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>182900</v>
+        <v>15136</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>182900</v>
+        <v>45077</v>
       </c>
     </row>
     <row r="30">
@@ -3230,27 +3283,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>15288</v>
+        <v>182900</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>538046</v>
+        <v>182900</v>
       </c>
     </row>
     <row r="31">
@@ -3259,26 +3312,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>His Name is Diogo</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" t="n">
+        <v>15288</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>538046</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Yash Beohar</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Fluente in Football</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E32" t="n">
         <v>30971</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>2018/19</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="G32" t="n">
         <v>58227</v>
       </c>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -15,7 +15,8 @@
     <sheet name="Comeback" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Differential Diamond" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Profiles" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Pity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Season Stats" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Pity" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1217,6 +1218,52 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ruled-out starters</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Valid?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3375,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,29 +3433,1158 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Avg GW</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ruled-out starters</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Valid?</t>
-        </is>
-      </c>
+          <t>Cap Return</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>High GW</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Low GW</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transfers</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Hits (n)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Hits (pts)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Squad £m</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Value Δ £m</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Bank £m</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Global Rank</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Best Jump</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Best Jump GW</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Parakh Tripathy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Malisahi Randuas</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pranav Thomas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Invincibles</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Deepankar Sachdeva</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cment_mixers</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ajith Thomas Kuthukatt George</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Onside Offside</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>prateek gupta</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sakalaka</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Karan Chopra</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fpl_26_27</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aquib Razack</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BattleBorn</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Satweek Nayak</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Xa bing chilling</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arshaq Razack</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ShakeNBake</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rohan Agrawal</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Southall United</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dean Jenkins</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Slumber FC</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ashwin Jose</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pole Calmer �</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shivanshu Madan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cold Palmer</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sid Shaurya</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Old Reijnders Nagar</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Karan Khanna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Amad Aura</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Abhinav Premsekhar</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Totally Szobo</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Danish Javed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ItDzntMata</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nilay jain</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Redsbay</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Anish Joshi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fiery Raiders</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Abhay Rawat</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>115 FC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Raveesh Kalra</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MaSalah</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Abhiraj Singh</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KingOfKings Fc</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Varun Khurana</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goal Diggers FC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rajit Das</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FC Teetotallers</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aparnesh Mishra</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mishra's 13</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Aayush Khanna</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Loading...</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Abhishek Gupte</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Enzotic</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Naman Agrawal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Captn Magnifico</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pranshul Jain</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Carrick Janta Party</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>His Name is Diogo</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Yash Beohar</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fluente in Football</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -2483,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2519,7 +2519,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Avg Rank</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Last Season Rank</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Last Season</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2559,15 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>1414622</v>
+      </c>
+      <c r="H2" t="n">
         <v>339763</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2596,7 +2614,15 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3434302</v>
+      </c>
+      <c r="H4" t="n">
         <v>1128645</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2625,7 +2651,15 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>604934</v>
+      </c>
+      <c r="H5" t="n">
         <v>545267</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2654,7 +2688,15 @@
         </is>
       </c>
       <c r="G6" t="n">
+        <v>4684930</v>
+      </c>
+      <c r="H6" t="n">
         <v>117338</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2683,7 +2725,15 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>3252487</v>
+      </c>
+      <c r="H7" t="n">
         <v>11118394</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2712,7 +2762,15 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>1929309</v>
+      </c>
+      <c r="H8" t="n">
         <v>297407</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2741,7 +2799,15 @@
         </is>
       </c>
       <c r="G9" t="n">
+        <v>949628</v>
+      </c>
+      <c r="H9" t="n">
         <v>515830</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2770,7 +2836,15 @@
         </is>
       </c>
       <c r="G10" t="n">
+        <v>1177681</v>
+      </c>
+      <c r="H10" t="n">
         <v>6474</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2799,7 +2873,15 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2490743</v>
+      </c>
+      <c r="H11" t="n">
         <v>1861933</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2828,7 +2910,15 @@
         </is>
       </c>
       <c r="G12" t="n">
+        <v>998938</v>
+      </c>
+      <c r="H12" t="n">
         <v>676529</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2857,7 +2947,15 @@
         </is>
       </c>
       <c r="G13" t="n">
+        <v>2404119</v>
+      </c>
+      <c r="H13" t="n">
         <v>5124417</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2886,7 +2984,15 @@
         </is>
       </c>
       <c r="G14" t="n">
+        <v>820692</v>
+      </c>
+      <c r="H14" t="n">
         <v>1637750</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2915,7 +3021,15 @@
         </is>
       </c>
       <c r="G15" t="n">
+        <v>1757289</v>
+      </c>
+      <c r="H15" t="n">
         <v>250879</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -2944,7 +3058,15 @@
         </is>
       </c>
       <c r="G16" t="n">
+        <v>5483351</v>
+      </c>
+      <c r="H16" t="n">
         <v>8188106</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -2973,7 +3095,15 @@
         </is>
       </c>
       <c r="G17" t="n">
+        <v>606381</v>
+      </c>
+      <c r="H17" t="n">
         <v>240451</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -3002,7 +3132,15 @@
         </is>
       </c>
       <c r="G18" t="n">
+        <v>1994005</v>
+      </c>
+      <c r="H18" t="n">
         <v>1917309</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -3033,6 +3171,14 @@
       <c r="G19" t="n">
         <v>4884220</v>
       </c>
+      <c r="H19" t="n">
+        <v>4884220</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3060,7 +3206,15 @@
         </is>
       </c>
       <c r="G20" t="n">
+        <v>1051323</v>
+      </c>
+      <c r="H20" t="n">
         <v>1076546</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3089,7 +3243,15 @@
         </is>
       </c>
       <c r="G21" t="n">
+        <v>858178</v>
+      </c>
+      <c r="H21" t="n">
         <v>726260</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -3118,7 +3280,15 @@
         </is>
       </c>
       <c r="G22" t="n">
+        <v>2118382</v>
+      </c>
+      <c r="H22" t="n">
         <v>9146930</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3147,7 +3317,15 @@
         </is>
       </c>
       <c r="G23" t="n">
+        <v>881388</v>
+      </c>
+      <c r="H23" t="n">
         <v>239490</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -3176,7 +3354,15 @@
         </is>
       </c>
       <c r="G24" t="n">
+        <v>2088802</v>
+      </c>
+      <c r="H24" t="n">
         <v>5360778</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -3205,7 +3391,15 @@
         </is>
       </c>
       <c r="G25" t="n">
+        <v>4234674</v>
+      </c>
+      <c r="H25" t="n">
         <v>6092784</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -3234,7 +3428,15 @@
         </is>
       </c>
       <c r="G26" t="n">
+        <v>2156629</v>
+      </c>
+      <c r="H26" t="n">
         <v>2691725</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -3263,7 +3465,15 @@
         </is>
       </c>
       <c r="G27" t="n">
+        <v>2415786</v>
+      </c>
+      <c r="H27" t="n">
         <v>1206623</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -3292,7 +3502,15 @@
         </is>
       </c>
       <c r="G28" t="n">
+        <v>1571193</v>
+      </c>
+      <c r="H28" t="n">
         <v>3349378</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -3321,7 +3539,15 @@
         </is>
       </c>
       <c r="G29" t="n">
+        <v>983840</v>
+      </c>
+      <c r="H29" t="n">
         <v>45077</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -3350,7 +3576,15 @@
         </is>
       </c>
       <c r="G30" t="n">
+        <v>2098988</v>
+      </c>
+      <c r="H30" t="n">
         <v>182900</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3379,7 +3613,15 @@
         </is>
       </c>
       <c r="G31" t="n">
+        <v>329510</v>
+      </c>
+      <c r="H31" t="n">
         <v>538046</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -3408,7 +3650,15 @@
         </is>
       </c>
       <c r="G32" t="n">
+        <v>820221</v>
+      </c>
+      <c r="H32" t="n">
         <v>58227</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,22 +475,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -499,190 +499,190 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pranshul Jain</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Carrick Janta Party</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Deepankar Sachdeva</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cment_mixers</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -691,195 +691,195 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -892,85 +892,85 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -979,238 +979,238 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1283,119 +1283,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
@@ -1409,91 +1409,91 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1994,7 +1994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2005,7 +2005,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2047,7 +2047,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2386,7 +2386,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2397,7 +2397,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2539,30 +2539,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>60517</v>
+        <v>676529</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1414622</v>
+        <v>998938</v>
       </c>
       <c r="H2" t="n">
-        <v>339763</v>
+        <v>676529</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2576,37 +2576,56 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30971</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2018/19</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>820221</v>
+      </c>
+      <c r="H3" t="n">
+        <v>58227</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>1128645</v>
+        <v>182900</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2614,10 +2633,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3434302</v>
+        <v>2098988</v>
       </c>
       <c r="H4" t="n">
-        <v>1128645</v>
+        <v>182900</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2627,34 +2646,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>545267</v>
+        <v>37120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>604934</v>
+        <v>1571193</v>
       </c>
       <c r="H5" t="n">
-        <v>545267</v>
+        <v>3349378</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2664,34 +2683,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>117338</v>
+        <v>71857</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4684930</v>
+        <v>1929309</v>
       </c>
       <c r="H6" t="n">
-        <v>117338</v>
+        <v>297407</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2701,34 +2720,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>81907</v>
+        <v>486041</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3252487</v>
+        <v>2415786</v>
       </c>
       <c r="H7" t="n">
-        <v>11118394</v>
+        <v>1206623</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2738,34 +2757,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>71857</v>
+        <v>15136</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1929309</v>
+        <v>983840</v>
       </c>
       <c r="H8" t="n">
-        <v>297407</v>
+        <v>45077</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2775,34 +2794,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>14603</v>
+        <v>95791</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>949628</v>
+        <v>2404119</v>
       </c>
       <c r="H9" t="n">
-        <v>515830</v>
+        <v>5124417</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2812,34 +2831,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>6474</v>
+        <v>28582</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1177681</v>
+        <v>881388</v>
       </c>
       <c r="H10" t="n">
-        <v>6474</v>
+        <v>239490</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2853,67 +2872,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>1320699</v>
+        <v>31543</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2490743</v>
+        <v>820692</v>
       </c>
       <c r="H11" t="n">
-        <v>1861933</v>
+        <v>1637750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>676529</v>
+        <v>453230</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>998938</v>
+        <v>5483351</v>
       </c>
       <c r="H12" t="n">
-        <v>676529</v>
+        <v>8188106</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2923,34 +2942,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>His Name is Diogo</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ashwin Jose</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pole Calmer �</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11</v>
-      </c>
       <c r="E13" t="n">
-        <v>95791</v>
+        <v>15288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2404119</v>
+        <v>329510</v>
       </c>
       <c r="H13" t="n">
-        <v>5124417</v>
+        <v>538046</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2960,23 +2979,23 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>31543</v>
+        <v>27153</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2984,10 +3003,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>820692</v>
+        <v>606381</v>
       </c>
       <c r="H14" t="n">
-        <v>1637750</v>
+        <v>240451</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2997,34 +3016,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>189374</v>
+        <v>6474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1757289</v>
+        <v>1177681</v>
       </c>
       <c r="H15" t="n">
-        <v>250879</v>
+        <v>6474</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3034,34 +3053,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>453230</v>
+        <v>189374</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5483351</v>
+        <v>1757289</v>
       </c>
       <c r="H16" t="n">
-        <v>8188106</v>
+        <v>250879</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3071,34 +3090,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>27153</v>
+        <v>38561</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>606381</v>
+        <v>858178</v>
       </c>
       <c r="H17" t="n">
-        <v>240451</v>
+        <v>726260</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3108,34 +3127,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>273503</v>
+        <v>410102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1994005</v>
+        <v>2088802</v>
       </c>
       <c r="H18" t="n">
-        <v>1917309</v>
+        <v>5360778</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3145,7 +3164,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3182,34 +3201,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>281617</v>
+        <v>545267</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1051323</v>
+        <v>604934</v>
       </c>
       <c r="H20" t="n">
-        <v>1076546</v>
+        <v>545267</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3219,71 +3238,71 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H21" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>8917</v>
+        <v>1615102</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2118382</v>
+        <v>4234674</v>
       </c>
       <c r="H22" t="n">
-        <v>9146930</v>
+        <v>6092784</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3297,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>28582</v>
+        <v>273503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>881388</v>
+        <v>1994005</v>
       </c>
       <c r="H23" t="n">
-        <v>239490</v>
+        <v>1917309</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3330,71 +3349,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
-      </c>
-      <c r="E24" t="n">
-        <v>410102</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2009/10</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>2088802</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5360778</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>1615102</v>
+        <v>117338</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4234674</v>
+        <v>4684930</v>
       </c>
       <c r="H25" t="n">
-        <v>6092784</v>
+        <v>117338</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3404,34 +3404,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>334016</v>
+        <v>14603</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2156629</v>
+        <v>949628</v>
       </c>
       <c r="H26" t="n">
-        <v>2691725</v>
+        <v>515830</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3441,34 +3441,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>486041</v>
+        <v>281617</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2415786</v>
+        <v>1051323</v>
       </c>
       <c r="H27" t="n">
-        <v>1206623</v>
+        <v>1076546</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3478,34 +3478,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>37120</v>
+        <v>334016</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1571193</v>
+        <v>2156629</v>
       </c>
       <c r="H28" t="n">
-        <v>3349378</v>
+        <v>2691725</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3515,34 +3515,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>15136</v>
+        <v>60517</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>983840</v>
+        <v>1414622</v>
       </c>
       <c r="H29" t="n">
-        <v>45077</v>
+        <v>339763</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3552,34 +3552,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>182900</v>
+        <v>8917</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2098988</v>
+        <v>2118382</v>
       </c>
       <c r="H30" t="n">
-        <v>182900</v>
+        <v>9146930</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>15288</v>
+        <v>81907</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>329510</v>
+        <v>3252487</v>
       </c>
       <c r="H31" t="n">
-        <v>538046</v>
+        <v>11118394</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3626,34 +3626,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>30971</v>
+        <v>1128645</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>820221</v>
+        <v>3434302</v>
       </c>
       <c r="H32" t="n">
-        <v>58227</v>
+        <v>1128645</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3819,16 +3819,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3853,16 +3853,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3887,16 +3887,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3921,16 +3921,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3955,16 +3955,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3989,16 +3989,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4023,16 +4023,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4057,16 +4057,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4091,16 +4091,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4125,16 +4125,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4159,16 +4159,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4193,16 +4193,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4227,16 +4227,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4261,16 +4261,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4295,16 +4295,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4329,16 +4329,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4397,16 +4397,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4431,16 +4431,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4465,16 +4465,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4499,16 +4499,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4533,16 +4533,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4567,16 +4567,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4601,16 +4601,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4635,16 +4635,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4669,16 +4669,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4703,16 +4703,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4737,16 +4737,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -4771,16 +4771,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -4805,16 +4805,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -499,22 +499,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -523,27 +523,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -556,133 +556,133 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -691,27 +691,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -724,18 +724,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -748,229 +748,229 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -979,22 +979,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1123,22 +1123,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1156,61 +1156,61 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1290,14 +1290,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
@@ -1311,42 +1311,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
@@ -1367,112 +1367,112 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1486,14 +1486,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1994,7 +1994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2005,7 +2005,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2386,7 +2386,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2397,7 +2397,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>30971</v>
+        <v>15136</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>820221</v>
+        <v>983840</v>
       </c>
       <c r="H3" t="n">
-        <v>58227</v>
+        <v>45077</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2613,30 +2613,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>182900</v>
+        <v>28582</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2098988</v>
+        <v>881388</v>
       </c>
       <c r="H4" t="n">
-        <v>182900</v>
+        <v>239490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2683,34 +2683,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H6" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2720,34 +2720,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>486041</v>
+        <v>71857</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2415786</v>
+        <v>1929309</v>
       </c>
       <c r="H7" t="n">
-        <v>1206623</v>
+        <v>297407</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2757,34 +2757,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>15136</v>
+        <v>182900</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>983840</v>
+        <v>2098988</v>
       </c>
       <c r="H8" t="n">
-        <v>45077</v>
+        <v>182900</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2794,34 +2794,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>95791</v>
+        <v>31543</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2404119</v>
+        <v>820692</v>
       </c>
       <c r="H9" t="n">
-        <v>5124417</v>
+        <v>1637750</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2831,34 +2831,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>28582</v>
+        <v>486041</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>881388</v>
+        <v>2415786</v>
       </c>
       <c r="H10" t="n">
-        <v>239490</v>
+        <v>1206623</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>31543</v>
+        <v>30971</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820692</v>
+        <v>820221</v>
       </c>
       <c r="H11" t="n">
-        <v>1637750</v>
+        <v>58227</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2979,34 +2979,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>27153</v>
+        <v>6474</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>606381</v>
+        <v>1177681</v>
       </c>
       <c r="H14" t="n">
-        <v>240451</v>
+        <v>6474</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3016,23 +3016,23 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>6474</v>
+        <v>545267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1177681</v>
+        <v>604934</v>
       </c>
       <c r="H15" t="n">
-        <v>6474</v>
+        <v>545267</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3053,34 +3053,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>189374</v>
+        <v>38561</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1757289</v>
+        <v>858178</v>
       </c>
       <c r="H16" t="n">
-        <v>250879</v>
+        <v>726260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3090,34 +3090,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>38561</v>
+        <v>189374</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>858178</v>
+        <v>1757289</v>
       </c>
       <c r="H17" t="n">
-        <v>726260</v>
+        <v>250879</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3127,34 +3127,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>410102</v>
+        <v>1615102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2088802</v>
+        <v>4234674</v>
       </c>
       <c r="H18" t="n">
-        <v>5360778</v>
+        <v>6092784</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3164,34 +3164,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>4884220</v>
+        <v>410102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4884220</v>
+        <v>2088802</v>
       </c>
       <c r="H19" t="n">
-        <v>4884220</v>
+        <v>5360778</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3201,108 +3201,108 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>545267</v>
+        <v>1320699</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>604934</v>
+        <v>2490743</v>
       </c>
       <c r="H20" t="n">
-        <v>545267</v>
+        <v>1861933</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>1320699</v>
+        <v>27153</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2490743</v>
+        <v>606381</v>
       </c>
       <c r="H21" t="n">
-        <v>1861933</v>
+        <v>240451</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>1615102</v>
+        <v>4884220</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4234674</v>
+        <v>4884220</v>
       </c>
       <c r="H22" t="n">
-        <v>6092784</v>
+        <v>4884220</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>273503</v>
+        <v>117338</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1994005</v>
+        <v>4684930</v>
       </c>
       <c r="H23" t="n">
-        <v>1917309</v>
+        <v>117338</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,16 +3353,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1128645</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>3434302</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1128645</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -3371,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>117338</v>
+        <v>281617</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4684930</v>
+        <v>1051323</v>
       </c>
       <c r="H25" t="n">
-        <v>117338</v>
+        <v>1076546</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3408,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>14603</v>
+        <v>334016</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>949628</v>
+        <v>2156629</v>
       </c>
       <c r="H26" t="n">
-        <v>515830</v>
+        <v>2691725</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3445,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>281617</v>
+        <v>60517</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1051323</v>
+        <v>1414622</v>
       </c>
       <c r="H27" t="n">
-        <v>1076546</v>
+        <v>339763</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3482,19 +3501,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3502,10 +3521,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H28" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3519,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>60517</v>
+        <v>273503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1414622</v>
+        <v>1994005</v>
       </c>
       <c r="H29" t="n">
-        <v>339763</v>
+        <v>1917309</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3589,34 +3608,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>81907</v>
+        <v>14603</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3252487</v>
+        <v>949628</v>
       </c>
       <c r="H31" t="n">
-        <v>11118394</v>
+        <v>515830</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3626,39 +3645,20 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1128645</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>3434302</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1128645</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3819,16 +3819,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3853,16 +3853,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3921,16 +3921,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3955,16 +3955,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3989,16 +3989,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4023,16 +4023,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4057,16 +4057,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4091,16 +4091,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4193,16 +4193,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4227,16 +4227,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4261,16 +4261,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4295,16 +4295,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4329,16 +4329,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4363,16 +4363,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4397,16 +4397,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4431,16 +4431,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4465,16 +4465,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4499,16 +4499,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4533,16 +4533,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4560,6 +4560,15 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>100</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -4567,16 +4576,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4601,16 +4610,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4635,16 +4644,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4669,16 +4678,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4703,16 +4712,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4746,7 +4755,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -4771,16 +4780,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -4805,16 +4814,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
@@ -1353,49 +1353,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
@@ -1409,14 +1409,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
@@ -1430,14 +1430,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
@@ -1451,21 +1451,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>95791</v>
+        <v>71857</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2404119</v>
+        <v>1929309</v>
       </c>
       <c r="H6" t="n">
-        <v>5124417</v>
+        <v>297407</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H7" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2909,34 +2909,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>453230</v>
+        <v>1320699</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5483351</v>
+        <v>2490743</v>
       </c>
       <c r="H12" t="n">
-        <v>8188106</v>
+        <v>1861933</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>15288</v>
+        <v>27153</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>329510</v>
+        <v>606381</v>
       </c>
       <c r="H13" t="n">
-        <v>538046</v>
+        <v>240451</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>6474</v>
+        <v>38561</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1177681</v>
+        <v>858178</v>
       </c>
       <c r="H14" t="n">
-        <v>6474</v>
+        <v>726260</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3020,19 +3020,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>545267</v>
+        <v>6474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>604934</v>
+        <v>1177681</v>
       </c>
       <c r="H15" t="n">
-        <v>545267</v>
+        <v>6474</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>38561</v>
+        <v>189374</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>858178</v>
+        <v>1757289</v>
       </c>
       <c r="H16" t="n">
-        <v>726260</v>
+        <v>250879</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>189374</v>
+        <v>453230</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1757289</v>
+        <v>5483351</v>
       </c>
       <c r="H17" t="n">
-        <v>250879</v>
+        <v>8188106</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>1615102</v>
+        <v>15288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4234674</v>
+        <v>329510</v>
       </c>
       <c r="H18" t="n">
-        <v>6092784</v>
+        <v>538046</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3205,34 +3205,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>1320699</v>
+        <v>545267</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2490743</v>
+        <v>604934</v>
       </c>
       <c r="H20" t="n">
-        <v>1861933</v>
+        <v>545267</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>27153</v>
+        <v>1615102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>606381</v>
+        <v>4234674</v>
       </c>
       <c r="H21" t="n">
-        <v>240451</v>
+        <v>6092784</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>117338</v>
+        <v>81907</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4684930</v>
+        <v>3252487</v>
       </c>
       <c r="H23" t="n">
-        <v>117338</v>
+        <v>11118394</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>1128645</v>
+        <v>60517</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3434302</v>
+        <v>1414622</v>
       </c>
       <c r="H24" t="n">
-        <v>1128645</v>
+        <v>339763</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>334016</v>
+        <v>8917</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2156629</v>
+        <v>2118382</v>
       </c>
       <c r="H26" t="n">
-        <v>2691725</v>
+        <v>9146930</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>60517</v>
+        <v>1128645</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1414622</v>
+        <v>3434302</v>
       </c>
       <c r="H27" t="n">
-        <v>339763</v>
+        <v>1128645</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3501,19 +3501,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H28" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>8917</v>
+        <v>117338</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2118382</v>
+        <v>4684930</v>
       </c>
       <c r="H30" t="n">
-        <v>9146930</v>
+        <v>117338</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3812,7 +3812,19 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>63521</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
@@ -3848,7 +3860,23 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>239174</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3882,7 +3910,23 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>239174</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3914,19 +3958,31 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>100</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>510626</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3950,17 +4006,33 @@
       <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>885437</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3984,6 +4056,18 @@
       <c r="N7" t="n">
         <v>0</v>
       </c>
+      <c r="O7" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>885437</v>
+      </c>
       <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4018,6 +4102,18 @@
       <c r="N8" t="n">
         <v>0</v>
       </c>
+      <c r="O8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>885437</v>
+      </c>
       <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4050,7 +4146,19 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1381598</v>
       </c>
       <c r="U9" t="inlineStr"/>
     </row>
@@ -4084,7 +4192,19 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1886838</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
@@ -4120,17 +4240,33 @@
       <c r="N11" t="n">
         <v>0</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2147456</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4152,19 +4288,31 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>100</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2683415</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4188,17 +4336,33 @@
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>100</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2683415</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4220,19 +4384,31 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="O14" t="n">
+        <v>100</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2683415</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4256,17 +4432,33 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2683415</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4288,19 +4480,31 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>100</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2683415</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4324,17 +4528,29 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
+      <c r="O17" t="n">
+        <v>100</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2683415</v>
+      </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4356,7 +4572,19 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>100</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2683415</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
@@ -4390,19 +4618,31 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>100</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2683415</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4426,17 +4666,29 @@
       <c r="N20" t="n">
         <v>0</v>
       </c>
+      <c r="O20" t="n">
+        <v>100</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2683415</v>
+      </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4460,7 +4712,23 @@
       <c r="N21" t="n">
         <v>0</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2683415</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4492,19 +4760,31 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>100</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4711763</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4528,17 +4808,29 @@
       <c r="N23" t="n">
         <v>0</v>
       </c>
+      <c r="O23" t="n">
+        <v>100</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5439838</v>
+      </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4571,6 +4863,9 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
+      <c r="R24" t="n">
+        <v>5439838</v>
+      </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -4605,17 +4900,33 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>100</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5439838</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4639,17 +4950,33 @@
       <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>100</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5439838</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4673,17 +5000,29 @@
       <c r="N27" t="n">
         <v>0</v>
       </c>
+      <c r="O27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>5439838</v>
+      </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4705,7 +5044,19 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>100</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>5439838</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
@@ -4739,19 +5090,31 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>100</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5439838</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4773,7 +5136,19 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>100</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5439838</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
@@ -4807,7 +5182,19 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>100</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6699465</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -4842,6 +5229,18 @@
       </c>
       <c r="N32" t="n">
         <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>100</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7752425</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -499,12 +499,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,12 +523,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1290,14 +1290,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
@@ -1367,28 +1367,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
@@ -1402,21 +1402,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
@@ -1444,42 +1444,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2576,19 +2576,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>15136</v>
+        <v>28582</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>983840</v>
+        <v>881388</v>
       </c>
       <c r="H3" t="n">
-        <v>45077</v>
+        <v>239490</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2613,19 +2613,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>28582</v>
+        <v>15136</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>881388</v>
+        <v>983840</v>
       </c>
       <c r="H4" t="n">
-        <v>239490</v>
+        <v>45077</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H6" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>95791</v>
+        <v>71857</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2404119</v>
+        <v>1929309</v>
       </c>
       <c r="H7" t="n">
-        <v>5124417</v>
+        <v>297407</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2909,34 +2909,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>1320699</v>
+        <v>453230</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2490743</v>
+        <v>5483351</v>
       </c>
       <c r="H12" t="n">
-        <v>1861933</v>
+        <v>8188106</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -2983,34 +2983,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H14" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>6474</v>
+        <v>410102</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1177681</v>
+        <v>2088802</v>
       </c>
       <c r="H15" t="n">
-        <v>6474</v>
+        <v>5360778</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>189374</v>
+        <v>545267</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1757289</v>
+        <v>604934</v>
       </c>
       <c r="H16" t="n">
-        <v>250879</v>
+        <v>545267</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>453230</v>
+        <v>189374</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5483351</v>
+        <v>1757289</v>
       </c>
       <c r="H17" t="n">
-        <v>8188106</v>
+        <v>250879</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>410102</v>
+        <v>6474</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2088802</v>
+        <v>1177681</v>
       </c>
       <c r="H19" t="n">
-        <v>5360778</v>
+        <v>6474</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>545267</v>
+        <v>1615102</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>604934</v>
+        <v>4234674</v>
       </c>
       <c r="H20" t="n">
-        <v>545267</v>
+        <v>6092784</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>1615102</v>
+        <v>38561</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4234674</v>
+        <v>858178</v>
       </c>
       <c r="H21" t="n">
-        <v>6092784</v>
+        <v>726260</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>281617</v>
+        <v>1128645</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1051323</v>
+        <v>3434302</v>
       </c>
       <c r="H25" t="n">
-        <v>1076546</v>
+        <v>1128645</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>8917</v>
+        <v>273503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2118382</v>
+        <v>1994005</v>
       </c>
       <c r="H26" t="n">
-        <v>9146930</v>
+        <v>1917309</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>1128645</v>
+        <v>8917</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3434302</v>
+        <v>2118382</v>
       </c>
       <c r="H27" t="n">
-        <v>1128645</v>
+        <v>9146930</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>334016</v>
+        <v>117338</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2156629</v>
+        <v>4684930</v>
       </c>
       <c r="H28" t="n">
-        <v>2691725</v>
+        <v>117338</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>273503</v>
+        <v>334016</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1994005</v>
+        <v>2156629</v>
       </c>
       <c r="H29" t="n">
-        <v>1917309</v>
+        <v>2691725</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>117338</v>
+        <v>281617</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4684930</v>
+        <v>1051323</v>
       </c>
       <c r="H30" t="n">
-        <v>117338</v>
+        <v>1076546</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3831,12 +3831,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3881,12 +3881,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3977,12 +3977,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4018,21 +4018,17 @@
       <c r="R6" t="n">
         <v>885437</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4068,7 +4064,11 @@
       <c r="R7" t="n">
         <v>885437</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4261,12 +4261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4357,12 +4357,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4403,12 +4403,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4444,21 +4444,17 @@
       <c r="R15" t="n">
         <v>2683415</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4480,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4499,12 +4495,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4526,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4591,12 +4587,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4618,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4632,17 +4628,21 @@
       <c r="R19" t="n">
         <v>2683415</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4678,17 +4678,21 @@
       <c r="R20" t="n">
         <v>2683415</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4710,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4724,11 +4728,7 @@
       <c r="R21" t="n">
         <v>2683415</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4871,12 +4871,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4912,21 +4912,17 @@
       <c r="R25" t="n">
         <v>5439838</v>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4948,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4962,21 +4958,17 @@
       <c r="R26" t="n">
         <v>5439838</v>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5012,17 +5004,21 @@
       <c r="R27" t="n">
         <v>5439838</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5053,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>5439838</v>
@@ -5063,12 +5059,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5099,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R29" t="n">
         <v>5439838</v>
@@ -5109,12 +5105,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5136,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5150,7 +5146,11 @@
       <c r="R30" t="n">
         <v>5439838</v>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -499,12 +499,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,12 +523,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -619,12 +619,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1290,14 +1290,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
@@ -1311,21 +1311,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
@@ -1353,70 +1353,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
@@ -1430,21 +1430,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
@@ -1458,28 +1458,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2576,19 +2576,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>28582</v>
+        <v>15136</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>881388</v>
+        <v>983840</v>
       </c>
       <c r="H3" t="n">
-        <v>239490</v>
+        <v>45077</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2613,19 +2613,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>15136</v>
+        <v>28582</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>983840</v>
+        <v>881388</v>
       </c>
       <c r="H4" t="n">
-        <v>45077</v>
+        <v>239490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>95791</v>
+        <v>182900</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2404119</v>
+        <v>2098988</v>
       </c>
       <c r="H6" t="n">
-        <v>5124417</v>
+        <v>182900</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H7" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2761,30 +2761,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>182900</v>
+        <v>71857</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2098988</v>
+        <v>1929309</v>
       </c>
       <c r="H8" t="n">
-        <v>182900</v>
+        <v>297407</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>453230</v>
+        <v>189374</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5483351</v>
+        <v>1757289</v>
       </c>
       <c r="H12" t="n">
-        <v>8188106</v>
+        <v>250879</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>27153</v>
+        <v>15288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>606381</v>
+        <v>329510</v>
       </c>
       <c r="H13" t="n">
-        <v>240451</v>
+        <v>538046</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,34 +2983,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>1320699</v>
+        <v>453230</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2490743</v>
+        <v>5483351</v>
       </c>
       <c r="H14" t="n">
-        <v>1861933</v>
+        <v>8188106</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>410102</v>
+        <v>545267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2088802</v>
+        <v>604934</v>
       </c>
       <c r="H15" t="n">
-        <v>5360778</v>
+        <v>545267</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>545267</v>
+        <v>1615102</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>604934</v>
+        <v>4234674</v>
       </c>
       <c r="H16" t="n">
-        <v>545267</v>
+        <v>6092784</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>189374</v>
+        <v>410102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1757289</v>
+        <v>2088802</v>
       </c>
       <c r="H17" t="n">
-        <v>250879</v>
+        <v>5360778</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>15288</v>
+        <v>27153</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>329510</v>
+        <v>606381</v>
       </c>
       <c r="H18" t="n">
-        <v>538046</v>
+        <v>240451</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>6474</v>
+        <v>38561</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1177681</v>
+        <v>858178</v>
       </c>
       <c r="H19" t="n">
-        <v>6474</v>
+        <v>726260</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,34 +3205,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>1615102</v>
+        <v>1320699</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2490743</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1861933</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>2024/25</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>4234674</v>
-      </c>
-      <c r="H20" t="n">
-        <v>6092784</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>38561</v>
+        <v>6474</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>858178</v>
+        <v>1177681</v>
       </c>
       <c r="H21" t="n">
-        <v>726260</v>
+        <v>6474</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>81907</v>
+        <v>60517</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3252487</v>
+        <v>1414622</v>
       </c>
       <c r="H23" t="n">
-        <v>11118394</v>
+        <v>339763</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>60517</v>
+        <v>117338</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1414622</v>
+        <v>4684930</v>
       </c>
       <c r="H24" t="n">
-        <v>339763</v>
+        <v>117338</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>1128645</v>
+        <v>8917</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3434302</v>
+        <v>2118382</v>
       </c>
       <c r="H25" t="n">
-        <v>1128645</v>
+        <v>9146930</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>8917</v>
+        <v>281617</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2118382</v>
+        <v>1051323</v>
       </c>
       <c r="H27" t="n">
-        <v>9146930</v>
+        <v>1076546</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>117338</v>
+        <v>81907</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4684930</v>
+        <v>3252487</v>
       </c>
       <c r="H28" t="n">
-        <v>117338</v>
+        <v>11118394</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>334016</v>
+        <v>1128645</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2156629</v>
+        <v>3434302</v>
       </c>
       <c r="H29" t="n">
-        <v>2691725</v>
+        <v>1128645</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>281617</v>
+        <v>334016</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1051323</v>
+        <v>2156629</v>
       </c>
       <c r="H30" t="n">
-        <v>1076546</v>
+        <v>2691725</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3831,12 +3831,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3881,12 +3881,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3977,12 +3977,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4023,12 +4023,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4064,21 +4064,17 @@
       <c r="R7" t="n">
         <v>885437</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4114,7 +4110,11 @@
       <c r="R8" t="n">
         <v>885437</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4261,12 +4261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4307,12 +4307,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4348,21 +4348,17 @@
       <c r="R13" t="n">
         <v>2683415</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4384,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4403,12 +4399,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4430,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4449,12 +4445,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4490,17 +4486,21 @@
       <c r="R16" t="n">
         <v>2683415</v>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4541,12 +4541,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4582,17 +4582,21 @@
       <c r="R18" t="n">
         <v>2683415</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4614,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4628,21 +4632,17 @@
       <c r="R19" t="n">
         <v>2683415</v>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4678,21 +4678,17 @@
       <c r="R20" t="n">
         <v>2683415</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4714,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4728,7 +4724,11 @@
       <c r="R21" t="n">
         <v>2683415</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4825,12 +4825,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4871,12 +4871,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4912,7 +4912,11 @@
       <c r="R25" t="n">
         <v>5439838</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4963,12 +4967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5013,12 +5017,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5040,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5059,12 +5063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5086,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5095,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>5439838</v>
@@ -5105,12 +5109,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5132,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5141,16 +5145,12 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R30" t="n">
         <v>5439838</v>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
@@ -1367,42 +1367,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
@@ -1430,35 +1430,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1472,14 +1472,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>182900</v>
+        <v>95791</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2098988</v>
+        <v>2404119</v>
       </c>
       <c r="H6" t="n">
-        <v>182900</v>
+        <v>5124417</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>95791</v>
+        <v>182900</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2404119</v>
+        <v>2098988</v>
       </c>
       <c r="H7" t="n">
-        <v>5124417</v>
+        <v>182900</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>189374</v>
+        <v>545267</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1757289</v>
+        <v>604934</v>
       </c>
       <c r="H12" t="n">
-        <v>250879</v>
+        <v>545267</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>453230</v>
+        <v>1615102</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5483351</v>
+        <v>4234674</v>
       </c>
       <c r="H14" t="n">
-        <v>8188106</v>
+        <v>6092784</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>545267</v>
+        <v>27153</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>604934</v>
+        <v>606381</v>
       </c>
       <c r="H15" t="n">
-        <v>545267</v>
+        <v>240451</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>1615102</v>
+        <v>38561</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4234674</v>
+        <v>858178</v>
       </c>
       <c r="H16" t="n">
-        <v>6092784</v>
+        <v>726260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>410102</v>
+        <v>189374</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2088802</v>
+        <v>1757289</v>
       </c>
       <c r="H17" t="n">
-        <v>5360778</v>
+        <v>250879</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>27153</v>
+        <v>6474</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>606381</v>
+        <v>1177681</v>
       </c>
       <c r="H18" t="n">
-        <v>240451</v>
+        <v>6474</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>38561</v>
+        <v>453230</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>858178</v>
+        <v>5483351</v>
       </c>
       <c r="H19" t="n">
-        <v>726260</v>
+        <v>8188106</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>6474</v>
+        <v>410102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1177681</v>
+        <v>2088802</v>
       </c>
       <c r="H21" t="n">
-        <v>6474</v>
+        <v>5360778</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>60517</v>
+        <v>273503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1414622</v>
+        <v>1994005</v>
       </c>
       <c r="H23" t="n">
-        <v>339763</v>
+        <v>1917309</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,19 +3353,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>117338</v>
+        <v>1128645</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4684930</v>
+        <v>3434302</v>
       </c>
       <c r="H24" t="n">
-        <v>117338</v>
+        <v>1128645</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>8917</v>
+        <v>60517</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2118382</v>
+        <v>1414622</v>
       </c>
       <c r="H25" t="n">
-        <v>9146930</v>
+        <v>339763</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>273503</v>
+        <v>117338</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1994005</v>
+        <v>4684930</v>
       </c>
       <c r="H26" t="n">
-        <v>1917309</v>
+        <v>117338</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>281617</v>
+        <v>334016</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1051323</v>
+        <v>2156629</v>
       </c>
       <c r="H27" t="n">
-        <v>1076546</v>
+        <v>2691725</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>1128645</v>
+        <v>281617</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3434302</v>
+        <v>1051323</v>
       </c>
       <c r="H29" t="n">
-        <v>1128645</v>
+        <v>1076546</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>334016</v>
+        <v>8917</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2156629</v>
+        <v>2118382</v>
       </c>
       <c r="H30" t="n">
-        <v>2691725</v>
+        <v>9146930</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3977,12 +3977,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4023,12 +4023,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4261,12 +4261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4353,12 +4353,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4394,17 +4394,21 @@
       <c r="R14" t="n">
         <v>2683415</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4440,17 +4444,21 @@
       <c r="R15" t="n">
         <v>2683415</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4472,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4486,21 +4494,17 @@
       <c r="R16" t="n">
         <v>2683415</v>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4541,12 +4545,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4591,12 +4595,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4618,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4683,12 +4687,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4710,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4724,11 +4728,7 @@
       <c r="R21" t="n">
         <v>2683415</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4825,12 +4825,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4871,12 +4871,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4912,21 +4912,17 @@
       <c r="R25" t="n">
         <v>5439838</v>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4967,12 +4963,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4994,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5003,16 +4999,12 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R27" t="n">
         <v>5439838</v>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5063,12 +5055,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5104,17 +5096,21 @@
       <c r="R29" t="n">
         <v>5439838</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5136,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5145,12 +5141,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>5439838</v>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -619,12 +619,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1311,21 +1311,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
@@ -1353,63 +1353,63 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
@@ -1430,21 +1430,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1458,28 +1458,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>95791</v>
+        <v>182900</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2404119</v>
+        <v>2098988</v>
       </c>
       <c r="H6" t="n">
-        <v>5124417</v>
+        <v>182900</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>182900</v>
+        <v>71857</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2098988</v>
+        <v>1929309</v>
       </c>
       <c r="H7" t="n">
-        <v>182900</v>
+        <v>297407</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2761,30 +2761,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H8" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>545267</v>
+        <v>1615102</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>604934</v>
+        <v>4234674</v>
       </c>
       <c r="H12" t="n">
-        <v>545267</v>
+        <v>6092784</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>15288</v>
+        <v>27153</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>329510</v>
+        <v>606381</v>
       </c>
       <c r="H13" t="n">
-        <v>538046</v>
+        <v>240451</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>1615102</v>
+        <v>15288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4234674</v>
+        <v>329510</v>
       </c>
       <c r="H14" t="n">
-        <v>6092784</v>
+        <v>538046</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>27153</v>
+        <v>38561</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>606381</v>
+        <v>858178</v>
       </c>
       <c r="H15" t="n">
-        <v>240451</v>
+        <v>726260</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,34 +3057,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H16" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>189374</v>
+        <v>6474</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1757289</v>
+        <v>1177681</v>
       </c>
       <c r="H17" t="n">
-        <v>250879</v>
+        <v>6474</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6474</v>
+        <v>453230</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1177681</v>
+        <v>5483351</v>
       </c>
       <c r="H18" t="n">
-        <v>6474</v>
+        <v>8188106</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>453230</v>
+        <v>545267</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5483351</v>
+        <v>604934</v>
       </c>
       <c r="H19" t="n">
-        <v>8188106</v>
+        <v>545267</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,34 +3205,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>1320699</v>
+        <v>189374</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2490743</v>
+        <v>1757289</v>
       </c>
       <c r="H20" t="n">
-        <v>1861933</v>
+        <v>250879</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>273503</v>
+        <v>81907</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1994005</v>
+        <v>3252487</v>
       </c>
       <c r="H23" t="n">
-        <v>1917309</v>
+        <v>11118394</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>1128645</v>
+        <v>60517</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3434302</v>
+        <v>1414622</v>
       </c>
       <c r="H24" t="n">
-        <v>1128645</v>
+        <v>339763</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>60517</v>
+        <v>1128645</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1414622</v>
+        <v>3434302</v>
       </c>
       <c r="H25" t="n">
-        <v>339763</v>
+        <v>1128645</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>334016</v>
+        <v>8917</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2156629</v>
+        <v>2118382</v>
       </c>
       <c r="H27" t="n">
-        <v>2691725</v>
+        <v>9146930</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>81907</v>
+        <v>273503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3252487</v>
+        <v>1994005</v>
       </c>
       <c r="H28" t="n">
-        <v>11118394</v>
+        <v>1917309</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>281617</v>
+        <v>334016</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1051323</v>
+        <v>2156629</v>
       </c>
       <c r="H29" t="n">
-        <v>1076546</v>
+        <v>2691725</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>8917</v>
+        <v>281617</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2118382</v>
+        <v>1051323</v>
       </c>
       <c r="H30" t="n">
-        <v>9146930</v>
+        <v>1076546</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3977,12 +3977,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4023,12 +4023,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4064,17 +4064,21 @@
       <c r="R7" t="n">
         <v>885437</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4110,11 +4114,7 @@
       <c r="R8" t="n">
         <v>885437</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4261,12 +4261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4302,17 +4302,21 @@
       <c r="R12" t="n">
         <v>2683415</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4334,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4348,17 +4352,21 @@
       <c r="R13" t="n">
         <v>2683415</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4380,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4394,21 +4402,17 @@
       <c r="R14" t="n">
         <v>2683415</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4430,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4444,21 +4448,17 @@
       <c r="R15" t="n">
         <v>2683415</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4499,12 +4499,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4526,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4540,17 +4540,21 @@
       <c r="R17" t="n">
         <v>2683415</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4586,21 +4590,17 @@
       <c r="R18" t="n">
         <v>2683415</v>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4641,12 +4641,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4779,12 +4779,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4825,12 +4825,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4871,12 +4871,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4963,12 +4963,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -4999,22 +4999,26 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>5439838</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5036,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5055,12 +5059,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5082,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5091,26 +5095,22 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R29" t="n">
         <v>5439838</v>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C30" t="n">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -619,12 +619,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1311,21 +1311,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
@@ -1353,14 +1353,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
@@ -1388,35 +1388,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
@@ -1430,56 +1430,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>182900</v>
+        <v>71857</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2098988</v>
+        <v>1929309</v>
       </c>
       <c r="H6" t="n">
-        <v>182900</v>
+        <v>297407</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H7" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2761,30 +2761,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>95791</v>
+        <v>182900</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2404119</v>
+        <v>2098988</v>
       </c>
       <c r="H8" t="n">
-        <v>5124417</v>
+        <v>182900</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>1615102</v>
+        <v>38561</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4234674</v>
+        <v>858178</v>
       </c>
       <c r="H12" t="n">
-        <v>6092784</v>
+        <v>726260</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>27153</v>
+        <v>545267</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>606381</v>
+        <v>604934</v>
       </c>
       <c r="H13" t="n">
-        <v>240451</v>
+        <v>545267</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>38561</v>
+        <v>27153</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>858178</v>
+        <v>606381</v>
       </c>
       <c r="H15" t="n">
-        <v>726260</v>
+        <v>240451</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>6474</v>
+        <v>189374</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1177681</v>
+        <v>1757289</v>
       </c>
       <c r="H17" t="n">
-        <v>6474</v>
+        <v>250879</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>453230</v>
+        <v>410102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5483351</v>
+        <v>2088802</v>
       </c>
       <c r="H18" t="n">
-        <v>8188106</v>
+        <v>5360778</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,19 +3168,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>545267</v>
+        <v>6474</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>604934</v>
+        <v>1177681</v>
       </c>
       <c r="H19" t="n">
-        <v>545267</v>
+        <v>6474</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,19 +3205,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>189374</v>
+        <v>1615102</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1757289</v>
+        <v>4234674</v>
       </c>
       <c r="H20" t="n">
-        <v>250879</v>
+        <v>6092784</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>410102</v>
+        <v>453230</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2088802</v>
+        <v>5483351</v>
       </c>
       <c r="H21" t="n">
-        <v>5360778</v>
+        <v>8188106</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3316,19 +3316,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H23" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>60517</v>
+        <v>281617</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1414622</v>
+        <v>1051323</v>
       </c>
       <c r="H24" t="n">
-        <v>339763</v>
+        <v>1076546</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,19 +3390,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>1128645</v>
+        <v>117338</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3434302</v>
+        <v>4684930</v>
       </c>
       <c r="H25" t="n">
-        <v>1128645</v>
+        <v>117338</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>117338</v>
+        <v>273503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4684930</v>
+        <v>1994005</v>
       </c>
       <c r="H26" t="n">
-        <v>117338</v>
+        <v>1917309</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>8917</v>
+        <v>60517</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2118382</v>
+        <v>1414622</v>
       </c>
       <c r="H27" t="n">
-        <v>9146930</v>
+        <v>339763</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>273503</v>
+        <v>8917</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1994005</v>
+        <v>2118382</v>
       </c>
       <c r="H28" t="n">
-        <v>1917309</v>
+        <v>9146930</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,19 +3538,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H29" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>281617</v>
+        <v>1128645</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1051323</v>
+        <v>3434302</v>
       </c>
       <c r="H30" t="n">
-        <v>1076546</v>
+        <v>1128645</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3977,12 +3977,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4018,17 +4018,21 @@
       <c r="R6" t="n">
         <v>885437</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4064,21 +4068,17 @@
       <c r="R7" t="n">
         <v>885437</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4261,12 +4261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4302,21 +4302,17 @@
       <c r="R12" t="n">
         <v>2683415</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4352,11 +4348,7 @@
       <c r="R13" t="n">
         <v>2683415</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4407,12 +4399,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4434,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4448,7 +4440,11 @@
       <c r="R15" t="n">
         <v>2683415</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4499,12 +4495,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4526,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4540,21 +4536,17 @@
       <c r="R17" t="n">
         <v>2683415</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4576,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4595,12 +4587,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4636,17 +4628,21 @@
       <c r="R19" t="n">
         <v>2683415</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4668,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4682,17 +4678,21 @@
       <c r="R20" t="n">
         <v>2683415</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4714,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4779,12 +4779,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R23" t="n">
         <v>5439838</v>
@@ -4825,12 +4825,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4866,17 +4866,21 @@
       <c r="R24" t="n">
         <v>5439838</v>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4898,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4917,12 +4921,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4963,12 +4967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5004,21 +5008,17 @@
       <c r="R27" t="n">
         <v>5439838</v>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5054,17 +5054,21 @@
       <c r="R28" t="n">
         <v>5439838</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5086,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5095,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>5439838</v>
@@ -5105,12 +5109,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5146,11 +5150,7 @@
       <c r="R30" t="n">
         <v>5439838</v>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -556,13 +556,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -580,85 +580,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -691,22 +691,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -715,22 +715,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -739,22 +739,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -763,190 +763,190 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -979,22 +979,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1051,75 +1051,75 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1132,61 +1132,61 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -1318,105 +1318,105 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
@@ -1430,42 +1430,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1479,14 +1479,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1994,7 +1994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2386,7 +2386,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2720,34 +2720,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>95791</v>
+        <v>182900</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2404119</v>
+        <v>2098988</v>
       </c>
       <c r="H7" t="n">
-        <v>5124417</v>
+        <v>182900</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2757,34 +2757,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>182900</v>
+        <v>31543</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2098988</v>
+        <v>820692</v>
       </c>
       <c r="H8" t="n">
-        <v>182900</v>
+        <v>1637750</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2794,34 +2794,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>31543</v>
+        <v>95791</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>820692</v>
+        <v>2404119</v>
       </c>
       <c r="H9" t="n">
-        <v>1637750</v>
+        <v>5124417</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>486041</v>
+        <v>30971</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2415786</v>
+        <v>820221</v>
       </c>
       <c r="H10" t="n">
-        <v>1206623</v>
+        <v>58227</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>30971</v>
+        <v>486041</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820221</v>
+        <v>2415786</v>
       </c>
       <c r="H11" t="n">
-        <v>58227</v>
+        <v>1206623</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>38561</v>
+        <v>453230</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>858178</v>
+        <v>5483351</v>
       </c>
       <c r="H12" t="n">
-        <v>726260</v>
+        <v>8188106</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>545267</v>
+        <v>410102</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>604934</v>
+        <v>2088802</v>
       </c>
       <c r="H13" t="n">
-        <v>545267</v>
+        <v>5360778</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,19 +2983,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>15288</v>
+        <v>1320699</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3003,47 +3003,47 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>329510</v>
+        <v>2490743</v>
       </c>
       <c r="H14" t="n">
-        <v>538046</v>
+        <v>1861933</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>27153</v>
+        <v>6474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>606381</v>
+        <v>1177681</v>
       </c>
       <c r="H15" t="n">
-        <v>240451</v>
+        <v>6474</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3053,71 +3053,71 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>1320699</v>
+        <v>189374</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2490743</v>
+        <v>1757289</v>
       </c>
       <c r="H16" t="n">
-        <v>1861933</v>
+        <v>250879</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>189374</v>
+        <v>27153</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1757289</v>
+        <v>606381</v>
       </c>
       <c r="H17" t="n">
-        <v>250879</v>
+        <v>240451</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3127,34 +3127,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Abhay Rawat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>115 FC</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>11</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Varun Khurana</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Goal Diggers FC</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>15</v>
-      </c>
       <c r="E18" t="n">
-        <v>410102</v>
+        <v>38561</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2088802</v>
+        <v>858178</v>
       </c>
       <c r="H18" t="n">
-        <v>5360778</v>
+        <v>726260</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3164,34 +3164,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>6474</v>
+        <v>1615102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1177681</v>
+        <v>4234674</v>
       </c>
       <c r="H19" t="n">
-        <v>6474</v>
+        <v>6092784</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3201,34 +3201,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>1615102</v>
+        <v>545267</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4234674</v>
+        <v>604934</v>
       </c>
       <c r="H20" t="n">
-        <v>6092784</v>
+        <v>545267</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3238,34 +3238,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>453230</v>
+        <v>15288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5483351</v>
+        <v>329510</v>
       </c>
       <c r="H21" t="n">
-        <v>8188106</v>
+        <v>538046</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>334016</v>
+        <v>8917</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2156629</v>
+        <v>2118382</v>
       </c>
       <c r="H23" t="n">
-        <v>2691725</v>
+        <v>9146930</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>281617</v>
+        <v>273503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1051323</v>
+        <v>1994005</v>
       </c>
       <c r="H24" t="n">
-        <v>1076546</v>
+        <v>1917309</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,19 +3390,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>117338</v>
+        <v>1128645</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4684930</v>
+        <v>3434302</v>
       </c>
       <c r="H25" t="n">
-        <v>117338</v>
+        <v>1128645</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>273503</v>
+        <v>60517</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1994005</v>
+        <v>1414622</v>
       </c>
       <c r="H26" t="n">
-        <v>1917309</v>
+        <v>339763</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>60517</v>
+        <v>117338</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1414622</v>
+        <v>4684930</v>
       </c>
       <c r="H27" t="n">
-        <v>339763</v>
+        <v>117338</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,34 +3497,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>8917</v>
+        <v>281617</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2118382</v>
+        <v>1051323</v>
       </c>
       <c r="H28" t="n">
-        <v>9146930</v>
+        <v>1076546</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3571,34 +3571,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
-        <v>1128645</v>
+        <v>14603</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3434302</v>
+        <v>949628</v>
       </c>
       <c r="H30" t="n">
-        <v>1128645</v>
+        <v>515830</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3608,34 +3608,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>14603</v>
+        <v>334016</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>949628</v>
+        <v>2156629</v>
       </c>
       <c r="H31" t="n">
-        <v>515830</v>
+        <v>2691725</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4027,16 +4027,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4073,16 +4073,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>100</v>
@@ -4109,26 +4109,26 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R8" t="n">
-        <v>885437</v>
+        <v>1381598</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>100</v>
@@ -4155,26 +4155,26 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1381598</v>
+        <v>885437</v>
       </c>
       <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4201,26 +4201,30 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1886838</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>2147456</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4238,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4247,30 +4251,26 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2147456</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1886838</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4307,16 +4307,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4353,16 +4353,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4495,16 +4495,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4536,21 +4536,25 @@
       <c r="R17" t="n">
         <v>2683415</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4568,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4587,16 +4591,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4637,16 +4641,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4678,25 +4682,21 @@
       <c r="R20" t="n">
         <v>2683415</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4779,16 +4779,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4815,26 +4815,30 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>5439838</v>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4852,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4866,25 +4870,21 @@
       <c r="R24" t="n">
         <v>5439838</v>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4921,16 +4921,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4967,16 +4967,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5013,16 +5013,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5109,16 +5109,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5148,23 +5148,23 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5439838</v>
+        <v>6699465</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5191,10 +5191,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>6699465</v>
+        <v>5439838</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -508,18 +508,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -604,61 +604,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -691,190 +691,190 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -883,70 +883,70 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ajith Thomas Kuthukatt George</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Onside Offside</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Aditya Vaidya</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>His Name is Diogo</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>18</v>
-      </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -955,75 +955,75 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1036,85 +1036,85 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -1132,51 +1132,51 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1304,14 +1304,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1325,119 +1325,119 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
@@ -1451,21 +1451,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
@@ -1479,14 +1479,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1994,7 +1994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2386,7 +2386,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2609,7 +2609,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2650,30 +2650,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>37120</v>
+        <v>71857</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1571193</v>
+        <v>1929309</v>
       </c>
       <c r="H5" t="n">
-        <v>3349378</v>
+        <v>297407</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>71857</v>
+        <v>37120</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1929309</v>
+        <v>1571193</v>
       </c>
       <c r="H6" t="n">
-        <v>297407</v>
+        <v>3349378</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2757,34 +2757,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>31543</v>
+        <v>30971</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>820692</v>
+        <v>820221</v>
       </c>
       <c r="H8" t="n">
-        <v>1637750</v>
+        <v>58227</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2794,34 +2794,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Shivanshu Madan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cold Palmer</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ashwin Jose</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pole Calmer �</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11</v>
-      </c>
       <c r="E9" t="n">
-        <v>95791</v>
+        <v>31543</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2404119</v>
+        <v>820692</v>
       </c>
       <c r="H9" t="n">
-        <v>5124417</v>
+        <v>1637750</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>30971</v>
+        <v>95791</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820221</v>
+        <v>2404119</v>
       </c>
       <c r="H10" t="n">
-        <v>58227</v>
+        <v>5124417</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>486041</v>
+        <v>27153</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2415786</v>
+        <v>606381</v>
       </c>
       <c r="H11" t="n">
-        <v>1206623</v>
+        <v>240451</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2905,34 +2905,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>453230</v>
+        <v>486041</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5483351</v>
+        <v>2415786</v>
       </c>
       <c r="H12" t="n">
-        <v>8188106</v>
+        <v>1206623</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2942,34 +2942,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>410102</v>
+        <v>1615102</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2088802</v>
+        <v>4234674</v>
       </c>
       <c r="H13" t="n">
-        <v>5360778</v>
+        <v>6092784</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2979,71 +2979,71 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>1320699</v>
+        <v>6474</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2490743</v>
+        <v>1177681</v>
       </c>
       <c r="H14" t="n">
-        <v>1861933</v>
+        <v>6474</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>6474</v>
+        <v>410102</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1177681</v>
+        <v>2088802</v>
       </c>
       <c r="H15" t="n">
-        <v>6474</v>
+        <v>5360778</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3053,34 +3053,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>189374</v>
+        <v>453230</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1757289</v>
+        <v>5483351</v>
       </c>
       <c r="H16" t="n">
-        <v>250879</v>
+        <v>8188106</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3090,71 +3090,71 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>27153</v>
+        <v>1320699</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>606381</v>
+        <v>2490743</v>
       </c>
       <c r="H17" t="n">
-        <v>240451</v>
+        <v>1861933</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>38561</v>
+        <v>189374</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>858178</v>
+        <v>1757289</v>
       </c>
       <c r="H18" t="n">
-        <v>726260</v>
+        <v>250879</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>1615102</v>
+        <v>38561</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4234674</v>
+        <v>858178</v>
       </c>
       <c r="H19" t="n">
-        <v>6092784</v>
+        <v>726260</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3201,23 +3201,23 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>545267</v>
+        <v>4884220</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>604934</v>
+        <v>4884220</v>
       </c>
       <c r="H20" t="n">
-        <v>545267</v>
+        <v>4884220</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3238,34 +3238,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>15288</v>
+        <v>545267</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>329510</v>
+        <v>604934</v>
       </c>
       <c r="H21" t="n">
-        <v>538046</v>
+        <v>545267</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3279,30 +3279,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>4884220</v>
+        <v>8917</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4884220</v>
+        <v>2118382</v>
       </c>
       <c r="H22" t="n">
-        <v>4884220</v>
+        <v>9146930</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3312,34 +3312,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>8917</v>
+        <v>15288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2118382</v>
+        <v>329510</v>
       </c>
       <c r="H23" t="n">
-        <v>9146930</v>
+        <v>538046</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>273503</v>
+        <v>60517</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1994005</v>
+        <v>1414622</v>
       </c>
       <c r="H24" t="n">
-        <v>1917309</v>
+        <v>339763</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3423,34 +3423,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>60517</v>
+        <v>281617</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1414622</v>
+        <v>1051323</v>
       </c>
       <c r="H26" t="n">
-        <v>339763</v>
+        <v>1076546</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>117338</v>
+        <v>273503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4684930</v>
+        <v>1994005</v>
       </c>
       <c r="H27" t="n">
-        <v>117338</v>
+        <v>1917309</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,34 +3497,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>281617</v>
+        <v>117338</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1051323</v>
+        <v>4684930</v>
       </c>
       <c r="H28" t="n">
-        <v>1076546</v>
+        <v>117338</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3571,34 +3571,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>14603</v>
+        <v>334016</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>949628</v>
+        <v>2156629</v>
       </c>
       <c r="H30" t="n">
-        <v>515830</v>
+        <v>2691725</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3608,34 +3608,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>334016</v>
+        <v>14603</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2156629</v>
+        <v>949628</v>
       </c>
       <c r="H31" t="n">
-        <v>2691725</v>
+        <v>515830</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3931,16 +3931,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>100</v>
@@ -3967,26 +3967,30 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>510626</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>885437</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4004,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4013,16 +4017,12 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>885437</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>510626</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4073,16 +4073,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>100</v>
@@ -4109,26 +4109,30 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1381598</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+        <v>2147456</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4146,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>100</v>
@@ -4155,26 +4159,26 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>885437</v>
+        <v>1381598</v>
       </c>
       <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4204,27 +4208,23 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2147456</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>885437</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4251,26 +4251,30 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1886838</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+        <v>2683415</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4288,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4297,26 +4301,26 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2683415</v>
+        <v>1886838</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4334,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4348,21 +4352,25 @@
       <c r="R13" t="n">
         <v>2683415</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4380,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4394,21 +4402,25 @@
       <c r="R14" t="n">
         <v>2683415</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4426,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4440,25 +4452,21 @@
       <c r="R15" t="n">
         <v>2683415</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4476,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4495,16 +4503,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4522,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4536,25 +4544,21 @@
       <c r="R17" t="n">
         <v>2683415</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4572,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4591,16 +4595,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4618,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4632,25 +4636,21 @@
       <c r="R19" t="n">
         <v>2683415</v>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4680,23 +4680,23 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2683415</v>
+        <v>4711763</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4733,16 +4733,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4772,23 +4772,27 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4711763</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+        <v>5439838</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4806,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4818,27 +4822,23 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5439838</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>2683415</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4921,16 +4921,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4962,21 +4962,25 @@
       <c r="R26" t="n">
         <v>5439838</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5013,16 +5017,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5040,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5054,11 +5058,7 @@
       <c r="R28" t="n">
         <v>5439838</v>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5109,16 +5109,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>6699465</v>
+        <v>5439838</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5191,10 +5191,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>5439838</v>
+        <v>6699465</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,22 +475,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -499,22 +499,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -532,37 +532,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -595,46 +595,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -643,22 +643,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -667,70 +667,70 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -748,66 +748,66 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -820,61 +820,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -883,22 +883,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -916,234 +916,234 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1283,14 +1283,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
@@ -1304,56 +1304,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
@@ -1367,14 +1367,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
@@ -1388,21 +1388,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1416,63 +1416,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2047,7 +2047,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2539,30 +2539,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>676529</v>
+        <v>30971</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>998938</v>
+        <v>820221</v>
       </c>
       <c r="H2" t="n">
-        <v>676529</v>
+        <v>58227</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>15136</v>
+        <v>71857</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>983840</v>
+        <v>1929309</v>
       </c>
       <c r="H3" t="n">
-        <v>45077</v>
+        <v>297407</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2646,34 +2646,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>71857</v>
+        <v>27153</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1929309</v>
+        <v>606381</v>
       </c>
       <c r="H5" t="n">
-        <v>297407</v>
+        <v>240451</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>37120</v>
+        <v>676529</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1571193</v>
+        <v>998938</v>
       </c>
       <c r="H6" t="n">
-        <v>3349378</v>
+        <v>676529</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>182900</v>
+        <v>6474</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2098988</v>
+        <v>1177681</v>
       </c>
       <c r="H7" t="n">
-        <v>182900</v>
+        <v>6474</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2757,34 +2757,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>30971</v>
+        <v>182900</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>820221</v>
+        <v>2098988</v>
       </c>
       <c r="H8" t="n">
-        <v>58227</v>
+        <v>182900</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2798,30 +2798,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>31543</v>
+        <v>15136</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>820692</v>
+        <v>983840</v>
       </c>
       <c r="H9" t="n">
-        <v>1637750</v>
+        <v>45077</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>95791</v>
+        <v>281617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2404119</v>
+        <v>1051323</v>
       </c>
       <c r="H10" t="n">
-        <v>5124417</v>
+        <v>1076546</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2868,34 +2868,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>27153</v>
+        <v>37120</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>606381</v>
+        <v>1571193</v>
       </c>
       <c r="H11" t="n">
-        <v>240451</v>
+        <v>3349378</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2905,34 +2905,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>486041</v>
+        <v>31543</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2415786</v>
+        <v>820692</v>
       </c>
       <c r="H12" t="n">
-        <v>1206623</v>
+        <v>1637750</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2979,34 +2979,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>6474</v>
+        <v>8917</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1177681</v>
+        <v>2118382</v>
       </c>
       <c r="H14" t="n">
-        <v>6474</v>
+        <v>9146930</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3016,34 +3016,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>410102</v>
+        <v>95791</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2088802</v>
+        <v>2404119</v>
       </c>
       <c r="H15" t="n">
-        <v>5360778</v>
+        <v>5124417</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3090,60 +3090,60 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>1320699</v>
+        <v>410102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2490743</v>
+        <v>2088802</v>
       </c>
       <c r="H17" t="n">
-        <v>1861933</v>
+        <v>5360778</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>189374</v>
+        <v>486041</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1757289</v>
+        <v>2415786</v>
       </c>
       <c r="H18" t="n">
-        <v>250879</v>
+        <v>1206623</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,34 +3168,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H19" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3238,23 +3238,23 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>604934</v>
+        <v>3434302</v>
       </c>
       <c r="H21" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3275,34 +3275,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>8917</v>
+        <v>189374</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2118382</v>
+        <v>1757289</v>
       </c>
       <c r="H22" t="n">
-        <v>9146930</v>
+        <v>250879</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3312,34 +3312,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>15288</v>
+        <v>38561</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>329510</v>
+        <v>858178</v>
       </c>
       <c r="H23" t="n">
-        <v>538046</v>
+        <v>726260</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>60517</v>
+        <v>81907</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1414622</v>
+        <v>3252487</v>
       </c>
       <c r="H24" t="n">
-        <v>339763</v>
+        <v>11118394</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3386,23 +3386,23 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1128645</v>
+        <v>545267</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3434302</v>
+        <v>604934</v>
       </c>
       <c r="H25" t="n">
-        <v>1128645</v>
+        <v>545267</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3423,34 +3423,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>281617</v>
+        <v>117338</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1051323</v>
+        <v>4684930</v>
       </c>
       <c r="H26" t="n">
-        <v>1076546</v>
+        <v>117338</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>273503</v>
+        <v>15288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1994005</v>
+        <v>329510</v>
       </c>
       <c r="H27" t="n">
-        <v>1917309</v>
+        <v>538046</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,34 +3497,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>117338</v>
+        <v>273503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4684930</v>
+        <v>1994005</v>
       </c>
       <c r="H28" t="n">
-        <v>117338</v>
+        <v>1917309</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3534,34 +3534,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>81907</v>
+        <v>60517</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3252487</v>
+        <v>1414622</v>
       </c>
       <c r="H29" t="n">
-        <v>11118394</v>
+        <v>339763</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>100</v>
@@ -3824,23 +3824,27 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>63521</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>2147456</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3870,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>239174</v>
+        <v>885437</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3890,7 +3894,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3931,16 +3935,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3970,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>885437</v>
+        <v>2683415</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3981,16 +3985,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4008,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4017,26 +4021,26 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>510626</v>
+        <v>63521</v>
       </c>
       <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4066,23 +4070,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>885437</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>2683415</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4112,27 +4120,23 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2147456</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>885437</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4150,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>100</v>
@@ -4159,26 +4163,30 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1381598</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>239174</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4208,23 +4216,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>885437</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>5439838</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4242,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4251,30 +4263,26 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2683415</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>510626</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4304,7 +4312,7 @@
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1886838</v>
+        <v>1381598</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
@@ -4320,7 +4328,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4361,16 +4369,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4400,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2683415</v>
+        <v>5439838</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -4411,16 +4419,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4438,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4450,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2683415</v>
+        <v>885437</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
@@ -4466,7 +4474,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4503,16 +4511,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4549,16 +4557,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4585,26 +4593,26 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2683415</v>
+        <v>1886838</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4622,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4650,7 +4658,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4687,16 +4695,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4726,23 +4734,23 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2683415</v>
+        <v>5439838</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4760,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4772,27 +4780,23 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5439838</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>2683415</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4810,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4829,16 +4833,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4875,16 +4879,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4914,23 +4918,23 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5439838</v>
+        <v>2683415</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4948,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4962,25 +4966,21 @@
       <c r="R26" t="n">
         <v>5439838</v>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5010,23 +5010,23 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5439838</v>
+        <v>2683415</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5063,16 +5063,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -499,22 +499,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -523,46 +523,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -604,13 +604,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -691,22 +691,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -748,61 +748,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -811,22 +811,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -835,27 +835,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -879,40 +879,40 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -927,16 +927,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -951,16 +951,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -975,40 +975,40 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1047,79 +1047,79 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1143,26 +1143,26 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -1290,21 +1290,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1367,28 +1367,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
@@ -1402,70 +1402,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>71857</v>
+        <v>27153</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1929309</v>
+        <v>606381</v>
       </c>
       <c r="H3" t="n">
-        <v>297407</v>
+        <v>240451</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2613,30 +2613,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>28582</v>
+        <v>71857</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>881388</v>
+        <v>1929309</v>
       </c>
       <c r="H4" t="n">
-        <v>239490</v>
+        <v>297407</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2646,34 +2646,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>27153</v>
+        <v>28582</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>606381</v>
+        <v>881388</v>
       </c>
       <c r="H5" t="n">
-        <v>240451</v>
+        <v>239490</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>37120</v>
+        <v>334016</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1571193</v>
+        <v>2156629</v>
       </c>
       <c r="H11" t="n">
-        <v>3349378</v>
+        <v>2691725</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2979,34 +2979,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>8917</v>
+        <v>37120</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2118382</v>
+        <v>1571193</v>
       </c>
       <c r="H14" t="n">
-        <v>9146930</v>
+        <v>3349378</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3016,34 +3016,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>95791</v>
+        <v>8917</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2404119</v>
+        <v>2118382</v>
       </c>
       <c r="H15" t="n">
-        <v>5124417</v>
+        <v>9146930</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>453230</v>
+        <v>95791</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5483351</v>
+        <v>2404119</v>
       </c>
       <c r="H16" t="n">
-        <v>8188106</v>
+        <v>5124417</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>410102</v>
+        <v>453230</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2088802</v>
+        <v>5483351</v>
       </c>
       <c r="H17" t="n">
-        <v>5360778</v>
+        <v>8188106</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3164,60 +3164,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>1320699</v>
+        <v>410102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2490743</v>
+        <v>2088802</v>
       </c>
       <c r="H19" t="n">
-        <v>1861933</v>
+        <v>5360778</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>4884220</v>
+        <v>1128645</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4884220</v>
+        <v>3434302</v>
       </c>
       <c r="H20" t="n">
-        <v>4884220</v>
+        <v>1128645</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3238,34 +3238,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>1128645</v>
+        <v>189374</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3434302</v>
+        <v>1757289</v>
       </c>
       <c r="H21" t="n">
-        <v>1128645</v>
+        <v>250879</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3275,34 +3275,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>189374</v>
+        <v>38561</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1757289</v>
+        <v>858178</v>
       </c>
       <c r="H22" t="n">
-        <v>250879</v>
+        <v>726260</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3312,71 +3312,71 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H23" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>81907</v>
+        <v>4884220</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3252487</v>
+        <v>4884220</v>
       </c>
       <c r="H24" t="n">
-        <v>11118394</v>
+        <v>4884220</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>545267</v>
+        <v>81907</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>604934</v>
+        <v>3252487</v>
       </c>
       <c r="H25" t="n">
-        <v>545267</v>
+        <v>11118394</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3423,23 +3423,23 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4684930</v>
+        <v>604934</v>
       </c>
       <c r="H26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>15288</v>
+        <v>117338</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>329510</v>
+        <v>4684930</v>
       </c>
       <c r="H27" t="n">
-        <v>538046</v>
+        <v>117338</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,34 +3497,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>273503</v>
+        <v>15288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1994005</v>
+        <v>329510</v>
       </c>
       <c r="H28" t="n">
-        <v>1917309</v>
+        <v>538046</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3571,34 +3571,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>334016</v>
+        <v>273503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2156629</v>
+        <v>1994005</v>
       </c>
       <c r="H30" t="n">
-        <v>2691725</v>
+        <v>1917309</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3835,16 +3835,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>885437</v>
+        <v>2683415</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>239174</v>
+        <v>885437</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3935,16 +3935,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2683415</v>
+        <v>239174</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4227,16 +4227,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4266,7 +4266,7 @@
         <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>510626</v>
+        <v>5439838</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4369,16 +4369,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,30 +4405,26 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>5439838</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>510626</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4458,23 +4454,27 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>885437</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
+        <v>5439838</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4504,23 +4504,23 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2683415</v>
+        <v>885437</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4603,16 +4603,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4649,12 +4649,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4688,19 +4688,19 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4711763</v>
+        <v>5439838</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4734,19 +4734,19 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5439838</v>
+        <v>2683415</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,16 +4787,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4833,12 +4833,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4872,19 +4872,19 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5439838</v>
+        <v>4711763</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4918,23 +4918,23 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2683415</v>
+        <v>5439838</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4964,23 +4964,23 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5439838</v>
+        <v>2683415</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5010,23 +5010,23 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2683415</v>
+        <v>5439838</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>5439838</v>
+        <v>2683415</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
@@ -5109,16 +5109,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>5439838</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
@@ -1360,14 +1360,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1381,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1444,21 +1444,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>1615102</v>
+        <v>37120</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4234674</v>
+        <v>1571193</v>
       </c>
       <c r="H13" t="n">
-        <v>6092784</v>
+        <v>3349378</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>37120</v>
+        <v>1615102</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1571193</v>
+        <v>4234674</v>
       </c>
       <c r="H14" t="n">
-        <v>3349378</v>
+        <v>6092784</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>95791</v>
+        <v>453230</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2404119</v>
+        <v>5483351</v>
       </c>
       <c r="H16" t="n">
-        <v>5124417</v>
+        <v>8188106</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>453230</v>
+        <v>95791</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5483351</v>
+        <v>2404119</v>
       </c>
       <c r="H17" t="n">
-        <v>8188106</v>
+        <v>5124417</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>486041</v>
+        <v>410102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2415786</v>
+        <v>2088802</v>
       </c>
       <c r="H18" t="n">
-        <v>1206623</v>
+        <v>5360778</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H19" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,34 +3205,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>1128645</v>
+        <v>1320699</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3434302</v>
+        <v>2490743</v>
       </c>
       <c r="H20" t="n">
-        <v>1128645</v>
+        <v>1861933</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3316,34 +3316,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>1320699</v>
+        <v>1128645</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2490743</v>
+        <v>3434302</v>
       </c>
       <c r="H23" t="n">
-        <v>1861933</v>
+        <v>1128645</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>81907</v>
+        <v>117338</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3252487</v>
+        <v>4684930</v>
       </c>
       <c r="H25" t="n">
-        <v>11118394</v>
+        <v>117338</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>545267</v>
+        <v>81907</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>604934</v>
+        <v>3252487</v>
       </c>
       <c r="H26" t="n">
-        <v>545267</v>
+        <v>11118394</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,19 +3464,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4684930</v>
+        <v>604934</v>
       </c>
       <c r="H27" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2147456</v>
+        <v>162561</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2683415</v>
+        <v>194557</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>885437</v>
+        <v>237914</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>239174</v>
+        <v>338135</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4024,19 +4024,23 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>63521</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>478912</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4058,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4070,13 +4074,9 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2683415</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>478912</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
         <v>100</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>885437</v>
+        <v>648855</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>239174</v>
+        <v>757460</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5439838</v>
+        <v>1933301</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4266,7 +4266,7 @@
         <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>5439838</v>
+        <v>1933301</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4312,19 +4312,19 @@
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1381598</v>
+        <v>1933301</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4355,26 +4355,22 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2683415</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>2175624</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,12 +4401,16 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>510626</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
+        <v>2175624</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4454,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5439838</v>
+        <v>2741472</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -4465,12 +4465,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4504,19 +4504,19 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>885437</v>
+        <v>3055805</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4550,19 +4550,19 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2683415</v>
+        <v>3055805</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4593,22 +4593,22 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1886838</v>
+        <v>3383283</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4639,22 +4639,22 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2683415</v>
+        <v>3383283</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5439838</v>
+        <v>4091852</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2683415</v>
+        <v>4091852</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4780,19 +4780,19 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2683415</v>
+        <v>4091852</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2683415</v>
+        <v>4091852</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4872,19 +4872,19 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4711763</v>
+        <v>4468366</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4918,19 +4918,19 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5439838</v>
+        <v>4831287</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4964,19 +4964,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2683415</v>
+        <v>4831287</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5439838</v>
+        <v>4831287</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2683415</v>
+        <v>5203238</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5439838</v>
+        <v>5562182</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5439838</v>
+        <v>5562182</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>100</v>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>6699465</v>
+        <v>7185986</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>100</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7752425</v>
+        <v>8650458</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
@@ -1339,21 +1339,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1444,21 +1444,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H6" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>281617</v>
+        <v>334016</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1051323</v>
+        <v>2156629</v>
       </c>
       <c r="H10" t="n">
-        <v>1076546</v>
+        <v>2691725</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>334016</v>
+        <v>31543</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2156629</v>
+        <v>820692</v>
       </c>
       <c r="H11" t="n">
-        <v>2691725</v>
+        <v>1637750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H12" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3205,34 +3205,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>1320699</v>
+        <v>38561</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2490743</v>
+        <v>858178</v>
       </c>
       <c r="H20" t="n">
-        <v>1861933</v>
+        <v>726260</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3279,34 +3279,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H22" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3390,19 +3390,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4684930</v>
+        <v>604934</v>
       </c>
       <c r="H25" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>81907</v>
+        <v>117338</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3252487</v>
+        <v>4684930</v>
       </c>
       <c r="H26" t="n">
-        <v>11118394</v>
+        <v>117338</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>545267</v>
+        <v>81907</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>604934</v>
+        <v>3252487</v>
       </c>
       <c r="H27" t="n">
-        <v>545267</v>
+        <v>11118394</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4026,21 +4026,17 @@
       <c r="R6" t="n">
         <v>478912</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4062,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4076,7 +4072,11 @@
       <c r="R7" t="n">
         <v>478912</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,26 +4213,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
         <v>1933301</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4254,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4273,12 +4269,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4300,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4309,12 +4305,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>1933301</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4649,12 +4649,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4741,12 +4741,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4879,12 +4879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4925,12 +4925,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4971,12 +4971,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1339,7 +1339,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1353,21 +1353,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1381,56 +1381,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1444,14 +1444,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>334016</v>
+        <v>281617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2156629</v>
+        <v>1051323</v>
       </c>
       <c r="H10" t="n">
-        <v>2691725</v>
+        <v>1076546</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>281617</v>
+        <v>334016</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1051323</v>
+        <v>2156629</v>
       </c>
       <c r="H12" t="n">
-        <v>1076546</v>
+        <v>2691725</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>37120</v>
+        <v>1615102</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1571193</v>
+        <v>4234674</v>
       </c>
       <c r="H13" t="n">
-        <v>3349378</v>
+        <v>6092784</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>1615102</v>
+        <v>37120</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4234674</v>
+        <v>1571193</v>
       </c>
       <c r="H14" t="n">
-        <v>6092784</v>
+        <v>3349378</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>453230</v>
+        <v>95791</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5483351</v>
+        <v>2404119</v>
       </c>
       <c r="H16" t="n">
-        <v>8188106</v>
+        <v>5124417</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>95791</v>
+        <v>453230</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2404119</v>
+        <v>5483351</v>
       </c>
       <c r="H17" t="n">
-        <v>5124417</v>
+        <v>8188106</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H18" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>486041</v>
+        <v>410102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2415786</v>
+        <v>2088802</v>
       </c>
       <c r="H19" t="n">
-        <v>1206623</v>
+        <v>5360778</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>38561</v>
+        <v>189374</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>858178</v>
+        <v>1757289</v>
       </c>
       <c r="H20" t="n">
-        <v>726260</v>
+        <v>250879</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>189374</v>
+        <v>38561</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1757289</v>
+        <v>858178</v>
       </c>
       <c r="H21" t="n">
-        <v>250879</v>
+        <v>726260</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3279,34 +3279,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1320699</v>
+        <v>1128645</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2490743</v>
+        <v>3434302</v>
       </c>
       <c r="H22" t="n">
-        <v>1861933</v>
+        <v>1128645</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3316,34 +3316,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>1128645</v>
+        <v>1320699</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3434302</v>
+        <v>2490743</v>
       </c>
       <c r="H23" t="n">
-        <v>1128645</v>
+        <v>1861933</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3390,19 +3390,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>545267</v>
+        <v>117338</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>604934</v>
+        <v>4684930</v>
       </c>
       <c r="H25" t="n">
-        <v>545267</v>
+        <v>117338</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,19 +3427,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4684930</v>
+        <v>604934</v>
       </c>
       <c r="H26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,12 +4213,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1933301</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4269,12 +4273,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4296,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4305,26 +4309,22 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R12" t="n">
         <v>1933301</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4355,22 +4355,26 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>2175624</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4392,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4401,16 +4405,12 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R14" t="n">
         <v>2175624</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4465,12 +4465,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4511,12 +4511,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4557,12 +4557,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
         <v>3383283</v>
@@ -4603,12 +4603,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>3383283</v>
@@ -4649,12 +4649,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4695,12 +4695,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4741,12 +4741,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,12 +4787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4879,12 +4879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4925,12 +4925,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -711,40 +711,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -759,16 +759,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
@@ -1339,35 +1339,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
@@ -1395,14 +1395,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
@@ -1416,21 +1416,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1444,21 +1444,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
@@ -1472,14 +1472,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H10" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H11" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2905,34 +2905,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>334016</v>
+        <v>37120</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2156629</v>
+        <v>1571193</v>
       </c>
       <c r="H12" t="n">
-        <v>2691725</v>
+        <v>3349378</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2942,34 +2942,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>1615102</v>
+        <v>334016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4234674</v>
+        <v>2156629</v>
       </c>
       <c r="H13" t="n">
-        <v>6092784</v>
+        <v>2691725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2979,34 +2979,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>37120</v>
+        <v>1615102</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1571193</v>
+        <v>4234674</v>
       </c>
       <c r="H14" t="n">
-        <v>3349378</v>
+        <v>6092784</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>486041</v>
+        <v>410102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2415786</v>
+        <v>2088802</v>
       </c>
       <c r="H18" t="n">
-        <v>1206623</v>
+        <v>5360778</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H19" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3242,34 +3242,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H21" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3279,30 +3279,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>1128645</v>
+        <v>38561</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3434302</v>
+        <v>858178</v>
       </c>
       <c r="H22" t="n">
-        <v>1128645</v>
+        <v>726260</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,34 +3316,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>1320699</v>
+        <v>1128645</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2490743</v>
+        <v>3434302</v>
       </c>
       <c r="H23" t="n">
-        <v>1861933</v>
+        <v>1128645</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>117338</v>
+        <v>81907</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4684930</v>
+        <v>3252487</v>
       </c>
       <c r="H25" t="n">
-        <v>117338</v>
+        <v>11118394</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,19 +3427,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>545267</v>
+        <v>117338</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>604934</v>
+        <v>4684930</v>
       </c>
       <c r="H26" t="n">
-        <v>545267</v>
+        <v>117338</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>81907</v>
+        <v>545267</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3252487</v>
+        <v>604934</v>
       </c>
       <c r="H27" t="n">
-        <v>11118394</v>
+        <v>545267</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>60517</v>
+        <v>273503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1414622</v>
+        <v>1994005</v>
       </c>
       <c r="H29" t="n">
-        <v>339763</v>
+        <v>1917309</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>273503</v>
+        <v>60517</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1994005</v>
+        <v>1414622</v>
       </c>
       <c r="H30" t="n">
-        <v>1917309</v>
+        <v>339763</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4026,17 +4026,21 @@
       <c r="R6" t="n">
         <v>478912</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4058,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4072,11 +4076,7 @@
       <c r="R7" t="n">
         <v>478912</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,26 +4213,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
         <v>1933301</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4254,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4263,26 +4259,30 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>1933301</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4312,19 +4312,19 @@
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1933301</v>
+        <v>2175624</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4355,26 +4355,22 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2175624</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1933301</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,12 +4401,16 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>2175624</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4557,12 +4557,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>3383283</v>
@@ -4603,12 +4603,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R19" t="n">
         <v>3383283</v>
@@ -4695,12 +4695,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4741,12 +4741,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,12 +4787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4879,12 +4879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4925,12 +4925,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4971,12 +4971,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5063,12 +5063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5109,12 +5109,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1339,21 +1339,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1381,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
@@ -1423,14 +1423,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
@@ -1444,21 +1444,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H10" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H11" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>37120</v>
+        <v>1615102</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1571193</v>
+        <v>4234674</v>
       </c>
       <c r="H12" t="n">
-        <v>3349378</v>
+        <v>6092784</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>1615102</v>
+        <v>37120</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4234674</v>
+        <v>1571193</v>
       </c>
       <c r="H14" t="n">
-        <v>6092784</v>
+        <v>3349378</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>95791</v>
+        <v>453230</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2404119</v>
+        <v>5483351</v>
       </c>
       <c r="H16" t="n">
-        <v>5124417</v>
+        <v>8188106</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>453230</v>
+        <v>95791</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5483351</v>
+        <v>2404119</v>
       </c>
       <c r="H17" t="n">
-        <v>8188106</v>
+        <v>5124417</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H18" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>486041</v>
+        <v>410102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2415786</v>
+        <v>2088802</v>
       </c>
       <c r="H19" t="n">
-        <v>1206623</v>
+        <v>5360778</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>189374</v>
+        <v>38561</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1757289</v>
+        <v>858178</v>
       </c>
       <c r="H20" t="n">
-        <v>250879</v>
+        <v>726260</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3279,30 +3279,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>38561</v>
+        <v>1128645</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>858178</v>
+        <v>3434302</v>
       </c>
       <c r="H22" t="n">
-        <v>726260</v>
+        <v>1128645</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>1128645</v>
+        <v>189374</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3434302</v>
+        <v>1757289</v>
       </c>
       <c r="H23" t="n">
-        <v>1128645</v>
+        <v>250879</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>81907</v>
+        <v>117338</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3252487</v>
+        <v>4684930</v>
       </c>
       <c r="H25" t="n">
-        <v>11118394</v>
+        <v>117338</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,19 +3427,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4684930</v>
+        <v>604934</v>
       </c>
       <c r="H26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>545267</v>
+        <v>81907</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>604934</v>
+        <v>3252487</v>
       </c>
       <c r="H27" t="n">
-        <v>545267</v>
+        <v>11118394</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,22 +4213,26 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1933301</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4250,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4259,26 +4263,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
         <v>1933301</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4309,12 +4309,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>2175624</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4365,12 +4369,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4392,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4401,16 +4405,12 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R14" t="n">
         <v>2175624</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4465,12 +4465,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4511,12 +4511,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4557,12 +4557,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
         <v>3383283</v>
@@ -4603,12 +4603,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>3383283</v>
@@ -4649,12 +4649,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4741,12 +4741,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,12 +4787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4879,12 +4879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4925,12 +4925,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4971,12 +4971,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
@@ -1353,14 +1353,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
@@ -1381,56 +1381,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H6" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>1615102</v>
+        <v>334016</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4234674</v>
+        <v>2156629</v>
       </c>
       <c r="H12" t="n">
-        <v>6092784</v>
+        <v>2691725</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>334016</v>
+        <v>1615102</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2156629</v>
+        <v>4234674</v>
       </c>
       <c r="H13" t="n">
-        <v>2691725</v>
+        <v>6092784</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>453230</v>
+        <v>95791</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5483351</v>
+        <v>2404119</v>
       </c>
       <c r="H16" t="n">
-        <v>8188106</v>
+        <v>5124417</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>95791</v>
+        <v>453230</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2404119</v>
+        <v>5483351</v>
       </c>
       <c r="H17" t="n">
-        <v>5124417</v>
+        <v>8188106</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>486041</v>
+        <v>410102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2415786</v>
+        <v>2088802</v>
       </c>
       <c r="H18" t="n">
-        <v>1206623</v>
+        <v>5360778</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H19" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>38561</v>
+        <v>189374</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>858178</v>
+        <v>1757289</v>
       </c>
       <c r="H20" t="n">
-        <v>726260</v>
+        <v>250879</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,34 +3242,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>1320699</v>
+        <v>1128645</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2490743</v>
+        <v>3434302</v>
       </c>
       <c r="H21" t="n">
-        <v>1861933</v>
+        <v>1128645</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3279,30 +3279,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>1128645</v>
+        <v>38561</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3434302</v>
+        <v>858178</v>
       </c>
       <c r="H22" t="n">
-        <v>1128645</v>
+        <v>726260</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,34 +3316,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>189374</v>
+        <v>1320699</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2490743</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1861933</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>2024/25</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1757289</v>
-      </c>
-      <c r="H23" t="n">
-        <v>250879</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4026,21 +4026,17 @@
       <c r="R6" t="n">
         <v>478912</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4062,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4076,7 +4072,11 @@
       <c r="R7" t="n">
         <v>478912</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4273,12 +4273,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4309,26 +4309,22 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2175624</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1933301</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4350,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,12 +4355,16 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1933301</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
+        <v>2175624</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4465,12 +4465,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4511,12 +4511,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4557,12 +4557,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>3383283</v>
@@ -4603,12 +4603,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R19" t="n">
         <v>3383283</v>
@@ -4649,12 +4649,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4695,12 +4695,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4741,12 +4741,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,12 +4787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1339,21 +1339,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1381,56 +1381,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
@@ -1444,14 +1444,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
@@ -1472,14 +1472,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H10" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H11" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>334016</v>
+        <v>37120</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2156629</v>
+        <v>1571193</v>
       </c>
       <c r="H12" t="n">
-        <v>2691725</v>
+        <v>3349378</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>37120</v>
+        <v>334016</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1571193</v>
+        <v>2156629</v>
       </c>
       <c r="H14" t="n">
-        <v>3349378</v>
+        <v>2691725</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>95791</v>
+        <v>453230</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2404119</v>
+        <v>5483351</v>
       </c>
       <c r="H16" t="n">
-        <v>5124417</v>
+        <v>8188106</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>453230</v>
+        <v>95791</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5483351</v>
+        <v>2404119</v>
       </c>
       <c r="H17" t="n">
-        <v>8188106</v>
+        <v>5124417</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H18" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>486041</v>
+        <v>410102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2415786</v>
+        <v>2088802</v>
       </c>
       <c r="H19" t="n">
-        <v>1206623</v>
+        <v>5360778</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>189374</v>
+        <v>1128645</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1757289</v>
+        <v>3434302</v>
       </c>
       <c r="H20" t="n">
-        <v>250879</v>
+        <v>1128645</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>1128645</v>
+        <v>38561</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3434302</v>
+        <v>858178</v>
       </c>
       <c r="H21" t="n">
-        <v>1128645</v>
+        <v>726260</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3279,34 +3279,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>38561</v>
+        <v>1320699</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>858178</v>
+        <v>2490743</v>
       </c>
       <c r="H22" t="n">
-        <v>726260</v>
+        <v>1861933</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3316,34 +3316,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>1320699</v>
+        <v>189374</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2490743</v>
+        <v>1757289</v>
       </c>
       <c r="H23" t="n">
-        <v>1861933</v>
+        <v>250879</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3390,19 +3390,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4684930</v>
+        <v>604934</v>
       </c>
       <c r="H25" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,19 +3427,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>545267</v>
+        <v>117338</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>604934</v>
+        <v>4684930</v>
       </c>
       <c r="H26" t="n">
-        <v>545267</v>
+        <v>117338</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>273503</v>
+        <v>60517</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1994005</v>
+        <v>1414622</v>
       </c>
       <c r="H29" t="n">
-        <v>1917309</v>
+        <v>339763</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,30 +3575,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>60517</v>
+        <v>273503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1414622</v>
+        <v>1994005</v>
       </c>
       <c r="H30" t="n">
-        <v>339763</v>
+        <v>1917309</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,26 +4213,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
         <v>1933301</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4254,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4263,22 +4259,26 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>1933301</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4312,7 +4312,7 @@
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1933301</v>
+        <v>2175624</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
@@ -4369,12 +4369,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4408,7 +4408,7 @@
         <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>2175624</v>
+        <v>1933301</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
@@ -4465,12 +4465,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4511,12 +4511,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4557,12 +4557,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
         <v>3383283</v>
@@ -4603,12 +4603,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>3383283</v>
@@ -4649,12 +4649,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4695,12 +4695,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4741,12 +4741,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,12 +4787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4879,12 +4879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4925,12 +4925,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -5063,12 +5063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5109,12 +5109,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,22 +475,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -499,22 +499,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -556,13 +556,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -571,46 +571,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -667,27 +667,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -715,22 +715,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -739,46 +739,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -787,22 +787,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -811,22 +811,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -868,13 +868,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -883,118 +883,118 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1036,18 +1036,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1060,42 +1060,42 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1283,14 +1283,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
@@ -1353,35 +1353,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1402,42 +1402,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2047,7 +2047,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2539,30 +2539,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>30971</v>
+        <v>27153</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>820221</v>
+        <v>606381</v>
       </c>
       <c r="H2" t="n">
-        <v>58227</v>
+        <v>240451</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>27153</v>
+        <v>30971</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>606381</v>
+        <v>820221</v>
       </c>
       <c r="H3" t="n">
-        <v>240451</v>
+        <v>58227</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2720,23 +2720,23 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dean Jenkins</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Slumber FC</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Arshaq Razack</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ShakeNBake</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>16</v>
-      </c>
       <c r="E7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>31543</v>
+        <v>38561</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820692</v>
+        <v>858178</v>
       </c>
       <c r="H10" t="n">
-        <v>1637750</v>
+        <v>726260</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>37120</v>
+        <v>8917</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1571193</v>
+        <v>2118382</v>
       </c>
       <c r="H12" t="n">
-        <v>3349378</v>
+        <v>9146930</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>1615102</v>
+        <v>334016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4234674</v>
+        <v>2156629</v>
       </c>
       <c r="H13" t="n">
-        <v>6092784</v>
+        <v>2691725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2979,34 +2979,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>334016</v>
+        <v>1615102</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2156629</v>
+        <v>4234674</v>
       </c>
       <c r="H14" t="n">
-        <v>2691725</v>
+        <v>6092784</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>8917</v>
+        <v>31543</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2118382</v>
+        <v>820692</v>
       </c>
       <c r="H15" t="n">
-        <v>9146930</v>
+        <v>1637750</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>453230</v>
+        <v>37120</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5483351</v>
+        <v>1571193</v>
       </c>
       <c r="H16" t="n">
-        <v>8188106</v>
+        <v>3349378</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>410102</v>
+        <v>81907</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2088802</v>
+        <v>3252487</v>
       </c>
       <c r="H19" t="n">
-        <v>5360778</v>
+        <v>11118394</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3201,34 +3201,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>1128645</v>
+        <v>453230</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3434302</v>
+        <v>5483351</v>
       </c>
       <c r="H20" t="n">
-        <v>1128645</v>
+        <v>8188106</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3238,34 +3238,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>38561</v>
+        <v>410102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>858178</v>
+        <v>2088802</v>
       </c>
       <c r="H21" t="n">
-        <v>726260</v>
+        <v>5360778</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3275,71 +3275,71 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>1320699</v>
+        <v>189374</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2490743</v>
+        <v>1757289</v>
       </c>
       <c r="H22" t="n">
-        <v>1861933</v>
+        <v>250879</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>189374</v>
+        <v>1128645</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1757289</v>
+        <v>3434302</v>
       </c>
       <c r="H23" t="n">
-        <v>250879</v>
+        <v>1128645</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,40 +3353,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4884220</v>
+        <v>1320699</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4884220</v>
+        <v>2490743</v>
       </c>
       <c r="H24" t="n">
-        <v>4884220</v>
+        <v>1861933</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>81907</v>
+        <v>4884220</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3252487</v>
+        <v>4884220</v>
       </c>
       <c r="H27" t="n">
-        <v>11118394</v>
+        <v>4884220</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>162561</v>
+        <v>194557</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3835,16 +3835,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>194557</v>
+        <v>162561</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3985,16 +3985,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4026,21 +4026,25 @@
       <c r="R6" t="n">
         <v>478912</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4058,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4072,11 +4076,7 @@
       <c r="R7" t="n">
         <v>478912</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4177,16 +4177,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1933301</v>
+        <v>4091852</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4273,16 +4273,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4309,26 +4309,30 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2175624</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
+        <v>2741472</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4346,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4355,30 +4359,26 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2175624</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1933301</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,26 +4405,30 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1933301</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
+        <v>2175624</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4442,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4451,30 +4455,26 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2741472</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1933301</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4501,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R16" t="n">
-        <v>3055805</v>
+        <v>2175624</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4603,16 +4603,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4642,23 +4642,23 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3383283</v>
+        <v>4831287</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4688,23 +4688,23 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4091852</v>
+        <v>3055805</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4734,23 +4734,23 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4091852</v>
+        <v>3383283</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,16 +4787,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4833,16 +4833,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4468366</v>
+        <v>4091852</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4971,16 +4971,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4831287</v>
+        <v>4468366</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -499,70 +499,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -595,22 +595,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -619,46 +619,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -691,22 +691,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -715,22 +715,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -739,22 +739,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -763,22 +763,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -787,22 +787,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -811,22 +811,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
@@ -835,118 +835,118 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -955,51 +955,51 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1012,90 +1012,90 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1123,46 +1123,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1290,147 +1290,147 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1444,21 +1444,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1472,14 +1472,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>30971</v>
+        <v>28582</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>820221</v>
+        <v>881388</v>
       </c>
       <c r="H3" t="n">
-        <v>58227</v>
+        <v>239490</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2609,34 +2609,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>71857</v>
+        <v>6474</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1929309</v>
+        <v>1177681</v>
       </c>
       <c r="H4" t="n">
-        <v>297407</v>
+        <v>6474</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2646,34 +2646,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>28582</v>
+        <v>71857</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>881388</v>
+        <v>1929309</v>
       </c>
       <c r="H5" t="n">
-        <v>239490</v>
+        <v>297407</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2687,30 +2687,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>6474</v>
+        <v>30971</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1177681</v>
+        <v>820221</v>
       </c>
       <c r="H6" t="n">
-        <v>6474</v>
+        <v>58227</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>676529</v>
+        <v>15136</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>998938</v>
+        <v>983840</v>
       </c>
       <c r="H7" t="n">
-        <v>676529</v>
+        <v>45077</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2761,19 +2761,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2098988</v>
+        <v>998938</v>
       </c>
       <c r="H8" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2794,34 +2794,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>15136</v>
+        <v>281617</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>983840</v>
+        <v>1051323</v>
       </c>
       <c r="H9" t="n">
-        <v>45077</v>
+        <v>1076546</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>38561</v>
+        <v>8917</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>858178</v>
+        <v>2118382</v>
       </c>
       <c r="H10" t="n">
-        <v>726260</v>
+        <v>9146930</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>281617</v>
+        <v>182900</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1051323</v>
+        <v>2098988</v>
       </c>
       <c r="H11" t="n">
-        <v>1076546</v>
+        <v>182900</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>8917</v>
+        <v>334016</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2118382</v>
+        <v>2156629</v>
       </c>
       <c r="H12" t="n">
-        <v>9146930</v>
+        <v>2691725</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H13" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>1615102</v>
+        <v>38561</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4234674</v>
+        <v>858178</v>
       </c>
       <c r="H14" t="n">
-        <v>6092784</v>
+        <v>726260</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>31543</v>
+        <v>1615102</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>820692</v>
+        <v>4234674</v>
       </c>
       <c r="H15" t="n">
-        <v>1637750</v>
+        <v>6092784</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>37120</v>
+        <v>410102</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1571193</v>
+        <v>2088802</v>
       </c>
       <c r="H16" t="n">
-        <v>3349378</v>
+        <v>5360778</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>95791</v>
+        <v>189374</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2404119</v>
+        <v>1757289</v>
       </c>
       <c r="H17" t="n">
-        <v>5124417</v>
+        <v>250879</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3127,34 +3127,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>486041</v>
+        <v>1128645</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2415786</v>
+        <v>3434302</v>
       </c>
       <c r="H18" t="n">
-        <v>1206623</v>
+        <v>1128645</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3164,34 +3164,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>81907</v>
+        <v>95791</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3252487</v>
+        <v>2404119</v>
       </c>
       <c r="H19" t="n">
-        <v>11118394</v>
+        <v>5124417</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3201,34 +3201,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>453230</v>
+        <v>31543</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5483351</v>
+        <v>820692</v>
       </c>
       <c r="H20" t="n">
-        <v>8188106</v>
+        <v>1637750</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3238,34 +3238,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H21" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3279,30 +3279,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>189374</v>
+        <v>453230</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1757289</v>
+        <v>5483351</v>
       </c>
       <c r="H22" t="n">
-        <v>250879</v>
+        <v>8188106</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3312,34 +3312,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>1128645</v>
+        <v>37120</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3434302</v>
+        <v>1571193</v>
       </c>
       <c r="H23" t="n">
-        <v>1128645</v>
+        <v>3349378</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3386,34 +3386,34 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>545267</v>
+        <v>60517</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>604934</v>
+        <v>1414622</v>
       </c>
       <c r="H25" t="n">
-        <v>545267</v>
+        <v>339763</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3423,23 +3423,23 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4684930</v>
+        <v>604934</v>
       </c>
       <c r="H26" t="n">
-        <v>117338</v>
+        <v>545267</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>4884220</v>
+        <v>273503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4884220</v>
+        <v>1994005</v>
       </c>
       <c r="H27" t="n">
-        <v>4884220</v>
+        <v>1917309</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>60517</v>
+        <v>117338</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1414622</v>
+        <v>4684930</v>
       </c>
       <c r="H29" t="n">
-        <v>339763</v>
+        <v>117338</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3571,34 +3571,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>273503</v>
+        <v>4884220</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1994005</v>
+        <v>4884220</v>
       </c>
       <c r="H30" t="n">
-        <v>1917309</v>
+        <v>4884220</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3835,16 +3835,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>162561</v>
+        <v>338135</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>237914</v>
+        <v>478912</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3935,16 +3935,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>338135</v>
+        <v>237914</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3985,16 +3985,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>478912</v>
+        <v>162561</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4035,16 +4035,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4074,23 +4074,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>478912</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>757460</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4108,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>100</v>
@@ -4120,23 +4124,23 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>648855</v>
+        <v>478912</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4166,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>757460</v>
+        <v>1933301</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4177,16 +4181,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4204,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4216,23 +4220,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4091852</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>2741472</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4250,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4262,27 +4270,23 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1933301</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>648855</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4300,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4309,30 +4313,26 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2741472</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1933301</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,26 +4359,26 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1933301</v>
+        <v>4831287</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4408,27 +4408,23 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2175624</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>4091852</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4446,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4455,26 +4451,30 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1933301</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
+        <v>2175624</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4501,26 +4501,26 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2175624</v>
+        <v>3383283</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4550,23 +4550,23 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3055805</v>
+        <v>4091852</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4593,26 +4593,26 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3383283</v>
+        <v>4091852</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4642,23 +4642,23 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4831287</v>
+        <v>3055805</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4685,26 +4685,26 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>3055805</v>
+        <v>1933301</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R21" t="n">
         <v>3383283</v>
@@ -4741,16 +4741,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4780,23 +4780,23 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4091852</v>
+        <v>3055805</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4823,10 +4823,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>4091852</v>
+        <v>2175624</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4879,16 +4879,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4918,23 +4918,23 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4831287</v>
+        <v>5562182</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4971,16 +4971,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4468366</v>
+        <v>5562182</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5063,16 +5063,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5102,23 +5102,23 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5562182</v>
+        <v>4831287</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5562182</v>
+        <v>4468366</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -499,94 +499,94 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -595,22 +595,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -619,46 +619,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -691,22 +691,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -715,70 +715,70 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -787,94 +787,94 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -883,22 +883,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -907,22 +907,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
@@ -931,46 +931,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -979,22 +979,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -1003,70 +1003,70 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -1099,46 +1099,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1290,203 +1290,203 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1994,7 +1994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2386,7 +2386,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>28582</v>
+        <v>71857</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>881388</v>
+        <v>1929309</v>
       </c>
       <c r="H3" t="n">
-        <v>239490</v>
+        <v>297407</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2609,34 +2609,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>6474</v>
+        <v>28582</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1177681</v>
+        <v>881388</v>
       </c>
       <c r="H4" t="n">
-        <v>6474</v>
+        <v>239490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2646,34 +2646,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>71857</v>
+        <v>6474</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1929309</v>
+        <v>1177681</v>
       </c>
       <c r="H5" t="n">
-        <v>297407</v>
+        <v>6474</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2683,34 +2683,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dean Jenkins</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Slumber FC</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Yash Beohar</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fluente in Football</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
       <c r="E6" t="n">
-        <v>30971</v>
+        <v>676529</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>820221</v>
+        <v>998938</v>
       </c>
       <c r="H6" t="n">
-        <v>58227</v>
+        <v>676529</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>15136</v>
+        <v>281617</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>983840</v>
+        <v>1051323</v>
       </c>
       <c r="H7" t="n">
-        <v>45077</v>
+        <v>1076546</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2761,30 +2761,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>676529</v>
+        <v>30971</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>998938</v>
+        <v>820221</v>
       </c>
       <c r="H8" t="n">
-        <v>676529</v>
+        <v>58227</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2794,34 +2794,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>281617</v>
+        <v>15136</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1051323</v>
+        <v>983840</v>
       </c>
       <c r="H9" t="n">
-        <v>1076546</v>
+        <v>45077</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>8917</v>
+        <v>81907</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2118382</v>
+        <v>3252487</v>
       </c>
       <c r="H10" t="n">
-        <v>9146930</v>
+        <v>11118394</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>182900</v>
+        <v>8917</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2098988</v>
+        <v>2118382</v>
       </c>
       <c r="H11" t="n">
-        <v>182900</v>
+        <v>9146930</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>334016</v>
+        <v>38561</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2156629</v>
+        <v>858178</v>
       </c>
       <c r="H12" t="n">
-        <v>2691725</v>
+        <v>726260</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2942,23 +2942,23 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H13" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2979,34 +2979,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>38561</v>
+        <v>182900</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>858178</v>
+        <v>2098988</v>
       </c>
       <c r="H14" t="n">
-        <v>726260</v>
+        <v>182900</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3020,30 +3020,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1615102</v>
+        <v>545267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4234674</v>
+        <v>604934</v>
       </c>
       <c r="H15" t="n">
-        <v>6092784</v>
+        <v>545267</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3053,71 +3053,71 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>410102</v>
+        <v>1320699</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2088802</v>
+        <v>2490743</v>
       </c>
       <c r="H16" t="n">
-        <v>5360778</v>
+        <v>1861933</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>189374</v>
+        <v>1128645</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1757289</v>
+        <v>3434302</v>
       </c>
       <c r="H17" t="n">
-        <v>250879</v>
+        <v>1128645</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3127,34 +3127,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>1128645</v>
+        <v>453230</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3434302</v>
+        <v>5483351</v>
       </c>
       <c r="H18" t="n">
-        <v>1128645</v>
+        <v>8188106</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>95791</v>
+        <v>1615102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2404119</v>
+        <v>4234674</v>
       </c>
       <c r="H19" t="n">
-        <v>5124417</v>
+        <v>6092784</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>31543</v>
+        <v>189374</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>820692</v>
+        <v>1757289</v>
       </c>
       <c r="H20" t="n">
-        <v>1637750</v>
+        <v>250879</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>486041</v>
+        <v>31543</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2415786</v>
+        <v>820692</v>
       </c>
       <c r="H21" t="n">
-        <v>1206623</v>
+        <v>1637750</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3275,34 +3275,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>453230</v>
+        <v>95791</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5483351</v>
+        <v>2404119</v>
       </c>
       <c r="H22" t="n">
-        <v>8188106</v>
+        <v>5124417</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>37120</v>
+        <v>410102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1571193</v>
+        <v>2088802</v>
       </c>
       <c r="H23" t="n">
-        <v>3349378</v>
+        <v>5360778</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3353,67 +3353,67 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>1320699</v>
+        <v>37120</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2490743</v>
+        <v>1571193</v>
       </c>
       <c r="H24" t="n">
-        <v>1861933</v>
+        <v>3349378</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>60517</v>
+        <v>486041</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1414622</v>
+        <v>2415786</v>
       </c>
       <c r="H25" t="n">
-        <v>339763</v>
+        <v>1206623</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3423,34 +3423,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>545267</v>
+        <v>60517</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>604934</v>
+        <v>1414622</v>
       </c>
       <c r="H26" t="n">
-        <v>545267</v>
+        <v>339763</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>273503</v>
+        <v>15288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1994005</v>
+        <v>329510</v>
       </c>
       <c r="H27" t="n">
-        <v>1917309</v>
+        <v>538046</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>15288</v>
+        <v>273503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>329510</v>
+        <v>1994005</v>
       </c>
       <c r="H28" t="n">
-        <v>538046</v>
+        <v>1917309</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3534,34 +3534,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>117338</v>
+        <v>14603</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4684930</v>
+        <v>949628</v>
       </c>
       <c r="H29" t="n">
-        <v>117338</v>
+        <v>515830</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3575,19 +3575,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>4884220</v>
+        <v>117338</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4884220</v>
+        <v>4684930</v>
       </c>
       <c r="H30" t="n">
-        <v>4884220</v>
+        <v>117338</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3612,30 +3612,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>14603</v>
+        <v>4884220</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>949628</v>
+        <v>4884220</v>
       </c>
       <c r="H31" t="n">
-        <v>515830</v>
+        <v>4884220</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3835,16 +3835,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>338135</v>
+        <v>237914</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>478912</v>
+        <v>338135</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3935,16 +3935,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>237914</v>
+        <v>478912</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3985,16 +3985,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4024,27 +4024,23 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>162561</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>478912</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4074,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>757460</v>
+        <v>1933301</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -4085,16 +4081,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4112,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>100</v>
@@ -4124,23 +4120,27 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>478912</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+        <v>162561</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1933301</v>
+        <v>757460</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4181,16 +4181,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4220,27 +4220,23 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2741472</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>4831287</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4258,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4270,23 +4266,27 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>648855</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+        <v>2741472</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4313,26 +4313,26 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1933301</v>
+        <v>4091852</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,26 +4359,26 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>4831287</v>
+        <v>1933301</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4408,23 +4408,23 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4091852</v>
+        <v>648855</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4454,27 +4454,23 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2175624</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>4831287</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4492,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4504,23 +4500,23 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3383283</v>
+        <v>4091852</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4538,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4557,16 +4553,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4584,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4596,23 +4592,23 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4091852</v>
+        <v>3055805</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4630,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4642,23 +4638,27 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3055805</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
+        <v>2175624</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4685,26 +4685,26 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1933301</v>
+        <v>4091852</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4734,23 +4734,23 @@
         <v>0.5</v>
       </c>
       <c r="R21" t="n">
-        <v>3383283</v>
+        <v>1933301</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4787,16 +4787,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4823,26 +4823,26 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2175624</v>
+        <v>3383283</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4869,26 +4869,26 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>4091852</v>
+        <v>2175624</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4915,26 +4915,26 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>5562182</v>
+        <v>3383283</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4964,23 +4964,23 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4831287</v>
+        <v>5562182</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,23 +5010,23 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5562182</v>
+        <v>5203238</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5056,23 +5056,23 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>5203238</v>
+        <v>5562182</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5102,23 +5102,23 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4831287</v>
+        <v>7185986</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5148,23 +5148,23 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4468366</v>
+        <v>4831287</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
         <v>100</v>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>7185986</v>
+        <v>4468366</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,22 +475,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -499,22 +499,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
@@ -523,22 +523,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -547,36 +547,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -591,26 +591,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -619,22 +619,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -643,22 +643,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -667,46 +667,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -715,118 +715,118 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -835,22 +835,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
@@ -859,22 +859,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -883,22 +883,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -907,22 +907,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -931,46 +931,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -979,36 +979,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1023,40 +1023,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1283,175 +1283,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2047,7 +2047,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2539,30 +2539,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>27153</v>
+        <v>71857</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>606381</v>
+        <v>1929309</v>
       </c>
       <c r="H2" t="n">
-        <v>240451</v>
+        <v>297407</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>71857</v>
+        <v>28582</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1929309</v>
+        <v>881388</v>
       </c>
       <c r="H3" t="n">
-        <v>297407</v>
+        <v>239490</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2613,30 +2613,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>28582</v>
+        <v>27153</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>881388</v>
+        <v>606381</v>
       </c>
       <c r="H4" t="n">
-        <v>239490</v>
+        <v>240451</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2650,30 +2650,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>6474</v>
+        <v>15136</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1177681</v>
+        <v>983840</v>
       </c>
       <c r="H5" t="n">
-        <v>6474</v>
+        <v>45077</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2683,23 +2683,23 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2720,34 +2720,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>281617</v>
+        <v>676529</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1051323</v>
+        <v>998938</v>
       </c>
       <c r="H7" t="n">
-        <v>1076546</v>
+        <v>676529</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2761,30 +2761,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>30971</v>
+        <v>8917</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>820221</v>
+        <v>2118382</v>
       </c>
       <c r="H8" t="n">
-        <v>58227</v>
+        <v>9146930</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2798,30 +2798,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>15136</v>
+        <v>281617</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>983840</v>
+        <v>1051323</v>
       </c>
       <c r="H9" t="n">
-        <v>45077</v>
+        <v>1076546</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>81907</v>
+        <v>38561</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3252487</v>
+        <v>858178</v>
       </c>
       <c r="H10" t="n">
-        <v>11118394</v>
+        <v>726260</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2868,34 +2868,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yash Beohar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fluente in Football</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Raveesh Kalra</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MaSalah</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>7</v>
-      </c>
       <c r="E11" t="n">
-        <v>8917</v>
+        <v>30971</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2118382</v>
+        <v>820221</v>
       </c>
       <c r="H11" t="n">
-        <v>9146930</v>
+        <v>58227</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,30 +2909,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>38561</v>
+        <v>334016</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>858178</v>
+        <v>2156629</v>
       </c>
       <c r="H12" t="n">
-        <v>726260</v>
+        <v>2691725</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2942,23 +2942,23 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Karan Chopra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fpl_26_27</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Aparnesh Mishra</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Mishra's 13</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>9</v>
-      </c>
       <c r="E13" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H13" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2979,23 +2979,23 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>182900</v>
+        <v>545267</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2098988</v>
+        <v>604934</v>
       </c>
       <c r="H14" t="n">
-        <v>182900</v>
+        <v>545267</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3016,75 +3016,75 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>545267</v>
+        <v>1320699</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>604934</v>
+        <v>2490743</v>
       </c>
       <c r="H15" t="n">
-        <v>545267</v>
+        <v>1861933</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>1320699</v>
+        <v>182900</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2490743</v>
+        <v>2098988</v>
       </c>
       <c r="H16" t="n">
-        <v>1861933</v>
+        <v>182900</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>1128645</v>
+        <v>189374</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3434302</v>
+        <v>1757289</v>
       </c>
       <c r="H17" t="n">
-        <v>1128645</v>
+        <v>250879</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>453230</v>
+        <v>31543</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5483351</v>
+        <v>820692</v>
       </c>
       <c r="H18" t="n">
-        <v>8188106</v>
+        <v>1637750</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>1615102</v>
+        <v>60517</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4234674</v>
+        <v>1414622</v>
       </c>
       <c r="H19" t="n">
-        <v>6092784</v>
+        <v>339763</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>189374</v>
+        <v>1128645</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1757289</v>
+        <v>3434302</v>
       </c>
       <c r="H20" t="n">
-        <v>250879</v>
+        <v>1128645</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>31543</v>
+        <v>453230</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>820692</v>
+        <v>5483351</v>
       </c>
       <c r="H21" t="n">
-        <v>1637750</v>
+        <v>8188106</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3275,34 +3275,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>95791</v>
+        <v>1615102</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2404119</v>
+        <v>4234674</v>
       </c>
       <c r="H22" t="n">
-        <v>5124417</v>
+        <v>6092784</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>410102</v>
+        <v>95791</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2088802</v>
+        <v>2404119</v>
       </c>
       <c r="H23" t="n">
-        <v>5360778</v>
+        <v>5124417</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>37120</v>
+        <v>410102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1571193</v>
+        <v>2088802</v>
       </c>
       <c r="H24" t="n">
-        <v>3349378</v>
+        <v>5360778</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3386,34 +3386,34 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>486041</v>
+        <v>37120</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2415786</v>
+        <v>1571193</v>
       </c>
       <c r="H25" t="n">
-        <v>1206623</v>
+        <v>3349378</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3423,34 +3423,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>60517</v>
+        <v>486041</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1414622</v>
+        <v>2415786</v>
       </c>
       <c r="H26" t="n">
-        <v>339763</v>
+        <v>1206623</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>273503</v>
+        <v>14603</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1994005</v>
+        <v>949628</v>
       </c>
       <c r="H28" t="n">
-        <v>1917309</v>
+        <v>515830</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>14603</v>
+        <v>273503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>949628</v>
+        <v>1994005</v>
       </c>
       <c r="H29" t="n">
-        <v>515830</v>
+        <v>1917309</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>194557</v>
+        <v>129301</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3835,16 +3835,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>237914</v>
+        <v>169929</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>338135</v>
+        <v>196944</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3935,16 +3935,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>478912</v>
+        <v>465434</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4024,23 +4024,27 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>478912</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>610764</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4058,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4070,27 +4074,23 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1933301</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>610764</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>162561</v>
+        <v>697042</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>757460</v>
+        <v>793389</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4181,16 +4181,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4220,23 +4220,23 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4831287</v>
+        <v>903220</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2741472</v>
+        <v>903220</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -4277,16 +4277,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4313,26 +4313,26 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>4091852</v>
+        <v>1166621</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,26 +4359,26 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1933301</v>
+        <v>1166621</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4408,23 +4408,23 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>648855</v>
+        <v>1908174</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4454,23 +4454,23 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4831287</v>
+        <v>1908174</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4500,23 +4500,23 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4091852</v>
+        <v>2393930</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4546,23 +4546,23 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4091852</v>
+        <v>2666208</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4589,26 +4589,26 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>3055805</v>
+        <v>2974470</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4638,27 +4638,23 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2175624</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>3926627</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4676,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4688,23 +4684,23 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4091852</v>
+        <v>3926627</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4722,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4731,26 +4727,26 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1933301</v>
+        <v>4279248</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4768,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4780,23 +4776,27 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3055805</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+        <v>4625053</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4826,19 +4826,19 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3383283</v>
+        <v>4983466</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4869,26 +4869,26 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2175624</v>
+        <v>5324535</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4918,19 +4918,19 @@
         <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>3383283</v>
+        <v>5324535</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4961,10 +4961,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>5562182</v>
+        <v>5994582</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,19 +5010,19 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5203238</v>
+        <v>6322267</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5056,19 +5056,19 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>5562182</v>
+        <v>6624262</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>7185986</v>
+        <v>6624262</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4831287</v>
+        <v>7174473</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4468366</v>
+        <v>7835222</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
         <v>100</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8650458</v>
+        <v>8682318</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1339,28 +1339,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2835,19 +2835,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>38561</v>
+        <v>30971</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>858178</v>
+        <v>820221</v>
       </c>
       <c r="H10" t="n">
-        <v>726260</v>
+        <v>58227</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,19 +2872,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>30971</v>
+        <v>38561</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820221</v>
+        <v>858178</v>
       </c>
       <c r="H11" t="n">
-        <v>58227</v>
+        <v>726260</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2909,19 +2909,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H12" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H13" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -4181,12 +4181,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4222,17 +4222,21 @@
       <c r="R10" t="n">
         <v>903220</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4254,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4268,21 +4272,17 @@
       <c r="R11" t="n">
         <v>903220</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>1166621</v>
@@ -4323,12 +4323,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
         <v>1166621</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1353,28 +1353,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2909,19 +2909,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H12" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H13" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,34 +2983,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>545267</v>
+        <v>1320699</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>604934</v>
+        <v>2490743</v>
       </c>
       <c r="H14" t="n">
-        <v>545267</v>
+        <v>1861933</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3020,34 +3020,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1320699</v>
+        <v>545267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2490743</v>
+        <v>604934</v>
       </c>
       <c r="H15" t="n">
-        <v>1861933</v>
+        <v>545267</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -4277,12 +4277,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R12" t="n">
         <v>1166621</v>
@@ -4323,12 +4323,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>1166621</v>
@@ -4369,12 +4369,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4415,12 +4415,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
@@ -1437,14 +1437,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H6" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>410102</v>
+        <v>37120</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2088802</v>
+        <v>1571193</v>
       </c>
       <c r="H24" t="n">
-        <v>5360778</v>
+        <v>3349378</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>37120</v>
+        <v>410102</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1571193</v>
+        <v>2088802</v>
       </c>
       <c r="H25" t="n">
-        <v>3349378</v>
+        <v>5360778</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>14603</v>
+        <v>273503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>949628</v>
+        <v>1994005</v>
       </c>
       <c r="H28" t="n">
-        <v>515830</v>
+        <v>1917309</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>273503</v>
+        <v>14603</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1994005</v>
+        <v>949628</v>
       </c>
       <c r="H29" t="n">
-        <v>1917309</v>
+        <v>515830</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4026,21 +4026,17 @@
       <c r="R6" t="n">
         <v>610764</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4062,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4076,7 +4072,11 @@
       <c r="R7" t="n">
         <v>610764</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4833,12 +4833,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R24" t="n">
         <v>5324535</v>
@@ -4879,12 +4879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4915,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>5324535</v>
@@ -5017,12 +5017,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5063,12 +5063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
@@ -1367,14 +1367,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1402,14 +1402,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
@@ -1437,14 +1437,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2983,34 +2983,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1320699</v>
+        <v>545267</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2490743</v>
+        <v>604934</v>
       </c>
       <c r="H14" t="n">
-        <v>1861933</v>
+        <v>545267</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3020,34 +3020,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>545267</v>
+        <v>1320699</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>604934</v>
+        <v>2490743</v>
       </c>
       <c r="H15" t="n">
-        <v>545267</v>
+        <v>1861933</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>60517</v>
+        <v>1128645</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1414622</v>
+        <v>3434302</v>
       </c>
       <c r="H19" t="n">
-        <v>339763</v>
+        <v>1128645</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>1128645</v>
+        <v>60517</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3434302</v>
+        <v>1414622</v>
       </c>
       <c r="H20" t="n">
-        <v>1128645</v>
+        <v>339763</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>37120</v>
+        <v>410102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1571193</v>
+        <v>2088802</v>
       </c>
       <c r="H24" t="n">
-        <v>3349378</v>
+        <v>5360778</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>410102</v>
+        <v>37120</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2088802</v>
+        <v>1571193</v>
       </c>
       <c r="H25" t="n">
-        <v>5360778</v>
+        <v>3349378</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>273503</v>
+        <v>14603</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1994005</v>
+        <v>949628</v>
       </c>
       <c r="H28" t="n">
-        <v>1917309</v>
+        <v>515830</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>14603</v>
+        <v>273503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>949628</v>
+        <v>1994005</v>
       </c>
       <c r="H29" t="n">
-        <v>515830</v>
+        <v>1917309</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4026,17 +4026,21 @@
       <c r="R6" t="n">
         <v>610764</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4058,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4072,11 +4076,7 @@
       <c r="R7" t="n">
         <v>610764</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4369,12 +4369,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4415,12 +4415,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4599,12 +4599,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4645,12 +4645,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4833,12 +4833,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>5324535</v>
@@ -4879,12 +4879,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4915,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R25" t="n">
         <v>5324535</v>
@@ -5017,12 +5017,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5063,12 +5063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -595,12 +595,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -715,12 +715,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1311,14 +1311,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
@@ -1353,28 +1353,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
     </row>
@@ -1402,14 +1402,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1818,7 +1818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H6" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1177681</v>
+        <v>998938</v>
       </c>
       <c r="H7" t="n">
-        <v>6474</v>
+        <v>676529</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2909,19 +2909,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H12" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H13" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,34 +2983,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>545267</v>
+        <v>1320699</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>604934</v>
+        <v>2490743</v>
       </c>
       <c r="H14" t="n">
-        <v>545267</v>
+        <v>1861933</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3020,34 +3020,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1320699</v>
+        <v>545267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2490743</v>
+        <v>604934</v>
       </c>
       <c r="H15" t="n">
-        <v>1861933</v>
+        <v>545267</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>1128645</v>
+        <v>60517</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3434302</v>
+        <v>1414622</v>
       </c>
       <c r="H19" t="n">
-        <v>1128645</v>
+        <v>339763</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>60517</v>
+        <v>1128645</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1414622</v>
+        <v>3434302</v>
       </c>
       <c r="H20" t="n">
-        <v>339763</v>
+        <v>1128645</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3501,30 +3501,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>273503</v>
+        <v>14603</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1994005</v>
+        <v>949628</v>
       </c>
       <c r="H28" t="n">
-        <v>1917309</v>
+        <v>515830</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>14603</v>
+        <v>273503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>949628</v>
+        <v>1994005</v>
       </c>
       <c r="H29" t="n">
-        <v>515830</v>
+        <v>1917309</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3985,12 +3985,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>100</v>
@@ -4026,17 +4026,21 @@
       <c r="R6" t="n">
         <v>610764</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4058,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4072,11 +4076,7 @@
       <c r="R7" t="n">
         <v>610764</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4277,12 +4277,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>1166621</v>
@@ -4323,12 +4323,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
         <v>1166621</v>
@@ -4369,12 +4369,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4415,12 +4415,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>100</v>
@@ -4599,12 +4599,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4645,12 +4645,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -5017,12 +5017,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5063,12 +5063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,12 +907,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1339,14 +1339,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
@@ -1402,14 +1402,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2835,19 +2835,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>30971</v>
+        <v>38561</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820221</v>
+        <v>858178</v>
       </c>
       <c r="H10" t="n">
-        <v>58227</v>
+        <v>726260</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,19 +2872,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>38561</v>
+        <v>30971</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>858178</v>
+        <v>820221</v>
       </c>
       <c r="H11" t="n">
-        <v>726260</v>
+        <v>58227</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>60517</v>
+        <v>1128645</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1414622</v>
+        <v>3434302</v>
       </c>
       <c r="H19" t="n">
-        <v>339763</v>
+        <v>1128645</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>1128645</v>
+        <v>60517</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3434302</v>
+        <v>1414622</v>
       </c>
       <c r="H20" t="n">
-        <v>1128645</v>
+        <v>339763</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4181,12 +4181,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4222,21 +4222,17 @@
       <c r="R10" t="n">
         <v>903220</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4258,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4272,7 +4268,11 @@
       <c r="R11" t="n">
         <v>903220</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4599,12 +4599,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4645,12 +4645,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -547,70 +547,70 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -667,94 +667,94 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -763,27 +763,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -859,22 +859,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -883,70 +883,70 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
@@ -1003,46 +1003,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -1075,27 +1075,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1108,18 +1108,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1304,21 +1304,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
@@ -1339,35 +1339,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
@@ -1395,28 +1395,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1437,28 +1437,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1479,14 +1479,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Nilay jain</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1983,7 +1983,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1994,7 +1994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2375,7 +2375,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2386,7 +2386,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2650,30 +2650,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>15136</v>
+        <v>38561</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>983840</v>
+        <v>858178</v>
       </c>
       <c r="H5" t="n">
-        <v>45077</v>
+        <v>726260</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2683,34 +2683,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>6474</v>
+        <v>15136</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1177681</v>
+        <v>983840</v>
       </c>
       <c r="H6" t="n">
-        <v>6474</v>
+        <v>45077</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2720,23 +2720,23 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>998938</v>
+        <v>1177681</v>
       </c>
       <c r="H7" t="n">
-        <v>676529</v>
+        <v>6474</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>38561</v>
+        <v>30971</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>858178</v>
+        <v>820221</v>
       </c>
       <c r="H10" t="n">
-        <v>726260</v>
+        <v>58227</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2868,34 +2868,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>30971</v>
+        <v>31543</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820221</v>
+        <v>820692</v>
       </c>
       <c r="H11" t="n">
-        <v>58227</v>
+        <v>1637750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2905,23 +2905,23 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H12" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2942,23 +2942,23 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H13" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,40 +2983,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>1320699</v>
+        <v>676529</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2490743</v>
+        <v>998938</v>
       </c>
       <c r="H14" t="n">
-        <v>1861933</v>
+        <v>676529</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>31543</v>
+        <v>37120</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>820692</v>
+        <v>1571193</v>
       </c>
       <c r="H18" t="n">
-        <v>1637750</v>
+        <v>3349378</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>1128645</v>
+        <v>60517</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3434302</v>
+        <v>1414622</v>
       </c>
       <c r="H19" t="n">
-        <v>1128645</v>
+        <v>339763</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3201,34 +3201,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>60517</v>
+        <v>453230</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1414622</v>
+        <v>5483351</v>
       </c>
       <c r="H20" t="n">
-        <v>339763</v>
+        <v>8188106</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3238,38 +3238,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>453230</v>
+        <v>1320699</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5483351</v>
+        <v>2490743</v>
       </c>
       <c r="H21" t="n">
-        <v>8188106</v>
+        <v>1861933</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3353,30 +3353,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>37120</v>
+        <v>410102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1571193</v>
+        <v>2088802</v>
       </c>
       <c r="H24" t="n">
-        <v>3349378</v>
+        <v>5360778</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3386,34 +3386,34 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>410102</v>
+        <v>486041</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2088802</v>
+        <v>2415786</v>
       </c>
       <c r="H25" t="n">
-        <v>5360778</v>
+        <v>1206623</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>486041</v>
+        <v>15288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2415786</v>
+        <v>329510</v>
       </c>
       <c r="H26" t="n">
-        <v>1206623</v>
+        <v>538046</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>15288</v>
+        <v>1128645</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>329510</v>
+        <v>3434302</v>
       </c>
       <c r="H27" t="n">
-        <v>538046</v>
+        <v>1128645</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3575,19 +3575,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>117338</v>
+        <v>4884220</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4684930</v>
+        <v>4884220</v>
       </c>
       <c r="H30" t="n">
-        <v>117338</v>
+        <v>4884220</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3612,19 +3612,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>4884220</v>
+        <v>117338</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4884220</v>
+        <v>4684930</v>
       </c>
       <c r="H31" t="n">
-        <v>4884220</v>
+        <v>117338</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3935,16 +3935,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O5" t="n">
         <v>100</v>
@@ -3974,27 +3974,23 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>465434</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>903220</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4024,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>610764</v>
+        <v>465434</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4035,16 +4031,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4062,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
@@ -4076,7 +4072,11 @@
       <c r="R7" t="n">
         <v>610764</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4181,16 +4181,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4222,21 +4222,25 @@
       <c r="R10" t="n">
         <v>903220</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4254,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4263,30 +4267,26 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>903220</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>2974470</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R12" t="n">
         <v>1166621</v>
@@ -4323,16 +4323,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>1166621</v>
@@ -4369,16 +4369,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1908174</v>
+        <v>610764</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4553,16 +4553,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4592,23 +4592,23 @@
         <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2974470</v>
+        <v>5324535</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
@@ -4645,16 +4645,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4684,23 +4684,23 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3926627</v>
+        <v>4279248</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4279248</v>
+        <v>1908174</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4833,16 +4833,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>5324535</v>
@@ -4879,16 +4879,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4915,26 +4915,26 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>5324535</v>
+        <v>5994582</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4961,26 +4961,26 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5994582</v>
+        <v>6322267</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6322267</v>
+        <v>3926627</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5109,16 +5109,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5148,23 +5148,23 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7174473</v>
+        <v>7835222</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O31" t="n">
         <v>100</v>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>7835222</v>
+        <v>7174473</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -484,37 +484,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -523,70 +523,70 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -595,22 +595,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -619,22 +619,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -643,22 +643,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -667,27 +667,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -700,42 +700,42 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -748,37 +748,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -820,37 +820,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
@@ -859,22 +859,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -916,37 +916,37 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -955,22 +955,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -979,27 +979,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -1108,27 +1108,27 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1290,56 +1290,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1388,14 +1388,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
@@ -1416,21 +1416,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1715,7 +1715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1730,7 +1730,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1741,7 +1741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1752,7 +1752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1785,7 +1785,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2107,7 +2107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2122,7 +2122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2133,7 +2133,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2177,7 +2177,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2572,34 +2572,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>28582</v>
+        <v>38561</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>881388</v>
+        <v>858178</v>
       </c>
       <c r="H3" t="n">
-        <v>239490</v>
+        <v>726260</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2613,30 +2613,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>27153</v>
+        <v>28582</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>606381</v>
+        <v>881388</v>
       </c>
       <c r="H4" t="n">
-        <v>240451</v>
+        <v>239490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2646,34 +2646,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>38561</v>
+        <v>37120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>858178</v>
+        <v>1571193</v>
       </c>
       <c r="H5" t="n">
-        <v>726260</v>
+        <v>3349378</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2683,34 +2683,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>15136</v>
+        <v>27153</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>983840</v>
+        <v>606381</v>
       </c>
       <c r="H6" t="n">
-        <v>45077</v>
+        <v>240451</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2724,30 +2724,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>6474</v>
+        <v>15136</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1177681</v>
+        <v>983840</v>
       </c>
       <c r="H7" t="n">
-        <v>6474</v>
+        <v>45077</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2761,30 +2761,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>8917</v>
+        <v>6474</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2118382</v>
+        <v>1177681</v>
       </c>
       <c r="H8" t="n">
-        <v>9146930</v>
+        <v>6474</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2798,30 +2798,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>281617</v>
+        <v>8917</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1051323</v>
+        <v>2118382</v>
       </c>
       <c r="H9" t="n">
-        <v>1076546</v>
+        <v>9146930</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>30971</v>
+        <v>281617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820221</v>
+        <v>1051323</v>
       </c>
       <c r="H10" t="n">
-        <v>58227</v>
+        <v>1076546</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2905,34 +2905,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yash Beohar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fluente in Football</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Aparnesh Mishra</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Mishra's 13</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>9</v>
-      </c>
       <c r="E12" t="n">
-        <v>334016</v>
+        <v>30971</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2156629</v>
+        <v>820221</v>
       </c>
       <c r="H12" t="n">
-        <v>2691725</v>
+        <v>58227</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2979,34 +2979,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>676529</v>
+        <v>334016</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>998938</v>
+        <v>2156629</v>
       </c>
       <c r="H14" t="n">
-        <v>676529</v>
+        <v>2691725</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3090,34 +3090,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>189374</v>
+        <v>676529</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1757289</v>
+        <v>998938</v>
       </c>
       <c r="H17" t="n">
-        <v>250879</v>
+        <v>676529</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>37120</v>
+        <v>189374</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1571193</v>
+        <v>1757289</v>
       </c>
       <c r="H18" t="n">
-        <v>3349378</v>
+        <v>250879</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3238,38 +3238,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>1320699</v>
+        <v>1615102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2490743</v>
+        <v>4234674</v>
       </c>
       <c r="H21" t="n">
-        <v>1861933</v>
+        <v>6092784</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3279,30 +3279,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>1615102</v>
+        <v>95791</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4234674</v>
+        <v>2404119</v>
       </c>
       <c r="H22" t="n">
-        <v>6092784</v>
+        <v>5124417</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,40 +3316,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>95791</v>
+        <v>1320699</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2404119</v>
+        <v>2490743</v>
       </c>
       <c r="H23" t="n">
-        <v>5124417</v>
+        <v>1861933</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3464,30 +3464,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>1128645</v>
+        <v>273503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3434302</v>
+        <v>1994005</v>
       </c>
       <c r="H27" t="n">
-        <v>1128645</v>
+        <v>1917309</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3534,34 +3534,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>273503</v>
+        <v>1128645</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1994005</v>
+        <v>3434302</v>
       </c>
       <c r="H29" t="n">
-        <v>1917309</v>
+        <v>1128645</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3835,16 +3835,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
         <v>100</v>
@@ -3874,27 +3874,23 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>169929</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>903220</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3924,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>196944</v>
+        <v>169929</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3935,16 +3931,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3962,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>100</v>
@@ -3971,26 +3967,26 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>903220</v>
+        <v>5324535</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4020,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>465434</v>
+        <v>196944</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4031,16 +4027,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4070,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>610764</v>
+        <v>465434</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -4081,16 +4077,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4120,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>697042</v>
+        <v>610764</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -4131,16 +4127,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4170,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>793389</v>
+        <v>697042</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4181,16 +4177,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4220,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>903220</v>
+        <v>793389</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -4240,7 +4236,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4277,16 +4273,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4304,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
@@ -4313,12 +4309,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1166621</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
+        <v>903220</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4369,16 +4369,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,10 +4405,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>610764</v>
+        <v>1166621</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -4507,16 +4507,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -4546,23 +4546,23 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2666208</v>
+        <v>610764</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>5324535</v>
+        <v>2666208</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4691,16 +4691,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4730,23 +4730,27 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1908174</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+        <v>4625053</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4764,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4776,27 +4780,23 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4625053</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>4983466</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4983466</v>
+        <v>1908174</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4971,16 +4971,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3926627</v>
+        <v>6624262</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5063,12 +5063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>6624262</v>
+        <v>3926627</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -547,12 +547,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1297,14 +1297,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
@@ -1381,14 +1381,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2613,30 +2613,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>28582</v>
+        <v>37120</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>881388</v>
+        <v>1571193</v>
       </c>
       <c r="H4" t="n">
-        <v>239490</v>
+        <v>3349378</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2650,30 +2650,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>37120</v>
+        <v>28582</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1571193</v>
+        <v>881388</v>
       </c>
       <c r="H5" t="n">
-        <v>3349378</v>
+        <v>239490</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3057,19 +3057,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2098988</v>
+        <v>998938</v>
       </c>
       <c r="H16" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>998938</v>
+        <v>2098988</v>
       </c>
       <c r="H17" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>129301</v>
+        <v>227612</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3874,19 +3874,19 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>903220</v>
+        <v>227612</v>
       </c>
       <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
         <v>100</v>
@@ -3917,26 +3917,22 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>169929</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>282653</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3958,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>100</v>
@@ -3967,12 +3963,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5324535</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>282653</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4016,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>196944</v>
+        <v>325933</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>465434</v>
+        <v>728229</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>610764</v>
+        <v>933083</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>697042</v>
+        <v>1048239</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>793389</v>
+        <v>1176755</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2974470</v>
+        <v>1176755</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>903220</v>
+        <v>1318225</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1166621</v>
+        <v>1639201</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
@@ -4408,7 +4408,7 @@
         <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1166621</v>
+        <v>1639201</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
@@ -4454,19 +4454,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1908174</v>
+        <v>2453870</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4500,19 +4500,19 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2393930</v>
+        <v>2933691</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4546,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>610764</v>
+        <v>2933691</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2666208</v>
+        <v>3191650</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3926627</v>
+        <v>4296648</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4279248</v>
+        <v>4591177</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4625053</v>
+        <v>4872274</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4983466</v>
+        <v>5156448</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1908174</v>
+        <v>5422725</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5324535</v>
+        <v>5422725</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
@@ -4918,7 +4918,7 @@
         <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>5994582</v>
+        <v>5940335</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>6322267</v>
+        <v>6192234</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6624262</v>
+        <v>6430955</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>6624262</v>
+        <v>6430955</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3926627</v>
+        <v>7068324</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7835222</v>
+        <v>7432405</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>7174473</v>
+        <v>8436180</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8682318</v>
+        <v>8580188</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,12 +475,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -499,12 +499,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1283,14 +1283,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
     </row>
@@ -1339,14 +1339,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1360,14 +1360,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
@@ -1381,14 +1381,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1670,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2047,7 +2047,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2062,7 +2062,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2539,30 +2539,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>71857</v>
+        <v>38561</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1929309</v>
+        <v>858178</v>
       </c>
       <c r="H2" t="n">
-        <v>297407</v>
+        <v>726260</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2576,30 +2576,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>38561</v>
+        <v>71857</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>858178</v>
+        <v>1929309</v>
       </c>
       <c r="H3" t="n">
-        <v>726260</v>
+        <v>297407</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H10" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H11" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H13" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,19 +2983,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H14" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3057,19 +3057,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>998938</v>
+        <v>2098988</v>
       </c>
       <c r="H16" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2098988</v>
+        <v>998938</v>
       </c>
       <c r="H17" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3785,12 +3785,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
         <v>100</v>
@@ -3826,21 +3826,17 @@
       <c r="R2" t="n">
         <v>227612</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3862,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>100</v>
@@ -3876,7 +3872,11 @@
       <c r="R3" t="n">
         <v>227612</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,26 +4213,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
         <v>1176755</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4254,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4263,12 +4259,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>1176755</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4323,12 +4323,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
         <v>1639201</v>
@@ -4369,12 +4369,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1639201</v>
@@ -4461,12 +4461,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4507,12 +4507,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -547,12 +547,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1297,14 +1297,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
     </row>
@@ -1381,14 +1381,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1700,7 +1700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1840,7 +1840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2232,7 +2232,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2613,30 +2613,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>37120</v>
+        <v>28582</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1571193</v>
+        <v>881388</v>
       </c>
       <c r="H4" t="n">
-        <v>3349378</v>
+        <v>239490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2650,30 +2650,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>28582</v>
+        <v>37120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>881388</v>
+        <v>1571193</v>
       </c>
       <c r="H5" t="n">
-        <v>239490</v>
+        <v>3349378</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3057,19 +3057,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2098988</v>
+        <v>998938</v>
       </c>
       <c r="H16" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>998938</v>
+        <v>2098988</v>
       </c>
       <c r="H17" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3881,12 +3881,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>100</v>
@@ -3917,22 +3917,26 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>282653</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3954,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>100</v>
@@ -3963,16 +3967,12 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R5" t="n">
         <v>282653</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4461,12 +4461,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4507,12 +4507,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1339,14 +1339,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
@@ -1430,14 +1430,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H10" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H11" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3316,34 +3316,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>1320699</v>
+        <v>410102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2490743</v>
+        <v>2088802</v>
       </c>
       <c r="H23" t="n">
-        <v>1861933</v>
+        <v>5360778</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3353,34 +3353,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>410102</v>
+        <v>1320699</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2088802</v>
+        <v>2490743</v>
       </c>
       <c r="H24" t="n">
-        <v>5360778</v>
+        <v>1861933</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,22 +4213,26 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1176755</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4250,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4259,16 +4263,12 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
         <v>1176755</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4787,12 +4787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4833,12 +4833,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -855,26 +855,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -883,22 +883,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
@@ -907,22 +907,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -931,22 +931,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -955,22 +955,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -979,36 +979,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -1051,70 +1051,70 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
@@ -1123,22 +1123,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -1195,22 +1195,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1339,14 +1339,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
     </row>
@@ -1360,14 +1360,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
     </row>
@@ -1395,84 +1395,84 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
     </row>
@@ -1486,14 +1486,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1774,7 +1774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1796,7 +1796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1829,7 +1829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1862,7 +1862,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1873,7 +1873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1884,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1895,7 +1895,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1906,7 +1906,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,7 +1917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1928,7 +1928,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1939,7 +1939,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1950,7 +1950,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1961,7 +1961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1972,7 +1972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1994,7 +1994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2005,7 +2005,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2155,7 +2155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2188,7 +2188,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2199,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2221,7 +2221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2254,7 +2254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2265,7 +2265,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2276,7 +2276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2287,7 +2287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2298,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2309,7 +2309,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2320,7 +2320,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2331,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2353,7 +2353,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2364,7 +2364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2386,7 +2386,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2397,7 +2397,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2835,30 +2835,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H10" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +2872,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H11" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H13" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,19 +2983,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H14" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3057,34 +3057,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>676529</v>
+        <v>1320699</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>998938</v>
+        <v>2490743</v>
       </c>
       <c r="H16" t="n">
-        <v>676529</v>
+        <v>1861933</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3127,34 +3127,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>189374</v>
+        <v>676529</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1757289</v>
+        <v>998938</v>
       </c>
       <c r="H18" t="n">
-        <v>250879</v>
+        <v>676529</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3168,30 +3168,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>60517</v>
+        <v>189374</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1414622</v>
+        <v>1757289</v>
       </c>
       <c r="H19" t="n">
-        <v>339763</v>
+        <v>250879</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3205,30 +3205,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>453230</v>
+        <v>60517</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5483351</v>
+        <v>1414622</v>
       </c>
       <c r="H20" t="n">
-        <v>8188106</v>
+        <v>339763</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3242,30 +3242,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>1615102</v>
+        <v>453230</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4234674</v>
+        <v>5483351</v>
       </c>
       <c r="H21" t="n">
-        <v>6092784</v>
+        <v>8188106</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3279,30 +3279,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>95791</v>
+        <v>1615102</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2404119</v>
+        <v>4234674</v>
       </c>
       <c r="H22" t="n">
-        <v>5124417</v>
+        <v>6092784</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3316,30 +3316,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>410102</v>
+        <v>95791</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2088802</v>
+        <v>2404119</v>
       </c>
       <c r="H23" t="n">
-        <v>5360778</v>
+        <v>5124417</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3349,38 +3349,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>1320699</v>
+        <v>410102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2490743</v>
+        <v>2088802</v>
       </c>
       <c r="H24" t="n">
-        <v>1861933</v>
+        <v>5360778</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3390,30 +3390,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>486041</v>
+        <v>1128645</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2415786</v>
+        <v>3434302</v>
       </c>
       <c r="H25" t="n">
-        <v>1206623</v>
+        <v>1128645</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3427,30 +3427,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>15288</v>
+        <v>486041</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>329510</v>
+        <v>2415786</v>
       </c>
       <c r="H26" t="n">
-        <v>538046</v>
+        <v>1206623</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>273503</v>
+        <v>14603</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1994005</v>
+        <v>949628</v>
       </c>
       <c r="H27" t="n">
-        <v>1917309</v>
+        <v>515830</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3497,34 +3497,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>14603</v>
+        <v>15288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>949628</v>
+        <v>329510</v>
       </c>
       <c r="H28" t="n">
-        <v>515830</v>
+        <v>538046</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3538,30 +3538,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>1128645</v>
+        <v>273503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3434302</v>
+        <v>1994005</v>
       </c>
       <c r="H29" t="n">
-        <v>1128645</v>
+        <v>1917309</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3612,35 +3612,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>117338</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>4684930</v>
-      </c>
-      <c r="H31" t="n">
-        <v>117338</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3649,16 +3630,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>117338</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>4684930</v>
+      </c>
+      <c r="H32" t="n">
+        <v>117338</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>227612</v>
+        <v>279827</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>227612</v>
+        <v>279827</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>282653</v>
+        <v>344108</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>282653</v>
+        <v>344108</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
@@ -4016,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>325933</v>
+        <v>398656</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>728229</v>
+        <v>893714</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>933083</v>
+        <v>1142767</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1048239</v>
+        <v>1282717</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4177,12 +4177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,26 +4213,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1176755</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1436683</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4254,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4263,12 +4259,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1176755</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+        <v>1436683</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1318225</v>
+        <v>1605173</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -4323,12 +4323,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,22 +4359,22 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1639201</v>
+        <v>1987556</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,10 +4405,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1639201</v>
+        <v>1987556</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
@@ -4454,19 +4454,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2453870</v>
+        <v>2935782</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -4500,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2933691</v>
+        <v>3482299</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
@@ -4546,23 +4546,23 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2933691</v>
+        <v>3482299</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4592,23 +4592,23 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3191650</v>
+        <v>3482299</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4638,23 +4638,23 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4296648</v>
+        <v>3770910</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
@@ -4684,23 +4684,23 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4591177</v>
+        <v>4969899</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
         <v>100</v>
@@ -4730,27 +4730,23 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4872274</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>5282775</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4768,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>100</v>
@@ -4780,23 +4776,27 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5156448</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+        <v>5572584</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
         <v>100</v>
@@ -4826,19 +4826,19 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5422725</v>
+        <v>5859109</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
@@ -4872,23 +4872,23 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5422725</v>
+        <v>6124832</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>100</v>
@@ -4915,26 +4915,26 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5940335</v>
+        <v>6382778</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4961,26 +4961,26 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>6192234</v>
+        <v>6633922</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5010,23 +5010,23 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6430955</v>
+        <v>6633922</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>100</v>
@@ -5056,23 +5056,23 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>6430955</v>
+        <v>6875541</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>7068324</v>
+        <v>7094513</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
@@ -5148,23 +5148,23 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7432405</v>
+        <v>7658231</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>100</v>
@@ -5194,23 +5194,23 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>8436180</v>
+        <v>7960655</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>100</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8580188</v>
+        <v>8566706</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,12 +475,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -499,12 +499,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,12 +523,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -547,12 +547,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -763,12 +763,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1224,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,6 +1256,294 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Valid?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prateek gupta</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pranav Thomas</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nilay jain</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Danish Javed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aditya Vaidya</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Satweek Nayak</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>42</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aayush Khanna</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>42</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Deepankar Sachdeva</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>43</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Varun Khurana</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>44</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ashwin Jose</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rajit Das</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Karan Khanna</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>47</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1279,33 +1567,50 @@
           <t>Manager</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>GW1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
-        </is>
+          <t>Aquib Razack</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
-        </is>
+          <t>Abhay Rawat</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
-        </is>
+          <t>Abhishek Gupte</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
-        </is>
+          <t>Abhiraj Singh</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -1314,6 +1619,9 @@
           <t>Abhinav Premsekhar</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1321,6 +1629,9 @@
           <t>Naman Agrawal</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1328,6 +1639,9 @@
           <t>Arshaq Razack</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1335,19 +1649,28 @@
           <t>Raveesh Kalra</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
-        </is>
+          <t>Anish Joshi</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
-        </is>
+          <t>Shivanshu Madan</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1356,19 +1679,28 @@
           <t>Yash Beohar</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
-        </is>
+          <t>Aparnesh Mishra</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
-        </is>
+          <t>Karan Chopra</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -1377,6 +1709,9 @@
           <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1384,19 +1719,28 @@
           <t>Rohan Agrawal</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
-        </is>
+          <t>Dean Jenkins</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
-        </is>
+          <t>Pranshul Jain</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -1405,6 +1749,9 @@
           <t>Sid Shaurya</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1412,6 +1759,9 @@
           <t>Parakh Tripathy</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1419,6 +1769,9 @@
           <t>Karan Khanna</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1426,6 +1779,9 @@
           <t>Rajit Das</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1433,6 +1789,9 @@
           <t>Ashwin Jose</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1440,6 +1799,9 @@
           <t>Varun Khurana</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1447,19 +1809,28 @@
           <t>Deepankar Sachdeva</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
-        </is>
+          <t>Satweek Nayak</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
-        </is>
+          <t>Aayush Khanna</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="28">
@@ -1468,6 +1839,9 @@
           <t>Aditya Vaidya</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1475,6 +1849,9 @@
           <t>Danish Javed</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1482,6 +1859,9 @@
           <t>Nilay jain</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1489,12 +1869,18 @@
           <t>Pranav Thomas</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>prateek gupta</t>
         </is>
+      </c>
+      <c r="B32" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1563,18 +1949,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Aquib Razack</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1655,41 +2037,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1700,11 +2074,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1715,11 +2089,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1730,77 +2104,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr"/>
     </row>
@@ -1811,51 +2193,51 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr"/>
     </row>
@@ -1866,7 +2248,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr"/>
     </row>
@@ -1877,7 +2259,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr"/>
     </row>
@@ -1888,7 +2270,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr"/>
     </row>
@@ -1899,7 +2281,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr"/>
     </row>
@@ -1910,7 +2292,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr"/>
     </row>
@@ -1921,7 +2303,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr"/>
     </row>
@@ -1932,29 +2314,29 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C27" t="inlineStr"/>
     </row>
@@ -1965,7 +2347,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C28" t="inlineStr"/>
     </row>
@@ -1976,7 +2358,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
@@ -1987,25 +2369,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2047,7 +2429,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2062,7 +2444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2077,7 +2459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2092,7 +2474,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2155,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2166,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2188,7 +2570,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2199,7 +2581,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2232,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2243,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2331,7 +2713,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2724,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2442,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,6 +2852,321 @@
         <is>
           <t>Own %</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Abhay Rawat</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>De Cuyper</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aparnesh Mishra</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kayode</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Abhiraj Singh</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Naman Agrawal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shivanshu Madan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Abhiraj Singh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rodon</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Abhinav Premsekhar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rodon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Abhinav Premsekhar</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arshaq Razack</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rodon</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Raveesh Kalra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rodon</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Raveesh Kalra</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yash Beohar</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Muharemović</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Karan Chopra</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vuskovic</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Deepankar Sachdeva</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Muharemović</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Deepankar Sachdeva</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wissa</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -2539,30 +3236,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>38561</v>
+        <v>71857</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>858178</v>
+        <v>1929309</v>
       </c>
       <c r="H2" t="n">
-        <v>726260</v>
+        <v>297407</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2576,30 +3273,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>71857</v>
+        <v>38561</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1929309</v>
+        <v>858178</v>
       </c>
       <c r="H3" t="n">
-        <v>297407</v>
+        <v>726260</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2613,30 +3310,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>28582</v>
+        <v>37120</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>881388</v>
+        <v>1571193</v>
       </c>
       <c r="H4" t="n">
-        <v>239490</v>
+        <v>3349378</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2650,30 +3347,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>37120</v>
+        <v>28582</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1571193</v>
+        <v>881388</v>
       </c>
       <c r="H5" t="n">
-        <v>3349378</v>
+        <v>239490</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2835,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H10" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2872,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H11" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2946,19 +3643,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>81907</v>
+        <v>334016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2966,10 +3663,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3252487</v>
+        <v>2156629</v>
       </c>
       <c r="H13" t="n">
-        <v>11118394</v>
+        <v>2691725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2983,19 +3680,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>334016</v>
+        <v>81907</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3003,10 +3700,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2156629</v>
+        <v>3252487</v>
       </c>
       <c r="H14" t="n">
-        <v>2691725</v>
+        <v>11118394</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3094,19 +3791,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3114,10 +3811,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2098988</v>
+        <v>998938</v>
       </c>
       <c r="H17" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3131,19 +3828,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3151,10 +3848,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>998938</v>
+        <v>2098988</v>
       </c>
       <c r="H18" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3427,30 +4124,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>486041</v>
+        <v>14603</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2415786</v>
+        <v>949628</v>
       </c>
       <c r="H26" t="n">
-        <v>1206623</v>
+        <v>515830</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3464,30 +4161,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>14603</v>
+        <v>486041</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>949628</v>
+        <v>2415786</v>
       </c>
       <c r="H27" t="n">
-        <v>515830</v>
+        <v>1206623</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3785,22 +4482,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>74</v>
       </c>
+      <c r="D2" t="n">
+        <v>74</v>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>74</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>74</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -3812,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>100</v>
@@ -3826,27 +4538,46 @@
       <c r="R2" t="n">
         <v>279827</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>74</v>
       </c>
+      <c r="D3" t="n">
+        <v>74</v>
+      </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>74</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>74</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -3858,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
         <v>100</v>
@@ -3872,31 +4603,42 @@
       <c r="R3" t="n">
         <v>279827</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>73</v>
       </c>
+      <c r="D4" t="n">
+        <v>73</v>
+      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="G4" t="n">
+        <v>73</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>73</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -3908,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
         <v>100</v>
@@ -3917,36 +4659,47 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R4" t="n">
         <v>344108</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>73</v>
       </c>
+      <c r="D5" t="n">
+        <v>73</v>
+      </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>73</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -3958,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>100</v>
@@ -3967,12 +4720,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>344108</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3988,11 +4745,26 @@
       <c r="C6" t="n">
         <v>72</v>
       </c>
+      <c r="D6" t="n">
+        <v>72</v>
+      </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>72</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>72</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -4038,11 +4810,26 @@
       <c r="C7" t="n">
         <v>66</v>
       </c>
+      <c r="D7" t="n">
+        <v>66</v>
+      </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>66</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>66</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -4088,11 +4875,26 @@
       <c r="C8" t="n">
         <v>64</v>
       </c>
+      <c r="D8" t="n">
+        <v>64</v>
+      </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>64</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>64</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -4138,11 +4940,26 @@
       <c r="C9" t="n">
         <v>63</v>
       </c>
+      <c r="D9" t="n">
+        <v>63</v>
+      </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>63</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>63</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -4177,22 +4994,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>62</v>
       </c>
+      <c r="D10" t="n">
+        <v>62</v>
+      </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>62</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>62</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -4204,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -4213,32 +5045,51 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1436683</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>62</v>
       </c>
+      <c r="D11" t="n">
+        <v>62</v>
+      </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>62</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -4250,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -4259,16 +5110,12 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
         <v>1436683</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4284,11 +5131,26 @@
       <c r="C12" t="n">
         <v>61</v>
       </c>
+      <c r="D12" t="n">
+        <v>61</v>
+      </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>61</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>61</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -4323,22 +5185,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>59</v>
       </c>
+      <c r="D13" t="n">
+        <v>59</v>
+      </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>59</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -4350,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -4359,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
         <v>1987556</v>
@@ -4369,22 +5246,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>59</v>
       </c>
+      <c r="D14" t="n">
+        <v>59</v>
+      </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>59</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -4396,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -4405,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1987556</v>
@@ -4426,11 +5318,26 @@
       <c r="C15" t="n">
         <v>55</v>
       </c>
+      <c r="D15" t="n">
+        <v>55</v>
+      </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -4472,11 +5379,26 @@
       <c r="C16" t="n">
         <v>53</v>
       </c>
+      <c r="D16" t="n">
+        <v>53</v>
+      </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>53</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>53</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -4507,22 +5429,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>53</v>
       </c>
+      <c r="D17" t="n">
+        <v>53</v>
+      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>53</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>53</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -4534,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -4553,22 +5490,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>53</v>
       </c>
+      <c r="D18" t="n">
+        <v>53</v>
+      </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>53</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>53</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -4580,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -4610,11 +5562,26 @@
       <c r="C19" t="n">
         <v>52</v>
       </c>
+      <c r="D19" t="n">
+        <v>52</v>
+      </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>52</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>52</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -4656,11 +5623,26 @@
       <c r="C20" t="n">
         <v>48</v>
       </c>
+      <c r="D20" t="n">
+        <v>48</v>
+      </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>48</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -4702,11 +5684,26 @@
       <c r="C21" t="n">
         <v>47</v>
       </c>
+      <c r="D21" t="n">
+        <v>47</v>
+      </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>47</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>47</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -4748,11 +5745,26 @@
       <c r="C22" t="n">
         <v>46</v>
       </c>
+      <c r="D22" t="n">
+        <v>46</v>
+      </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>46</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -4798,11 +5810,26 @@
       <c r="C23" t="n">
         <v>45</v>
       </c>
+      <c r="D23" t="n">
+        <v>45</v>
+      </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>45</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>45</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -4844,11 +5871,26 @@
       <c r="C24" t="n">
         <v>44</v>
       </c>
+      <c r="D24" t="n">
+        <v>44</v>
+      </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>44</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>44</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -4890,11 +5932,26 @@
       <c r="C25" t="n">
         <v>43</v>
       </c>
+      <c r="D25" t="n">
+        <v>43</v>
+      </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>43</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>43</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -4925,22 +5982,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>42</v>
       </c>
+      <c r="D26" t="n">
+        <v>42</v>
+      </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>42</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>42</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -4952,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -4961,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>6633922</v>
@@ -4971,22 +6043,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>42</v>
       </c>
+      <c r="D27" t="n">
+        <v>42</v>
+      </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>42</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>42</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -4998,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -5007,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R27" t="n">
         <v>6633922</v>
@@ -5028,11 +6115,26 @@
       <c r="C28" t="n">
         <v>41</v>
       </c>
+      <c r="D28" t="n">
+        <v>41</v>
+      </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>41</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>41</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -5074,11 +6176,26 @@
       <c r="C29" t="n">
         <v>40</v>
       </c>
+      <c r="D29" t="n">
+        <v>40</v>
+      </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>40</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>40</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -5120,11 +6237,26 @@
       <c r="C30" t="n">
         <v>37</v>
       </c>
+      <c r="D30" t="n">
+        <v>37</v>
+      </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>37</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>37</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -5166,11 +6298,26 @@
       <c r="C31" t="n">
         <v>35</v>
       </c>
+      <c r="D31" t="n">
+        <v>35</v>
+      </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>35</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>35</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -5212,11 +6359,26 @@
       <c r="C32" t="n">
         <v>29</v>
       </c>
+      <c r="D32" t="n">
+        <v>29</v>
+      </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>29</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>29</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,12 +475,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -499,12 +499,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1382,7 +1382,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1406,7 +1406,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1576,7 +1576,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1726,7 +1726,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1736,7 +1736,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1816,7 +1816,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1826,7 +1826,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2074,7 +2074,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2089,7 +2089,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2321,7 +2321,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2332,7 +2332,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2429,7 +2429,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2444,7 +2444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2713,7 +2713,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2724,7 +2724,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3236,30 +3236,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>71857</v>
+        <v>38561</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1929309</v>
+        <v>858178</v>
       </c>
       <c r="H2" t="n">
-        <v>297407</v>
+        <v>726260</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3273,30 +3273,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>38561</v>
+        <v>71857</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>858178</v>
+        <v>1929309</v>
       </c>
       <c r="H3" t="n">
-        <v>726260</v>
+        <v>297407</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3791,19 +3791,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>998938</v>
+        <v>2098988</v>
       </c>
       <c r="H17" t="n">
-        <v>676529</v>
+        <v>182900</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3828,19 +3828,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2098988</v>
+        <v>998938</v>
       </c>
       <c r="H18" t="n">
-        <v>182900</v>
+        <v>676529</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4124,30 +4124,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>14603</v>
+        <v>486041</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>949628</v>
+        <v>2415786</v>
       </c>
       <c r="H26" t="n">
-        <v>515830</v>
+        <v>1206623</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4161,30 +4161,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>486041</v>
+        <v>14603</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2415786</v>
+        <v>949628</v>
       </c>
       <c r="H27" t="n">
-        <v>1206623</v>
+        <v>515830</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4482,12 +4482,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
         <v>100</v>
@@ -4538,21 +4538,17 @@
       <c r="R2" t="n">
         <v>279827</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4589,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>100</v>
@@ -4603,7 +4599,11 @@
       <c r="R3" t="n">
         <v>279827</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5429,12 +5429,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>53</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -5490,12 +5490,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
         <v>53</v>
@@ -5532,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -5982,12 +5982,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R26" t="n">
         <v>6633922</v>
@@ -6043,12 +6043,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6085,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>6633922</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1656,7 +1656,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1666,7 +1666,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1716,7 +1716,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1726,7 +1726,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2222,7 +2222,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2233,7 +2233,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2537,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2548,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2603,7 +2603,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -3532,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H10" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3569,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H11" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3754,34 +3754,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>1320699</v>
+        <v>182900</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2490743</v>
+        <v>2098988</v>
       </c>
       <c r="H16" t="n">
-        <v>1861933</v>
+        <v>182900</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3791,34 +3791,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>182900</v>
+        <v>1320699</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2098988</v>
+        <v>2490743</v>
       </c>
       <c r="H17" t="n">
-        <v>182900</v>
+        <v>1861933</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5012,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
         <v>62</v>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -5045,26 +5045,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
         <v>1436683</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5077,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>62</v>
@@ -5101,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -5110,12 +5106,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>1436683</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5368,12 +5368,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5410,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>100</v>
@@ -5429,12 +5429,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -547,12 +547,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,12 +691,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,12 +859,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1382,7 +1382,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1406,7 +1406,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1596,7 +1596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1606,7 +1606,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1656,7 +1656,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1666,7 +1666,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1726,7 +1726,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1736,7 +1736,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1816,7 +1816,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1826,7 +1826,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2321,7 +2321,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2332,7 +2332,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2459,7 +2459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2474,7 +2474,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2537,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2548,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2713,7 +2713,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2724,7 +2724,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3310,30 +3310,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>37120</v>
+        <v>28582</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1571193</v>
+        <v>881388</v>
       </c>
       <c r="H4" t="n">
-        <v>3349378</v>
+        <v>239490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3347,30 +3347,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>28582</v>
+        <v>37120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>881388</v>
+        <v>1571193</v>
       </c>
       <c r="H5" t="n">
-        <v>239490</v>
+        <v>3349378</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3532,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>31543</v>
+        <v>281617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>820692</v>
+        <v>1051323</v>
       </c>
       <c r="H10" t="n">
-        <v>1637750</v>
+        <v>1076546</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3569,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>281617</v>
+        <v>31543</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1051323</v>
+        <v>820692</v>
       </c>
       <c r="H11" t="n">
-        <v>1076546</v>
+        <v>1637750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3791,34 +3791,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>1320699</v>
+        <v>676529</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2490743</v>
+        <v>998938</v>
       </c>
       <c r="H17" t="n">
-        <v>1861933</v>
+        <v>676529</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3828,34 +3828,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>676529</v>
+        <v>1320699</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>998938</v>
+        <v>2490743</v>
       </c>
       <c r="H18" t="n">
-        <v>676529</v>
+        <v>1861933</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -4124,30 +4124,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>486041</v>
+        <v>14603</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2415786</v>
+        <v>949628</v>
       </c>
       <c r="H26" t="n">
-        <v>1206623</v>
+        <v>515830</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4161,30 +4161,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>14603</v>
+        <v>486041</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>949628</v>
+        <v>2415786</v>
       </c>
       <c r="H27" t="n">
-        <v>515830</v>
+        <v>1206623</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4626,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>73</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>100</v>
@@ -4659,22 +4659,26 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>344108</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4687,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
         <v>73</v>
@@ -4711,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>100</v>
@@ -4720,16 +4724,12 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R5" t="n">
         <v>344108</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4994,12 +4994,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5012,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>62</v>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
@@ -5045,22 +5045,26 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1436683</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5073,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
         <v>62</v>
@@ -5097,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
@@ -5106,16 +5110,12 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
         <v>1436683</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5429,12 +5429,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>53</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
@@ -5490,12 +5490,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>53</v>
@@ -5532,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>100</v>
@@ -5982,12 +5982,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>100</v>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>6633922</v>
@@ -6043,12 +6043,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6085,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R27" t="n">
         <v>6633922</v>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,46 +475,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -523,46 +523,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -595,22 +595,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -619,22 +619,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -643,22 +643,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -691,46 +691,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -739,46 +739,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -787,22 +787,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -811,70 +811,70 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -883,22 +883,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -907,22 +907,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -931,46 +931,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
@@ -979,22 +979,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
@@ -1051,46 +1051,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -1099,46 +1099,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
@@ -1195,22 +1195,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1576,41 +1576,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -1626,261 +1626,261 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2065,16 +2065,12 @@
       <c r="B4" t="n">
         <v>16</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2089,7 +2085,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2104,7 +2100,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2119,7 +2115,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2134,18 +2130,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2156,7 +2156,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2167,7 +2167,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2178,7 +2178,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2189,7 +2189,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2200,7 +2200,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2211,7 +2211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2222,7 +2222,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2233,7 +2233,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2244,7 +2244,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2255,7 +2255,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2266,7 +2266,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2277,7 +2277,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2288,7 +2288,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2299,7 +2299,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2310,7 +2310,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2321,7 +2321,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2332,7 +2332,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2354,7 +2354,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2365,7 +2365,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2429,7 +2429,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2444,7 +2444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2459,7 +2459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2474,7 +2474,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2504,7 +2504,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2515,7 +2515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2526,7 +2526,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2537,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2548,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2559,7 +2559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2570,7 +2570,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2581,7 +2581,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2592,7 +2592,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2603,7 +2603,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2636,7 +2636,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2647,7 +2647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2658,7 +2658,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2669,7 +2669,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2680,7 +2680,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2691,7 +2691,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2702,7 +2702,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2713,7 +2713,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2724,7 +2724,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2735,7 +2735,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2746,7 +2746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2757,7 +2757,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2768,7 +2768,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2779,7 +2779,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2920,7 +2920,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2962,12 +2962,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rodon</t>
+          <t>Vuskovic</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2977,13 +2977,13 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gomez</t>
+          <t>Rodon</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3019,18 +3019,18 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rodon</t>
+          <t>Gomez</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3040,13 +3040,13 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gomez</t>
+          <t>Rodon</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3082,18 +3082,18 @@
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Muharemović</t>
+          <t>Gomez</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3103,18 +3103,18 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vuskovic</t>
+          <t>Muharemović</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3124,13 +3124,13 @@
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3236,30 +3236,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>38561</v>
+        <v>81907</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>858178</v>
+        <v>3252487</v>
       </c>
       <c r="H2" t="n">
-        <v>726260</v>
+        <v>11118394</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3269,34 +3269,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>71857</v>
+        <v>281617</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1929309</v>
+        <v>1051323</v>
       </c>
       <c r="H3" t="n">
-        <v>297407</v>
+        <v>1076546</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3310,30 +3310,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>28582</v>
+        <v>545267</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>881388</v>
+        <v>604934</v>
       </c>
       <c r="H4" t="n">
-        <v>239490</v>
+        <v>545267</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3343,34 +3343,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>37120</v>
+        <v>6474</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1571193</v>
+        <v>1177681</v>
       </c>
       <c r="H5" t="n">
-        <v>3349378</v>
+        <v>6474</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3421,30 +3421,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>15136</v>
+        <v>334016</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>983840</v>
+        <v>2156629</v>
       </c>
       <c r="H7" t="n">
-        <v>45077</v>
+        <v>2691725</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3458,34 +3458,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>6474</v>
+        <v>1320699</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1177681</v>
+        <v>2490743</v>
       </c>
       <c r="H8" t="n">
-        <v>6474</v>
+        <v>1861933</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
     </row>
@@ -3495,19 +3495,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>8917</v>
+        <v>28582</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2118382</v>
+        <v>881388</v>
       </c>
       <c r="H9" t="n">
-        <v>9146930</v>
+        <v>239490</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3532,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>281617</v>
+        <v>8917</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1051323</v>
+        <v>2118382</v>
       </c>
       <c r="H10" t="n">
-        <v>1076546</v>
+        <v>9146930</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3569,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>31543</v>
+        <v>95791</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>820692</v>
+        <v>2404119</v>
       </c>
       <c r="H11" t="n">
-        <v>1637750</v>
+        <v>5124417</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3602,34 +3602,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>30971</v>
+        <v>71857</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>820221</v>
+        <v>1929309</v>
       </c>
       <c r="H12" t="n">
-        <v>58227</v>
+        <v>297407</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3643,30 +3643,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>334016</v>
+        <v>31543</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2156629</v>
+        <v>820692</v>
       </c>
       <c r="H13" t="n">
-        <v>2691725</v>
+        <v>1637750</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3676,34 +3676,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>81907</v>
+        <v>1615102</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3252487</v>
+        <v>4234674</v>
       </c>
       <c r="H14" t="n">
-        <v>11118394</v>
+        <v>6092784</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3717,19 +3717,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>604934</v>
+        <v>3434302</v>
       </c>
       <c r="H15" t="n">
-        <v>545267</v>
+        <v>1128645</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3754,30 +3754,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>182900</v>
+        <v>38561</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2098988</v>
+        <v>858178</v>
       </c>
       <c r="H16" t="n">
-        <v>182900</v>
+        <v>726260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3787,34 +3787,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>676529</v>
+        <v>14603</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>998938</v>
+        <v>949628</v>
       </c>
       <c r="H17" t="n">
-        <v>676529</v>
+        <v>515830</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3824,38 +3824,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>1320699</v>
+        <v>37120</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2490743</v>
+        <v>1571193</v>
       </c>
       <c r="H18" t="n">
-        <v>1861933</v>
+        <v>3349378</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
     </row>
@@ -3865,30 +3865,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>189374</v>
+        <v>15288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1757289</v>
+        <v>329510</v>
       </c>
       <c r="H19" t="n">
-        <v>250879</v>
+        <v>538046</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3902,30 +3902,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>60517</v>
+        <v>15136</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2015/16</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1414622</v>
+        <v>983840</v>
       </c>
       <c r="H20" t="n">
-        <v>339763</v>
+        <v>45077</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3939,30 +3939,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>453230</v>
+        <v>182900</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5483351</v>
+        <v>2098988</v>
       </c>
       <c r="H21" t="n">
-        <v>8188106</v>
+        <v>182900</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3972,34 +3972,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>1615102</v>
+        <v>30971</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4234674</v>
+        <v>820221</v>
       </c>
       <c r="H22" t="n">
-        <v>6092784</v>
+        <v>58227</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4013,30 +4013,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>95791</v>
+        <v>189374</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2404119</v>
+        <v>1757289</v>
       </c>
       <c r="H23" t="n">
-        <v>5124417</v>
+        <v>250879</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -4050,30 +4050,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>410102</v>
+        <v>453230</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2009/10</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2088802</v>
+        <v>5483351</v>
       </c>
       <c r="H24" t="n">
-        <v>5360778</v>
+        <v>8188106</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4087,30 +4087,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>1128645</v>
+        <v>60517</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3434302</v>
+        <v>1414622</v>
       </c>
       <c r="H25" t="n">
-        <v>1128645</v>
+        <v>339763</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4124,30 +4124,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>14603</v>
+        <v>676529</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>949628</v>
+        <v>998938</v>
       </c>
       <c r="H26" t="n">
-        <v>515830</v>
+        <v>676529</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4157,34 +4157,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>486041</v>
+        <v>410102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2009/10</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2415786</v>
+        <v>2088802</v>
       </c>
       <c r="H27" t="n">
-        <v>1206623</v>
+        <v>5360778</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4198,30 +4198,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>15288</v>
+        <v>4884220</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>329510</v>
+        <v>4884220</v>
       </c>
       <c r="H28" t="n">
-        <v>538046</v>
+        <v>4884220</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4231,23 +4231,23 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>273503</v>
+        <v>486041</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1994005</v>
+        <v>2415786</v>
       </c>
       <c r="H29" t="n">
-        <v>1917309</v>
+        <v>1206623</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4272,30 +4272,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>4884220</v>
+        <v>273503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4884220</v>
+        <v>1994005</v>
       </c>
       <c r="H30" t="n">
-        <v>4884220</v>
+        <v>1917309</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4309,16 +4309,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>117338</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>4684930</v>
+      </c>
+      <c r="H31" t="n">
+        <v>117338</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -4327,35 +4346,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" t="n">
-        <v>117338</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>4684930</v>
-      </c>
-      <c r="H32" t="n">
-        <v>117338</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4482,19 +4482,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -4503,13 +4503,13 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -4524,38 +4524,38 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>279827</v>
+        <v>1987556</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -4564,19 +4564,19 @@
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -4588,16 +4588,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R3" t="n">
-        <v>279827</v>
+        <v>1436683</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4608,19 +4608,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhiraj Singh</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KingOfKings Fc</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -4629,13 +4629,13 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -4650,57 +4650,53 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>344108</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>2935782</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Arshaq Razack</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>ShakeNBake</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -4715,21 +4711,25 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>344108</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>1142767</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D6" t="n">
         <v>72</v>
@@ -4779,10 +4779,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -4799,19 +4799,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naman Agrawal</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Captn Magnifico</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -4820,19 +4820,19 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -4841,63 +4841,59 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>893714</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>1987556</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arshaq Razack</t>
+          <t>Rohan Agrawal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ShakeNBake</t>
+          <t>Southall United</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D8" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4906,42 +4902,38 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1142767</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>3482299</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Abhiraj Singh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>KingOfKings Fc</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4950,13 +4942,13 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -4974,16 +4966,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1282717</v>
+        <v>344108</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4994,19 +4986,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -5015,13 +5007,13 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -5039,16 +5031,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1436683</v>
+        <v>1282717</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -5059,34 +5051,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivanshu Madan</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cold Palmer</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -5101,38 +5093,38 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1436683</v>
+        <v>5859109</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -5141,13 +5133,13 @@
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -5165,16 +5157,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1605173</v>
+        <v>279827</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -5185,34 +5177,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Shivanshu Madan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Cold Palmer</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -5227,59 +5219,59 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1987556</v>
+        <v>1436683</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -5288,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
@@ -5297,111 +5289,115 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1987556</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
+        <v>5572584</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2935782</v>
+        <v>6382778</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -5410,53 +5406,57 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3482299</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
+        <v>279827</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dean Jenkins</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Slumber FC</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -5471,53 +5471,53 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3482299</v>
+        <v>6633922</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rohan Agrawal</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southall United</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -5532,38 +5532,42 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>3482299</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
+        <v>344108</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sid Shaurya</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Old Reijnders Nagar</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -5572,13 +5576,13 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -5593,53 +5597,53 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3770910</v>
+        <v>6875541</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parakh Tripathy</t>
+          <t>Naman Agrawal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Malisahi Randuas</t>
+          <t>Captn Magnifico</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -5654,38 +5658,42 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4969899</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
+        <v>893714</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karan Khanna</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amad Aura</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -5694,13 +5702,13 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -5715,53 +5723,53 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5282775</v>
+        <v>3482299</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -5779,16 +5787,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5572584</v>
+        <v>1605173</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -5799,19 +5807,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Sid Shaurya</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>Old Reijnders Nagar</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -5820,13 +5828,13 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -5841,38 +5849,38 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O23" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5859109</v>
+        <v>3770910</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Varun Khurana</t>
+          <t>Karan Khanna</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Goal Diggers FC</t>
+          <t>Amad Aura</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -5881,19 +5889,19 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5902,38 +5910,38 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6124832</v>
+        <v>5282775</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Parakh Tripathy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>Malisahi Randuas</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -5942,13 +5950,13 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -5963,59 +5971,59 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O25" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>6382778</v>
+        <v>4969899</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Dean Jenkins</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Slumber FC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6024,38 +6032,38 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O26" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>6633922</v>
+        <v>3482299</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Varun Khurana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Goal Diggers FC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -6064,19 +6072,19 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -6088,35 +6096,35 @@
         <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>6633922</v>
+        <v>6124832</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -6125,13 +6133,13 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -6146,38 +6154,42 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R28" t="n">
-        <v>6875541</v>
-      </c>
-      <c r="U28" t="inlineStr"/>
+        <v>7658231</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>wildcard</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Danish Javed</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ItDzntMata</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -6186,13 +6198,13 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -6207,38 +6219,38 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>7094513</v>
+        <v>6633922</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Danish Javed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>ItDzntMata</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -6247,13 +6259,13 @@
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -6268,53 +6280,53 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O30" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7658231</v>
+        <v>7094513</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -6329,59 +6341,59 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>7960655</v>
+        <v>8566706</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6390,19 +6402,19 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R32" t="n">
-        <v>8566706</v>
+        <v>7960655</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -835,16 +835,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -859,16 +859,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1726,21 +1726,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>14603</v>
+        <v>37120</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>949628</v>
+        <v>1571193</v>
       </c>
       <c r="H17" t="n">
-        <v>515830</v>
+        <v>3349378</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3828,30 +3828,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>37120</v>
+        <v>14603</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1571193</v>
+        <v>949628</v>
       </c>
       <c r="H18" t="n">
-        <v>3349378</v>
+        <v>515830</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5429,34 +5429,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -5471,53 +5471,57 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R17" t="n">
-        <v>6633922</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
+        <v>344108</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -5532,25 +5536,21 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>344108</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>6633922</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -835,16 +835,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -859,16 +859,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -931,16 +931,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -955,16 +955,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1099,16 +1099,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1123,16 +1123,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1726,21 +1726,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -1766,21 +1766,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -1836,21 +1836,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2288,7 +2288,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2354,7 +2354,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2658,7 +2658,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2669,7 +2669,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2735,7 +2735,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2746,7 +2746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>37120</v>
+        <v>14603</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1571193</v>
+        <v>949628</v>
       </c>
       <c r="H17" t="n">
-        <v>3349378</v>
+        <v>515830</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3828,30 +3828,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>14603</v>
+        <v>37120</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>949628</v>
+        <v>1571193</v>
       </c>
       <c r="H18" t="n">
-        <v>515830</v>
+        <v>3349378</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3939,30 +3939,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>182900</v>
+        <v>30971</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2098988</v>
+        <v>820221</v>
       </c>
       <c r="H21" t="n">
-        <v>182900</v>
+        <v>58227</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3976,30 +3976,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>30971</v>
+        <v>182900</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>820221</v>
+        <v>2098988</v>
       </c>
       <c r="H22" t="n">
-        <v>58227</v>
+        <v>182900</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4198,30 +4198,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>4884220</v>
+        <v>486041</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4884220</v>
+        <v>2415786</v>
       </c>
       <c r="H28" t="n">
-        <v>4884220</v>
+        <v>1206623</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4235,30 +4235,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>486041</v>
+        <v>4884220</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2415786</v>
+        <v>4884220</v>
       </c>
       <c r="H29" t="n">
-        <v>1206623</v>
+        <v>4884220</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1987556</v>
+        <v>398774</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
@@ -4597,7 +4597,7 @@
         <v>0.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1436683</v>
+        <v>559579</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2935782</v>
+        <v>662331</v>
       </c>
       <c r="U4" t="inlineStr"/>
     </row>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1142767</v>
+        <v>746790</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>398656</v>
+        <v>1306061</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1987556</v>
+        <v>1389433</v>
       </c>
       <c r="U7" t="inlineStr"/>
     </row>
@@ -4914,7 +4914,7 @@
         <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>3482299</v>
+        <v>1531813</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>344108</v>
+        <v>2077717</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1282717</v>
+        <v>2839056</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5859109</v>
+        <v>2839056</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
@@ -5166,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>279827</v>
+        <v>2839056</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1436683</v>
+        <v>3038518</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
@@ -5292,7 +5292,7 @@
         <v>0.8</v>
       </c>
       <c r="R14" t="n">
-        <v>5572584</v>
+        <v>3161599</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>6382778</v>
+        <v>3227024</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
@@ -5418,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>279827</v>
+        <v>3374969</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -5429,34 +5429,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -5471,57 +5471,53 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>344108</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>3459630</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -5536,21 +5532,25 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>6633922</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
+        <v>3459630</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5609,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6875541</v>
+        <v>3677588</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
@@ -5670,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>893714</v>
+        <v>3894324</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -5681,34 +5681,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>66</v>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -5723,53 +5723,57 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3482299</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+        <v>4978807</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>66</v>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -5784,25 +5788,21 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1605173</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>4978807</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3770910</v>
+        <v>5189215</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
@@ -5922,7 +5922,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5282775</v>
+        <v>5318033</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4969899</v>
+        <v>5995197</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
@@ -6044,7 +6044,7 @@
         <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>3482299</v>
+        <v>6292985</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
@@ -6105,26 +6105,26 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>6124832</v>
+        <v>6798096</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -6133,13 +6133,13 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -6154,42 +6154,38 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R28" t="n">
-        <v>7658231</v>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>wildcard</t>
-        </is>
-      </c>
+        <v>7021567</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>55</v>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -6198,13 +6194,13 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -6219,21 +6215,25 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="P29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q29" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0.5</v>
-      </c>
       <c r="R29" t="n">
-        <v>6633922</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
+        <v>7021567</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>wildcard</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6292,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7094513</v>
+        <v>7301770</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
@@ -6353,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>8566706</v>
+        <v>7958871</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -6414,7 +6414,7 @@
         <v>0.3</v>
       </c>
       <c r="R32" t="n">
-        <v>7960655</v>
+        <v>8003049</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,16 +667,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -691,16 +691,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -715,16 +715,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1099,16 +1099,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1123,16 +1123,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1656,31 +1656,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -1836,21 +1836,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
@@ -2178,7 +2178,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2189,7 +2189,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2200,7 +2200,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2354,7 +2354,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2537,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2548,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2559,7 +2559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2735,7 +2735,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2746,7 +2746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3532,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>8917</v>
+        <v>71857</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2118382</v>
+        <v>1929309</v>
       </c>
       <c r="H10" t="n">
-        <v>9146930</v>
+        <v>297407</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3569,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>95791</v>
+        <v>8917</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2404119</v>
+        <v>2118382</v>
       </c>
       <c r="H11" t="n">
-        <v>5124417</v>
+        <v>9146930</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3606,30 +3606,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H12" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4198,30 +4198,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>486041</v>
+        <v>4884220</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2415786</v>
+        <v>4884220</v>
       </c>
       <c r="H28" t="n">
-        <v>1206623</v>
+        <v>4884220</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4235,30 +4235,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>4884220</v>
+        <v>486041</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4884220</v>
+        <v>2415786</v>
       </c>
       <c r="H29" t="n">
-        <v>4884220</v>
+        <v>1206623</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4986,19 +4986,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>76</v>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -5007,13 +5007,13 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -5051,34 +5051,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100.2</v>
@@ -5107,39 +5107,43 @@
       <c r="R11" t="n">
         <v>2839056</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -5154,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
         <v>100.2</v>
@@ -5168,11 +5172,7 @@
       <c r="R12" t="n">
         <v>2839056</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6112,19 +6112,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -6133,13 +6133,13 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -6154,38 +6154,42 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="P28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q28" t="n">
         <v>0.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.5</v>
       </c>
       <c r="R28" t="n">
         <v>7021567</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>wildcard</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>55</v>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -6194,13 +6198,13 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -6215,25 +6219,21 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R29" t="n">
         <v>7021567</v>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>wildcard</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,16 +667,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -691,16 +691,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -715,16 +715,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1099,16 +1099,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1123,16 +1123,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1656,31 +1656,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -1836,21 +1836,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
@@ -2178,7 +2178,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2189,7 +2189,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2200,7 +2200,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2354,7 +2354,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2537,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2548,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2559,7 +2559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2735,7 +2735,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2746,7 +2746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3532,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H10" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3569,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>8917</v>
+        <v>71857</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2118382</v>
+        <v>1929309</v>
       </c>
       <c r="H11" t="n">
-        <v>9146930</v>
+        <v>297407</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3606,30 +3606,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>95791</v>
+        <v>8917</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2404119</v>
+        <v>2118382</v>
       </c>
       <c r="H12" t="n">
-        <v>5124417</v>
+        <v>9146930</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4198,30 +4198,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>4884220</v>
+        <v>486041</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4884220</v>
+        <v>2415786</v>
       </c>
       <c r="H28" t="n">
-        <v>4884220</v>
+        <v>1206623</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4235,30 +4235,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>486041</v>
+        <v>4884220</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2415786</v>
+        <v>4884220</v>
       </c>
       <c r="H29" t="n">
-        <v>1206623</v>
+        <v>4884220</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4986,34 +4986,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>76</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
         <v>100.2</v>
@@ -5042,28 +5042,24 @@
       <c r="R10" t="n">
         <v>2839056</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -5072,13 +5068,13 @@
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -5116,34 +5112,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -5158,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>100.2</v>
@@ -5172,7 +5168,11 @@
       <c r="R12" t="n">
         <v>2839056</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6112,19 +6112,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -6133,13 +6133,13 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -6154,42 +6154,38 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R28" t="n">
         <v>7021567</v>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>wildcard</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>55</v>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -6198,13 +6194,13 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -6219,21 +6215,25 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="P29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q29" t="n">
         <v>0.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.5</v>
       </c>
       <c r="R29" t="n">
         <v>7021567</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>wildcard</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -931,16 +931,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -955,16 +955,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1766,21 +1766,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -2277,7 +2277,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2288,7 +2288,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2658,7 +2658,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2669,7 +2669,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3939,30 +3939,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>30971</v>
+        <v>182900</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>820221</v>
+        <v>2098988</v>
       </c>
       <c r="H21" t="n">
-        <v>58227</v>
+        <v>182900</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3976,30 +3976,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>182900</v>
+        <v>30971</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2098988</v>
+        <v>820221</v>
       </c>
       <c r="H22" t="n">
-        <v>182900</v>
+        <v>58227</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -5681,34 +5681,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>66</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -5723,13 +5723,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -5737,43 +5737,39 @@
       <c r="R21" t="n">
         <v>4978807</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>66</v>
       </c>
       <c r="D22" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -5788,13 +5784,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -5802,7 +5798,11 @@
       <c r="R22" t="n">
         <v>4978807</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,16 +667,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -691,16 +691,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -715,16 +715,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -835,16 +835,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -859,16 +859,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -931,16 +931,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -955,16 +955,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1099,16 +1099,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1123,16 +1123,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1656,31 +1656,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -1726,21 +1726,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -1766,21 +1766,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -1836,21 +1836,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
@@ -2178,7 +2178,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2189,7 +2189,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2200,7 +2200,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2277,7 +2277,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2288,7 +2288,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2354,7 +2354,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2537,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2548,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2559,7 +2559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2658,7 +2658,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2669,7 +2669,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2735,7 +2735,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2746,7 +2746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3532,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>95791</v>
+        <v>8917</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2404119</v>
+        <v>2118382</v>
       </c>
       <c r="H10" t="n">
-        <v>5124417</v>
+        <v>9146930</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3569,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H11" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3606,30 +3606,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>8917</v>
+        <v>71857</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2118382</v>
+        <v>1929309</v>
       </c>
       <c r="H12" t="n">
-        <v>9146930</v>
+        <v>297407</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3791,30 +3791,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>14603</v>
+        <v>37120</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>949628</v>
+        <v>1571193</v>
       </c>
       <c r="H17" t="n">
-        <v>515830</v>
+        <v>3349378</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3828,30 +3828,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>37120</v>
+        <v>14603</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1571193</v>
+        <v>949628</v>
       </c>
       <c r="H18" t="n">
-        <v>3349378</v>
+        <v>515830</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3939,30 +3939,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>182900</v>
+        <v>30971</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2098988</v>
+        <v>820221</v>
       </c>
       <c r="H21" t="n">
-        <v>182900</v>
+        <v>58227</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3976,30 +3976,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>30971</v>
+        <v>182900</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>820221</v>
+        <v>2098988</v>
       </c>
       <c r="H22" t="n">
-        <v>58227</v>
+        <v>182900</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4198,30 +4198,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>486041</v>
+        <v>4884220</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2415786</v>
+        <v>4884220</v>
       </c>
       <c r="H28" t="n">
-        <v>1206623</v>
+        <v>4884220</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4235,30 +4235,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>4884220</v>
+        <v>486041</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4884220</v>
+        <v>2415786</v>
       </c>
       <c r="H29" t="n">
-        <v>4884220</v>
+        <v>1206623</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4986,34 +4986,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>76</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>100.2</v>
@@ -5042,39 +5042,43 @@
       <c r="R10" t="n">
         <v>2839056</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -5089,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
         <v>100.2</v>
@@ -5103,28 +5107,24 @@
       <c r="R11" t="n">
         <v>2839056</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -5133,13 +5133,13 @@
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -5429,34 +5429,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -5471,53 +5471,57 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R17" t="n">
         <v>3459630</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -5532,25 +5536,21 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>3459630</v>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5681,34 +5681,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pranshul Jain</t>
+          <t>Yash Beohar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carrick Janta Party</t>
+          <t>Fluente in Football</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>66</v>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -5723,13 +5723,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -5737,39 +5737,43 @@
       <c r="R21" t="n">
         <v>4978807</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yash Beohar</t>
+          <t>Pranshul Jain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fluente in Football</t>
+          <t>Carrick Janta Party</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>66</v>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -5784,13 +5788,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -5798,11 +5802,7 @@
       <c r="R22" t="n">
         <v>4978807</v>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6112,19 +6112,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aayush Khanna</t>
+          <t>Nilay jain</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Redsbay</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -6133,13 +6133,13 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -6154,38 +6154,42 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="P28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q28" t="n">
         <v>0.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.5</v>
       </c>
       <c r="R28" t="n">
         <v>7021567</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>wildcard</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nilay jain</t>
+          <t>Aayush Khanna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Redsbay</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>55</v>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -6194,13 +6198,13 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -6215,25 +6219,21 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R29" t="n">
         <v>7021567</v>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>wildcard</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -667,16 +667,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -691,16 +691,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -715,16 +715,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -835,16 +835,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -859,16 +859,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1656,31 +1656,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -1726,21 +1726,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -2178,7 +2178,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2189,7 +2189,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2200,7 +2200,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2537,7 +2537,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2548,7 +2548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2559,7 +2559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3532,30 +3532,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>8917</v>
+        <v>71857</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2118382</v>
+        <v>1929309</v>
       </c>
       <c r="H10" t="n">
-        <v>9146930</v>
+        <v>297407</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3569,30 +3569,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>95791</v>
+        <v>8917</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2021/22</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2404119</v>
+        <v>2118382</v>
       </c>
       <c r="H11" t="n">
-        <v>5124417</v>
+        <v>9146930</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3606,30 +3606,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>71857</v>
+        <v>95791</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1929309</v>
+        <v>2404119</v>
       </c>
       <c r="H12" t="n">
-        <v>297407</v>
+        <v>5124417</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3791,30 +3791,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>37120</v>
+        <v>14603</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1571193</v>
+        <v>949628</v>
       </c>
       <c r="H17" t="n">
-        <v>3349378</v>
+        <v>515830</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3828,30 +3828,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>14603</v>
+        <v>37120</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>949628</v>
+        <v>1571193</v>
       </c>
       <c r="H18" t="n">
-        <v>515830</v>
+        <v>3349378</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4986,19 +4986,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raveesh Kalra</t>
+          <t>Aquib Razack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MaSalah</t>
+          <t>BattleBorn</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>76</v>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -5007,13 +5007,13 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -5051,34 +5051,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwin Jose</t>
+          <t>Raveesh Kalra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pole Calmer �</t>
+          <t>MaSalah</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>100.2</v>
@@ -5107,39 +5107,43 @@
       <c r="R11" t="n">
         <v>2839056</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aquib Razack</t>
+          <t>Ashwin Jose</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BattleBorn</t>
+          <t>Pole Calmer �</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -5154,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
         <v>100.2</v>
@@ -5168,11 +5172,7 @@
       <c r="R12" t="n">
         <v>2839056</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5429,34 +5429,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -5471,57 +5471,53 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>3459630</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -5536,21 +5532,25 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="n">
         <v>3459630</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/docs/Laxmi_Chit_Fund_S5_audit.xlsx
+++ b/docs/Laxmi_Chit_Fund_S5_audit.xlsx
@@ -475,22 +475,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
@@ -499,22 +499,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
@@ -523,22 +523,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
@@ -556,13 +556,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -595,16 +595,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -700,18 +700,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -763,22 +763,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -787,19 +787,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>75</v>
@@ -807,26 +807,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -835,46 +835,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
@@ -883,22 +883,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -916,13 +916,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24">
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26">
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -1195,22 +1195,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1576,31 +1576,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1616,21 +1616,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -1696,61 +1696,61 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -1866,21 +1866,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2070,7 +2070,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2085,7 +2085,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2100,7 +2100,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2130,7 +2130,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2145,7 +2145,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2211,7 +2211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2222,7 +2222,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2233,7 +2233,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2244,7 +2244,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2255,7 +2255,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2429,7 +2429,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2444,7 +2444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2459,7 +2459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2489,7 +2489,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2504,7 +2504,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2581,7 +2581,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2592,7 +2592,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2603,7 +2603,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2614,7 +2614,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2636,7 +2636,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2768,7 +2768,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2779,7 +2779,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -3236,30 +3236,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>81907</v>
+        <v>545267</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3252487</v>
+        <v>604934</v>
       </c>
       <c r="H2" t="n">
-        <v>11118394</v>
+        <v>545267</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3273,30 +3273,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>281617</v>
+        <v>81907</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1051323</v>
+        <v>3252487</v>
       </c>
       <c r="H3" t="n">
-        <v>1076546</v>
+        <v>11118394</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3310,30 +3310,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>545267</v>
+        <v>281617</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>604934</v>
+        <v>1051323</v>
       </c>
       <c r="H4" t="n">
-        <v>545267</v>
+        <v>1076546</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3384,30 +3384,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abhinav Premsekhar</t>
+          <t>Aparnesh Mishra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Totally Szobo</t>
+          <t>Mishra's 13</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>27153</v>
+        <v>334016</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>606381</v>
+        <v>2156629</v>
       </c>
       <c r="H6" t="n">
-        <v>240451</v>
+        <v>2691725</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3421,30 +3421,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aparnesh Mishra</t>
+          <t>Abhinav Premsekhar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mishra's 13</t>
+          <t>Totally Szobo</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>334016</v>
+        <v>27153</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2022/23</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2156629</v>
+        <v>606381</v>
       </c>
       <c r="H7" t="n">
-        <v>2691725</v>
+        <v>240451</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -3680,30 +3680,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajit Das</t>
+          <t>Abhay Rawat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FC Teetotallers</t>
+          <t>115 FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>1615102</v>
+        <v>38561</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4234674</v>
+        <v>858178</v>
       </c>
       <c r="H14" t="n">
-        <v>6092784</v>
+        <v>726260</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3717,30 +3717,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deepankar Sachdeva</t>
+          <t>Aditya Vaidya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cment_mixers</t>
+          <t>His Name is Diogo</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>1128645</v>
+        <v>15288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3434302</v>
+        <v>329510</v>
       </c>
       <c r="H15" t="n">
-        <v>1128645</v>
+        <v>538046</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3750,34 +3750,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhay Rawat</t>
+          <t>Abhishek Gupte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115 FC</t>
+          <t>Enzotic</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>38561</v>
+        <v>37120</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>858178</v>
+        <v>1571193</v>
       </c>
       <c r="H16" t="n">
-        <v>726260</v>
+        <v>3349378</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3791,30 +3791,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Satweek Nayak</t>
+          <t>Rajit Das</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xa bing chilling</t>
+          <t>FC Teetotallers</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>14603</v>
+        <v>1615102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>949628</v>
+        <v>4234674</v>
       </c>
       <c r="H17" t="n">
-        <v>515830</v>
+        <v>6092784</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3824,34 +3824,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Gupte</t>
+          <t>Deepankar Sachdeva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enzotic</t>
+          <t>Cment_mixers</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>37120</v>
+        <v>1128645</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2014/15</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1571193</v>
+        <v>3434302</v>
       </c>
       <c r="H18" t="n">
-        <v>3349378</v>
+        <v>1128645</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3865,30 +3865,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aditya Vaidya</t>
+          <t>Satweek Nayak</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>His Name is Diogo</t>
+          <t>Xa bing chilling</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>15288</v>
+        <v>14603</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>329510</v>
+        <v>949628</v>
       </c>
       <c r="H19" t="n">
-        <v>538046</v>
+        <v>515830</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4309,35 +4309,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prateek gupta</t>
+          <t>Pranav Thomas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sakalaka</t>
+          <t>Invincibles</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>117338</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>4684930</v>
-      </c>
-      <c r="H31" t="n">
-        <v>117338</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -4346,16 +4327,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pranav Thomas</t>
+          <t>prateek gupta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Invincibles</t>
+          <t>sakalaka</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>117338</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>4684930</v>
+      </c>
+      <c r="H32" t="n">
+        <v>117338</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4482,19 +4482,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Karan Chopra</t>
+          <t>Ajith Thomas Kuthukatt George</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fpl_26_27</t>
+          <t>Onside Offside</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -4503,13 +4503,13 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>100.2</v>
@@ -4536,26 +4536,26 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>398774</v>
+        <v>662331</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anish Joshi</t>
+          <t>Karan Chopra</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fiery Raiders</t>
+          <t>fpl_26_27</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -4564,19 +4564,19 @@
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -4585,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
         <v>100.2</v>
@@ -4594,33 +4594,29 @@
         <v>0.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>559579</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>bboost</t>
-        </is>
-      </c>
+        <v>398774</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ajith Thomas Kuthukatt George</t>
+          <t>Anish Joshi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Onside Offside</t>
+          <t>Fiery Raiders</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -4629,19 +4625,19 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -4650,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>100.2</v>
@@ -4659,12 +4655,16 @@
         <v>0.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R4" t="n">
-        <v>662331</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>559579</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>bboost</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4678,7 +4678,7 @@
         </is>
       <